--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael\Desktop\Abnahmen_DGUV3_Lokal\10. Test\FlexPos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD456E6-73CF-403F-863F-91CCF38D6D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB609007-E86D-4854-BB39-42874B6F1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="111">
   <si>
     <t>Oberordner</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>Digital Signage</t>
+  </si>
+  <si>
+    <t>SCO 89 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 89 Kabelreserve</t>
   </si>
 </sst>
 </file>
@@ -367,6 +373,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -433,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -446,15 +453,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -809,690 +812,690 @@
         <v>12</v>
       </c>
       <c r="B2" s="6"/>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="4"/>
+      <c r="C10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="4"/>
+      <c r="C21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="4"/>
+      <c r="C25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="4"/>
+      <c r="C27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8" t="s">
+      <c r="B33" s="4"/>
+      <c r="C33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8" t="s">
+      <c r="B34" s="4"/>
+      <c r="C34" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="8" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="8" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="7"/>
-      <c r="C48" s="8" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="8" t="s">
+      <c r="B50" s="4"/>
+      <c r="C50" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="B52" s="4"/>
+      <c r="C52" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="4"/>
+      <c r="C54" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="8" t="s">
+      <c r="B55" s="4"/>
+      <c r="C55" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="4"/>
+      <c r="C56" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="4"/>
+      <c r="C58" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="4"/>
+      <c r="C59" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="4"/>
+      <c r="C60" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="8" t="s">
+      <c r="B61" s="4"/>
+      <c r="C61" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="8" t="s">
+      <c r="B62" s="4"/>
+      <c r="C62" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="4"/>
+      <c r="C63" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="4"/>
+      <c r="C64" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="8" t="s">
+      <c r="B65" s="4"/>
+      <c r="C65" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="8" t="s">
+      <c r="B66" s="4"/>
+      <c r="C66" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="5">
         <v>1</v>
       </c>
     </row>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael\Desktop\Abnahmen_DGUV3_Lokal\10. Test\FlexPos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB609007-E86D-4854-BB39-42874B6F1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0052AF4-BDF7-43B2-A223-33231B1EBC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="424">
   <si>
     <t>Oberordner</t>
   </si>
@@ -35,57 +35,9 @@
     <t>Pflichtanzahl</t>
   </si>
   <si>
-    <t>02_Serverraum</t>
-  </si>
-  <si>
-    <t>NWS-Schrank</t>
-  </si>
-  <si>
-    <t>Schrank_geschlossen</t>
-  </si>
-  <si>
-    <t>Schrank_offen</t>
-  </si>
-  <si>
-    <t>Patchpanel</t>
-  </si>
-  <si>
-    <t>Patchfeld</t>
-  </si>
-  <si>
-    <t>Uebersicht_Serverraum</t>
-  </si>
-  <si>
-    <t>03_Verkabelung</t>
-  </si>
-  <si>
     <t>Kassenzone</t>
   </si>
   <si>
-    <t>Kabelweg_Kasse</t>
-  </si>
-  <si>
-    <t>Lager</t>
-  </si>
-  <si>
-    <t>Kabelweg_Lager</t>
-  </si>
-  <si>
-    <t>Uebersicht_Verkabelung</t>
-  </si>
-  <si>
-    <t>04_Accesspoints</t>
-  </si>
-  <si>
-    <t>AP_Montage</t>
-  </si>
-  <si>
-    <t>05_Abschluss</t>
-  </si>
-  <si>
-    <t>Baustelle_aufgeraeumt</t>
-  </si>
-  <si>
     <t>01_Maengel</t>
   </si>
   <si>
@@ -350,10 +302,997 @@
     <t>Digital Signage</t>
   </si>
   <si>
-    <t>SCO 89 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 89 Kabelreserve</t>
+    <t>02_Pfandraum</t>
+  </si>
+  <si>
+    <t>Pfand 1 Dose</t>
+  </si>
+  <si>
+    <t>Pfand 2 Dose</t>
+  </si>
+  <si>
+    <t>Pfand 3 Dose</t>
+  </si>
+  <si>
+    <t>Pfand Reserve Dose</t>
+  </si>
+  <si>
+    <t>Pfand gesamt Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 1 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 1 Totale</t>
+  </si>
+  <si>
+    <t>03_Backnische</t>
+  </si>
+  <si>
+    <t>BA 01 + 02 Dose</t>
+  </si>
+  <si>
+    <t>BA 01 + 02 Totale</t>
+  </si>
+  <si>
+    <t>BA 03 + 04 Dose</t>
+  </si>
+  <si>
+    <t>BA 03 + 04 Totale</t>
+  </si>
+  <si>
+    <t>BA 05 + 06 Dose</t>
+  </si>
+  <si>
+    <t>BA 05 + 06 Totale</t>
+  </si>
+  <si>
+    <t>BA 07 + 08 Dose</t>
+  </si>
+  <si>
+    <t>BA 07 + 08 Totale</t>
+  </si>
+  <si>
+    <t>BA Totale</t>
+  </si>
+  <si>
+    <t>BakeOff 1 + BakeOff 2 Dose</t>
+  </si>
+  <si>
+    <t>BakeOff 1 + BakeOff2 Totale</t>
+  </si>
+  <si>
+    <t>04_Aktenraum</t>
+  </si>
+  <si>
+    <t>Thin Client + Res</t>
+  </si>
+  <si>
+    <t>Drucker + FAX</t>
+  </si>
+  <si>
+    <t>TEL + Res</t>
+  </si>
+  <si>
+    <t>Aktenraum Totale</t>
+  </si>
+  <si>
+    <t>Cashmaschine</t>
+  </si>
+  <si>
+    <t>Cashmaschine Totale</t>
+  </si>
+  <si>
+    <t>Kleinverteiler Ports</t>
+  </si>
+  <si>
+    <t>Kleinverteiler offen</t>
+  </si>
+  <si>
+    <t>Kleinverteiler Totale</t>
+  </si>
+  <si>
+    <t>Kabelcodierung Aktenraum</t>
+  </si>
+  <si>
+    <t>Geldwage</t>
+  </si>
+  <si>
+    <t>Serien-/LIN-Nummern</t>
+  </si>
+  <si>
+    <t>ELO</t>
+  </si>
+  <si>
+    <t>SN ELO</t>
+  </si>
+  <si>
+    <t>LIN ELO</t>
+  </si>
+  <si>
+    <t>SN Geldwage</t>
+  </si>
+  <si>
+    <t>LIN Geldwage</t>
+  </si>
+  <si>
+    <t>SN Drucker</t>
+  </si>
+  <si>
+    <t>Nachweis</t>
+  </si>
+  <si>
+    <t>Anmeldemaske BO</t>
+  </si>
+  <si>
+    <t>PZE online</t>
+  </si>
+  <si>
+    <t>KWLAN</t>
+  </si>
+  <si>
+    <t>Registrierung Vocovo Telefone</t>
+  </si>
+  <si>
+    <t>FTTH</t>
+  </si>
+  <si>
+    <t>FTTH Anschluß Dose</t>
+  </si>
+  <si>
+    <t>FTTH Anschluß Totale</t>
+  </si>
+  <si>
+    <t>FTTH Modem</t>
+  </si>
+  <si>
+    <t>FTTH Modem Totale</t>
+  </si>
+  <si>
+    <t>05_Filiallager</t>
+  </si>
+  <si>
+    <t>1. Lager + 2. Lager</t>
+  </si>
+  <si>
+    <t>1. Lager + 2. Lager Totale</t>
+  </si>
+  <si>
+    <t>3. Lager + 4. Lager</t>
+  </si>
+  <si>
+    <t>3. Lager + 4. Lager Totale</t>
+  </si>
+  <si>
+    <t>Xweb Dose</t>
+  </si>
+  <si>
+    <t>Xweb Totale</t>
+  </si>
+  <si>
+    <t>06_Technikebene</t>
+  </si>
+  <si>
+    <t>L-Box Dose</t>
+  </si>
+  <si>
+    <t>L-Box Totale</t>
+  </si>
+  <si>
+    <t>Integral / Wago Dose</t>
+  </si>
+  <si>
+    <t>Integral / Wago Totale</t>
+  </si>
+  <si>
+    <t>AP1 Dose</t>
+  </si>
+  <si>
+    <t>AP1 Totale</t>
+  </si>
+  <si>
+    <t>AP1 Brandschott</t>
+  </si>
+  <si>
+    <t>AP2 Dose</t>
+  </si>
+  <si>
+    <t>AP2 Totale</t>
+  </si>
+  <si>
+    <t>AP2 Brandschott</t>
+  </si>
+  <si>
+    <t>AP3 Dose</t>
+  </si>
+  <si>
+    <t>AP3 Totale</t>
+  </si>
+  <si>
+    <t>AP3 Brandschott</t>
+  </si>
+  <si>
+    <t>AP4 Dose</t>
+  </si>
+  <si>
+    <t>AP4 Totale</t>
+  </si>
+  <si>
+    <t>AP4 Brandschott</t>
+  </si>
+  <si>
+    <t>AP5 Dose</t>
+  </si>
+  <si>
+    <t>AP5 Totale</t>
+  </si>
+  <si>
+    <t>AP5 Brandschott</t>
+  </si>
+  <si>
+    <t>AP6 Dose</t>
+  </si>
+  <si>
+    <t>AP6 Totale</t>
+  </si>
+  <si>
+    <t>AP6 Brandschott</t>
+  </si>
+  <si>
+    <t>AP7 Dose</t>
+  </si>
+  <si>
+    <t>AP7 Totale</t>
+  </si>
+  <si>
+    <t>AP7 Brandschott</t>
+  </si>
+  <si>
+    <t>AP8 Dose</t>
+  </si>
+  <si>
+    <t>AP8 Totale</t>
+  </si>
+  <si>
+    <t>AP8 Brandschott</t>
+  </si>
+  <si>
+    <t>AP9 Dose</t>
+  </si>
+  <si>
+    <t>AP9 Totale</t>
+  </si>
+  <si>
+    <t>AP9 Brandschott</t>
+  </si>
+  <si>
+    <t>AP10 Dose</t>
+  </si>
+  <si>
+    <t>AP10 Totale</t>
+  </si>
+  <si>
+    <t>AP10 Brandschott</t>
+  </si>
+  <si>
+    <t>AP11 Dose</t>
+  </si>
+  <si>
+    <t>AP11 Totale</t>
+  </si>
+  <si>
+    <t>AP11 Brandschott</t>
+  </si>
+  <si>
+    <t>AP12 Dose</t>
+  </si>
+  <si>
+    <t>AP12 Totale</t>
+  </si>
+  <si>
+    <t>AP12 Brandschott</t>
+  </si>
+  <si>
+    <t>AP13 Dose</t>
+  </si>
+  <si>
+    <t>AP13 Totale</t>
+  </si>
+  <si>
+    <t>AP13 Brandschott</t>
+  </si>
+  <si>
+    <t>AP14 Dose</t>
+  </si>
+  <si>
+    <t>AP14 Totale</t>
+  </si>
+  <si>
+    <t>AP14 Brandschott</t>
+  </si>
+  <si>
+    <t>AP15 Dose</t>
+  </si>
+  <si>
+    <t>AP15 Totale</t>
+  </si>
+  <si>
+    <t>AP15 Brandschott</t>
+  </si>
+  <si>
+    <t>AP16 Dose</t>
+  </si>
+  <si>
+    <t>AP16 Totale</t>
+  </si>
+  <si>
+    <t>AP16 Brandschott</t>
+  </si>
+  <si>
+    <t>07_Accesspoints</t>
+  </si>
+  <si>
+    <t>AP1</t>
+  </si>
+  <si>
+    <t>AP2</t>
+  </si>
+  <si>
+    <t>AP3</t>
+  </si>
+  <si>
+    <t>AP4</t>
+  </si>
+  <si>
+    <t>AP5</t>
+  </si>
+  <si>
+    <t>AP6</t>
+  </si>
+  <si>
+    <t>AP7</t>
+  </si>
+  <si>
+    <t>AP8</t>
+  </si>
+  <si>
+    <t>AP9</t>
+  </si>
+  <si>
+    <t>AP10</t>
+  </si>
+  <si>
+    <t>AP11</t>
+  </si>
+  <si>
+    <t>AP12</t>
+  </si>
+  <si>
+    <t>AP13</t>
+  </si>
+  <si>
+    <t>AP14</t>
+  </si>
+  <si>
+    <t>AP15</t>
+  </si>
+  <si>
+    <t>AP16</t>
+  </si>
+  <si>
+    <t>SN AP1</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP1</t>
+  </si>
+  <si>
+    <t>LIN AP1</t>
+  </si>
+  <si>
+    <t>IoT AP1</t>
+  </si>
+  <si>
+    <t>SN AP2</t>
+  </si>
+  <si>
+    <t>LIN AP2</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP2</t>
+  </si>
+  <si>
+    <t>IoT AP2</t>
+  </si>
+  <si>
+    <t>SN AP3</t>
+  </si>
+  <si>
+    <t>LIN AP3</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP3</t>
+  </si>
+  <si>
+    <t>IoT AP3</t>
+  </si>
+  <si>
+    <t>SN AP4</t>
+  </si>
+  <si>
+    <t>LIN AP4</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP4</t>
+  </si>
+  <si>
+    <t>IoT AP4</t>
+  </si>
+  <si>
+    <t>SN AP5</t>
+  </si>
+  <si>
+    <t>LIN AP5</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP5</t>
+  </si>
+  <si>
+    <t>IoT AP5</t>
+  </si>
+  <si>
+    <t>SN AP6</t>
+  </si>
+  <si>
+    <t>LIN AP6</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP6</t>
+  </si>
+  <si>
+    <t>IoT AP6</t>
+  </si>
+  <si>
+    <t>SN AP7</t>
+  </si>
+  <si>
+    <t>LIN AP7</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP7</t>
+  </si>
+  <si>
+    <t>IoT AP7</t>
+  </si>
+  <si>
+    <t>SN AP8</t>
+  </si>
+  <si>
+    <t>LIN AP8</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP8</t>
+  </si>
+  <si>
+    <t>IoT AP8</t>
+  </si>
+  <si>
+    <t>SN AP9</t>
+  </si>
+  <si>
+    <t>LIN AP9</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP9</t>
+  </si>
+  <si>
+    <t>IoT AP9</t>
+  </si>
+  <si>
+    <t>SN AP10</t>
+  </si>
+  <si>
+    <t>LIN AP10</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP10</t>
+  </si>
+  <si>
+    <t>IoT AP10</t>
+  </si>
+  <si>
+    <t>SN AP11</t>
+  </si>
+  <si>
+    <t>LIN AP11</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP11</t>
+  </si>
+  <si>
+    <t>IoT AP11</t>
+  </si>
+  <si>
+    <t>SN AP12</t>
+  </si>
+  <si>
+    <t>LIN AP12</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP12</t>
+  </si>
+  <si>
+    <t>IoT AP12</t>
+  </si>
+  <si>
+    <t>SN AP13</t>
+  </si>
+  <si>
+    <t>LIN AP13</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP13</t>
+  </si>
+  <si>
+    <t>IoT AP13</t>
+  </si>
+  <si>
+    <t>SN AP14</t>
+  </si>
+  <si>
+    <t>LIN AP14</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP14</t>
+  </si>
+  <si>
+    <t>IoT AP14</t>
+  </si>
+  <si>
+    <t>SN AP15</t>
+  </si>
+  <si>
+    <t>LIN AP15</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP15</t>
+  </si>
+  <si>
+    <t>IoT AP15</t>
+  </si>
+  <si>
+    <t>SN AP16</t>
+  </si>
+  <si>
+    <t>LIN AP16</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP16</t>
+  </si>
+  <si>
+    <t>IoT AP16</t>
+  </si>
+  <si>
+    <t>08_Sozialräume</t>
+  </si>
+  <si>
+    <t>Lili Dose</t>
+  </si>
+  <si>
+    <t>Lili Totale</t>
+  </si>
+  <si>
+    <t>PZE Dose</t>
+  </si>
+  <si>
+    <t>PZE Totale</t>
+  </si>
+  <si>
+    <t>PZE gesamt</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2 Dose</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2Totale</t>
+  </si>
+  <si>
+    <t>Headset Strom</t>
+  </si>
+  <si>
+    <t>Headset Totale</t>
+  </si>
+  <si>
+    <t>SN MAT</t>
+  </si>
+  <si>
+    <t>LIN MAT</t>
+  </si>
+  <si>
+    <t>LIN PZE</t>
+  </si>
+  <si>
+    <t>SN Headsets</t>
+  </si>
+  <si>
+    <t>LIN Headset 2</t>
+  </si>
+  <si>
+    <t>LIN Headset 3</t>
+  </si>
+  <si>
+    <t>LIN Headset 4</t>
+  </si>
+  <si>
+    <t>09_Vocovo</t>
+  </si>
+  <si>
+    <t>Vocovo 1</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 2</t>
+  </si>
+  <si>
+    <t>Vocovo 3</t>
+  </si>
+  <si>
+    <t>Vocovo 4</t>
+  </si>
+  <si>
+    <t>Vocovo 5</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal Headsets Modul</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal Headsets Totale</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal</t>
+  </si>
+  <si>
+    <t>10_Serverraum</t>
+  </si>
+  <si>
+    <t>Netzwerkschränke Vorderseite</t>
+  </si>
+  <si>
+    <t>Netzwerkschränke Rückseite</t>
+  </si>
+  <si>
+    <t>Kabelverlegung Serverraum</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail mitte Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 1 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 1 Erdung</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 1</t>
+  </si>
+  <si>
+    <t>SN Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>LIN Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>Beschriftung Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>SN Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>LIN Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>Beschriftung Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>SN Huawei S5735-12P WAN-Switche 1</t>
+  </si>
+  <si>
+    <t>LIN + Beschr Huawei S5735-12P WAN-Switche 1</t>
+  </si>
+  <si>
+    <t>SN Huawei S5735-12P WAN-Switche 2</t>
+  </si>
+  <si>
+    <t>LIN + Besch Huawei S5735-12P WAN-Switche 2</t>
+  </si>
+  <si>
+    <t>SN Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>LIN Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>SN Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>LIN Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>SN Server</t>
+  </si>
+  <si>
+    <t>LIN Server</t>
+  </si>
+  <si>
+    <t>LIN HGA-Kasse 1</t>
+  </si>
+  <si>
+    <t>SN HGA-Kasse 1</t>
+  </si>
+  <si>
+    <t>SN PZE</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 2</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail mitte Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 2 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 2 Erdung</t>
+  </si>
+  <si>
+    <t>Switch 1 gepatcht</t>
+  </si>
+  <si>
+    <t>Switch 2 gepatcht</t>
+  </si>
+  <si>
+    <t>Switch 3 gepatcht</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 2</t>
+  </si>
+  <si>
+    <t>SN Frederix</t>
+  </si>
+  <si>
+    <t>LIN Frederix</t>
+  </si>
+  <si>
+    <t>SN Baracuda</t>
+  </si>
+  <si>
+    <t>LIN Baracuda</t>
+  </si>
+  <si>
+    <t>NWS 1 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>NWS 2 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>SN Switch 1</t>
+  </si>
+  <si>
+    <t>LIN Switch 1</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 1</t>
+  </si>
+  <si>
+    <t>SN Switch 2</t>
+  </si>
+  <si>
+    <t>LIN Switch 2</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 2</t>
+  </si>
+  <si>
+    <t>SN Switch 3</t>
+  </si>
+  <si>
+    <t>LIN Switch 3</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 3</t>
+  </si>
+  <si>
+    <t>SN Switch 4</t>
+  </si>
+  <si>
+    <t>LIN Switch 4</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 4</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 3</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 3 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 3 Erdung</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 3</t>
+  </si>
+  <si>
+    <t>NWS 3 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>SN AcessA</t>
+  </si>
+  <si>
+    <t>SN AcessB</t>
+  </si>
+  <si>
+    <t>SN LTE-Router Access A</t>
+  </si>
+  <si>
+    <t>SN LTE-Router Access B</t>
+  </si>
+  <si>
+    <t>NWS-UV</t>
+  </si>
+  <si>
+    <t>NWS-UV Front</t>
+  </si>
+  <si>
+    <t>Kabelführung Datenkabel NWS-UV</t>
+  </si>
+  <si>
+    <t>Erdung im NWS-UV</t>
+  </si>
+  <si>
+    <t>Abzweigdose + Potischiene überm NWS-UV</t>
+  </si>
+  <si>
+    <t>NWS-UV geschlossen Totale</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS-UV</t>
+  </si>
+  <si>
+    <t>Digitales Backschema</t>
+  </si>
+  <si>
+    <t>SN_KVM Switch</t>
+  </si>
+  <si>
+    <t>LIN_KVM Switch</t>
+  </si>
+  <si>
+    <t>Plantasche NWS</t>
+  </si>
+  <si>
+    <t>Kabelwege Pfand</t>
+  </si>
+  <si>
+    <t>Kabelwege Backnische</t>
+  </si>
+  <si>
+    <t>Kabelwege Kassenzone</t>
+  </si>
+  <si>
+    <t>Kabelwege Aktenraum</t>
+  </si>
+  <si>
+    <t>Kabelwege Filiallager</t>
+  </si>
+  <si>
+    <t>Kabelwege Technikebene</t>
+  </si>
+  <si>
+    <t>Kabelwege Sozialräume</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 1</t>
   </si>
 </sst>
 </file>
@@ -373,7 +1312,6 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -440,7 +1378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -460,6 +1398,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -784,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -809,11 +1751,11 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="7" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D2" s="8">
         <v>1</v>
@@ -823,7 +1765,7 @@
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -833,7 +1775,7 @@
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -843,7 +1785,7 @@
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -853,7 +1795,7 @@
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -863,29 +1805,29 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1</v>
+        <v>418</v>
+      </c>
+      <c r="D8" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="C9" s="7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
@@ -895,7 +1837,7 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D10" s="5">
         <v>1</v>
@@ -903,11 +1845,9 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
-        <v>33</v>
-      </c>
+      <c r="B11" s="4"/>
       <c r="C11" s="7" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -915,9 +1855,11 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C12" s="7" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -927,7 +1869,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -935,11 +1877,9 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="B14" s="4"/>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -947,9 +1887,11 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="C15" s="7" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -959,7 +1901,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -967,11 +1909,9 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="B17" s="4"/>
       <c r="C17" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -979,9 +1919,11 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="C18" s="7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -991,7 +1933,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -999,11 +1941,9 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -1011,9 +1951,11 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="C21" s="7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -1023,7 +1965,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="7" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -1031,11 +1973,9 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="B23" s="4"/>
       <c r="C23" s="7" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -1043,9 +1983,11 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="C24" s="7" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -1055,7 +1997,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -1063,11 +2005,9 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="B26" s="4"/>
       <c r="C26" s="7" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D26" s="5">
         <v>1</v>
@@ -1075,9 +2015,11 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="C27" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -1087,7 +2029,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -1095,11 +2037,9 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
-      <c r="B29" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="B29" s="4"/>
       <c r="C29" s="7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -1107,9 +2047,11 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="C30" s="7" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5">
         <v>1</v>
@@ -1119,7 +2061,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
@@ -1127,11 +2069,9 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="B32" s="4"/>
       <c r="C32" s="7" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D32" s="5">
         <v>1</v>
@@ -1139,9 +2079,11 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="C33" s="7" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -1151,7 +2093,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="7" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -1159,11 +2101,9 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="B35" s="4"/>
       <c r="C35" s="7" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
@@ -1171,9 +2111,11 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="C36" s="7" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
@@ -1181,11 +2123,9 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
-      <c r="B37" s="4" t="s">
-        <v>79</v>
-      </c>
+      <c r="B37" s="4"/>
       <c r="C37" s="7" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -1193,9 +2133,11 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="C38" s="7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
@@ -1203,11 +2145,9 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
-      <c r="B39" s="4" t="s">
-        <v>80</v>
-      </c>
+      <c r="B39" s="4"/>
       <c r="C39" s="7" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
@@ -1215,9 +2155,11 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
+      <c r="B40" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="C40" s="7" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
@@ -1225,11 +2167,9 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -1237,9 +2177,11 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="C42" s="7" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
@@ -1247,11 +2189,9 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
-      <c r="B43" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="B43" s="4"/>
       <c r="C43" s="7" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
@@ -1259,9 +2199,11 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
+      <c r="B44" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="C44" s="7" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -1269,11 +2211,9 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
-      <c r="B45" s="4" t="s">
-        <v>83</v>
-      </c>
+      <c r="B45" s="4"/>
       <c r="C45" s="7" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
@@ -1281,9 +2221,11 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
+      <c r="B46" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="C46" s="7" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D46" s="5">
         <v>1</v>
@@ -1291,11 +2233,9 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
-      <c r="B47" s="4" t="s">
-        <v>84</v>
-      </c>
+      <c r="B47" s="4"/>
       <c r="C47" s="7" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="D47" s="5">
         <v>1</v>
@@ -1303,9 +2243,11 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
+      <c r="B48" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="C48" s="7" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -1313,11 +2255,9 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
-      <c r="B49" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="B49" s="4"/>
       <c r="C49" s="7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D49" s="5">
         <v>1</v>
@@ -1325,9 +2265,11 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
+      <c r="B50" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="C50" s="7" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D50" s="5">
         <v>1</v>
@@ -1335,11 +2277,9 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
-      <c r="B51" s="4" t="s">
-        <v>86</v>
-      </c>
+      <c r="B51" s="4"/>
       <c r="C51" s="7" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -1347,9 +2287,11 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
+      <c r="B52" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="C52" s="7" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -1357,11 +2299,9 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
-      <c r="B53" s="4" t="s">
-        <v>87</v>
-      </c>
+      <c r="B53" s="4"/>
       <c r="C53" s="7" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D53" s="5">
         <v>1</v>
@@ -1369,9 +2309,11 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
+      <c r="B54" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="C54" s="7" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D54" s="5">
         <v>1</v>
@@ -1381,7 +2323,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -1391,7 +2333,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
@@ -1399,11 +2341,9 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4"/>
-      <c r="B57" s="4" t="s">
-        <v>108</v>
-      </c>
+      <c r="B57" s="4"/>
       <c r="C57" s="7" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D57" s="5">
         <v>1</v>
@@ -1411,9 +2351,11 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
+      <c r="B58" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="C58" s="7" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -1423,7 +2365,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D59" s="5">
         <v>1</v>
@@ -1433,7 +2375,7 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="7" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
@@ -1443,7 +2385,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="7" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
@@ -1453,7 +2395,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="7" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>
@@ -1463,7 +2405,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="7" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="D63" s="5">
         <v>1</v>
@@ -1473,7 +2415,7 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="7" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
@@ -1483,7 +2425,7 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="7" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D65" s="5">
         <v>1</v>
@@ -1493,21 +2435,17 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="7" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>6</v>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
@@ -1515,112 +2453,3230 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>7</v>
+        <v>93</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>9</v>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
+      <c r="C69" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="D69" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="A70" s="4"/>
       <c r="B70" s="4"/>
-      <c r="C70" s="4" t="s">
-        <v>10</v>
+      <c r="C70" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>13</v>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
+      <c r="C71" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="D71" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
+      <c r="C73" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
+      <c r="C74" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D75" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D72" s="5">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D76" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D77" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
+      <c r="C78" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D78" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
+      <c r="C80" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
+      <c r="C81" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D81" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D82" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D83" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D85" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D87" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D74" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D75" s="5">
-        <v>1</v>
-      </c>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D88" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="4"/>
+      <c r="C89" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D90" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D91" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D92" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D94" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
+      <c r="C97" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D97" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
+      <c r="C98" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
+      <c r="C99" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
+      <c r="C100" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D100" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
+      <c r="C101" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D101" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="4"/>
+      <c r="B102" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D102" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
+      <c r="C103" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D103" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
+      <c r="C104" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D104" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
+      <c r="C105" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D105" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
+      <c r="C106" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D106" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
+      <c r="C107" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="D107" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
+      <c r="C108" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="D108" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="4"/>
+      <c r="B109" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D109" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
+      <c r="C110" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D110" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
+      <c r="C111" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D111" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
+      <c r="C112" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D112" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D113" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
+      <c r="C114" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D114" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
+      <c r="C115" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D115" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
+      <c r="C116" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D116" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
+      <c r="C117" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
+      <c r="C118" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D118" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
+      <c r="C119" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D119" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="4"/>
+      <c r="C120" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D120" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
+      <c r="C121" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D121" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D122" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
+      <c r="C123" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D123" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
+      <c r="C124" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D124" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D125" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
+      <c r="C126" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D126" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
+      <c r="C127" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D127" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
+      <c r="C128" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D128" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
+      <c r="C129" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D129" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
+      <c r="C130" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D130" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
+      <c r="C131" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D131" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="4"/>
+      <c r="B132" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D132" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
+      <c r="C133" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D133" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
+      <c r="C134" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D134" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D135" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="4"/>
+      <c r="B136" s="4"/>
+      <c r="C136" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D136" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="4"/>
+      <c r="B137" s="4"/>
+      <c r="C137" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D137" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="4"/>
+      <c r="B138" s="4"/>
+      <c r="C138" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D138" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="4"/>
+      <c r="B139" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D139" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="4"/>
+      <c r="B140" s="4"/>
+      <c r="C140" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D140" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
+      <c r="C141" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D141" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D142" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D143" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D144" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
+      <c r="C145" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D145" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="4"/>
+      <c r="B146" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
+      <c r="C147" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D147" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
+      <c r="C148" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D148" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
+      <c r="C149" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D149" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
+      <c r="C150" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D150" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D151" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
+      <c r="C152" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D152" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="4"/>
+      <c r="B153" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D153" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
+      <c r="C154" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D154" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
+      <c r="C155" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D155" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+      <c r="C156" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D156" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="4"/>
+      <c r="B157" s="4"/>
+      <c r="C157" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D157" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
+      <c r="C158" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D158" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
+      <c r="C159" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D159" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="4"/>
+      <c r="B160" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D160" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
+      <c r="C161" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D161" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
+      <c r="C162" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D162" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
+      <c r="C163" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D163" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D164" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D165" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" s="4"/>
+      <c r="B166" s="4"/>
+      <c r="C166" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D166" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" s="4"/>
+      <c r="B167" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D167" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" s="4"/>
+      <c r="B168" s="4"/>
+      <c r="C168" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D168" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" s="4"/>
+      <c r="B169" s="4"/>
+      <c r="C169" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D169" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" s="4"/>
+      <c r="B170" s="4"/>
+      <c r="C170" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D170" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" s="4"/>
+      <c r="B171" s="4"/>
+      <c r="C171" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D171" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" s="4"/>
+      <c r="B172" s="4"/>
+      <c r="C172" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D172" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" s="4"/>
+      <c r="B173" s="4"/>
+      <c r="C173" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D173" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" s="4"/>
+      <c r="B174" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D174" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" s="4"/>
+      <c r="B175" s="4"/>
+      <c r="C175" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D175" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" s="4"/>
+      <c r="B176" s="4"/>
+      <c r="C176" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D176" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" s="4"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D177" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" s="4"/>
+      <c r="B178" s="4"/>
+      <c r="C178" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D178" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" s="4"/>
+      <c r="B179" s="4"/>
+      <c r="C179" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D179" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" s="4"/>
+      <c r="B180" s="4"/>
+      <c r="C180" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D180" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" s="4"/>
+      <c r="B181" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D181" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" s="4"/>
+      <c r="B182" s="4"/>
+      <c r="C182" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D182" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" s="4"/>
+      <c r="B183" s="4"/>
+      <c r="C183" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D183" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" s="4"/>
+      <c r="B184" s="4"/>
+      <c r="C184" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="D184" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" s="4"/>
+      <c r="B185" s="4"/>
+      <c r="C185" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D185" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" s="4"/>
+      <c r="B186" s="4"/>
+      <c r="C186" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D186" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" s="4"/>
+      <c r="B187" s="4"/>
+      <c r="C187" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D187" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" s="4"/>
+      <c r="B188" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D188" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" s="4"/>
+      <c r="B189" s="4"/>
+      <c r="C189" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D189" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" s="4"/>
+      <c r="B190" s="4"/>
+      <c r="C190" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D190" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" s="4"/>
+      <c r="B191" s="4"/>
+      <c r="C191" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D191" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" s="4"/>
+      <c r="B192" s="4"/>
+      <c r="C192" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D192" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="4"/>
+      <c r="B193" s="4"/>
+      <c r="C193" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D193" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="4"/>
+      <c r="B194" s="4"/>
+      <c r="C194" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D194" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="4"/>
+      <c r="B195" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D195" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="4"/>
+      <c r="B196" s="4"/>
+      <c r="C196" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D196" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="4"/>
+      <c r="B197" s="4"/>
+      <c r="C197" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D197" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="4"/>
+      <c r="B198" s="4"/>
+      <c r="C198" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D198" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="4"/>
+      <c r="B199" s="4"/>
+      <c r="C199" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D199" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="4"/>
+      <c r="B200" s="4"/>
+      <c r="C200" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D200" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="4"/>
+      <c r="B201" s="4"/>
+      <c r="C201" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="D201" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="4"/>
+      <c r="B202" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D202" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="4"/>
+      <c r="B203" s="4"/>
+      <c r="C203" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D203" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="4"/>
+      <c r="B204" s="4"/>
+      <c r="C204" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D204" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="4"/>
+      <c r="B205" s="4"/>
+      <c r="C205" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D205" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="4"/>
+      <c r="B206" s="4"/>
+      <c r="C206" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D206" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="4"/>
+      <c r="B207" s="4"/>
+      <c r="C207" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D207" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="4"/>
+      <c r="B208" s="4"/>
+      <c r="C208" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D208" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" s="4"/>
+      <c r="B209" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D209" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" s="4"/>
+      <c r="B210" s="4"/>
+      <c r="C210" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D210" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" s="4"/>
+      <c r="B211" s="4"/>
+      <c r="C211" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D211" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" s="4"/>
+      <c r="B212" s="4"/>
+      <c r="C212" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D212" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" s="4"/>
+      <c r="B213" s="4"/>
+      <c r="C213" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D213" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" s="4"/>
+      <c r="B214" s="4"/>
+      <c r="C214" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D214" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" s="4"/>
+      <c r="B215" s="4"/>
+      <c r="C215" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D215" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" s="4"/>
+      <c r="B216" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D216" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" s="4"/>
+      <c r="B217" s="4"/>
+      <c r="C217" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D217" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" s="4"/>
+      <c r="B218" s="4"/>
+      <c r="C218" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D218" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" s="4"/>
+      <c r="B219" s="4"/>
+      <c r="C219" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D219" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" s="4"/>
+      <c r="B220" s="4"/>
+      <c r="C220" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D220" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" s="4"/>
+      <c r="B221" s="4"/>
+      <c r="C221" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D221" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" s="4"/>
+      <c r="B222" s="4"/>
+      <c r="C222" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D222" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" s="4"/>
+      <c r="B223" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D223" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" s="4"/>
+      <c r="B224" s="4"/>
+      <c r="C224" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D224" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" s="4"/>
+      <c r="B225" s="4"/>
+      <c r="C225" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D225" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" s="4"/>
+      <c r="B226" s="4"/>
+      <c r="C226" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D226" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" s="4"/>
+      <c r="B227" s="4"/>
+      <c r="C227" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D227" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" s="4"/>
+      <c r="B228" s="4"/>
+      <c r="C228" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D228" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" s="4"/>
+      <c r="B229" s="4"/>
+      <c r="C229" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D229" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" s="4"/>
+      <c r="B230" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D230" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" s="4"/>
+      <c r="B231" s="4"/>
+      <c r="C231" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D231" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" s="4"/>
+      <c r="B232" s="4"/>
+      <c r="C232" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D232" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" s="4"/>
+      <c r="B233" s="4"/>
+      <c r="C233" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D233" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" s="4"/>
+      <c r="B234" s="4"/>
+      <c r="C234" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D234" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" s="4"/>
+      <c r="B235" s="4"/>
+      <c r="C235" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D235" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" s="4"/>
+      <c r="B236" s="4"/>
+      <c r="C236" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D236" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B237" s="4"/>
+      <c r="C237" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D237" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" s="4"/>
+      <c r="B238" s="4"/>
+      <c r="C238" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D238" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" s="4"/>
+      <c r="B239" s="4"/>
+      <c r="C239" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D239" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" s="4"/>
+      <c r="B240" s="4"/>
+      <c r="C240" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D240" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" s="4"/>
+      <c r="B241" s="4"/>
+      <c r="C241" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D241" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" s="4"/>
+      <c r="B242" s="4"/>
+      <c r="C242" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D242" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" s="4"/>
+      <c r="B243" s="4"/>
+      <c r="C243" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D243" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" s="4"/>
+      <c r="B244" s="4"/>
+      <c r="C244" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D244" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" s="4"/>
+      <c r="B245" s="4"/>
+      <c r="C245" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D245" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" s="4"/>
+      <c r="B246" s="4"/>
+      <c r="C246" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D246" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" s="4"/>
+      <c r="B247" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D247" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" s="4"/>
+      <c r="B248" s="4"/>
+      <c r="C248" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D248" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A249" s="4"/>
+      <c r="B249" s="4"/>
+      <c r="C249" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D249" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A250" s="4"/>
+      <c r="B250" s="4"/>
+      <c r="C250" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D250" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A251" s="4"/>
+      <c r="B251" s="4"/>
+      <c r="C251" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D251" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A252" s="4"/>
+      <c r="B252" s="4"/>
+      <c r="C252" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D252" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A253" s="4"/>
+      <c r="B253" s="4"/>
+      <c r="C253" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D253" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A254" s="4"/>
+      <c r="B254" s="4"/>
+      <c r="C254" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D254" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C255" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D255" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A256" s="4"/>
+      <c r="B256" s="4"/>
+      <c r="C256" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D256" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A257" s="4"/>
+      <c r="B257" s="4"/>
+      <c r="C257" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D257" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A258" s="4"/>
+      <c r="B258" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D258" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A259" s="4"/>
+      <c r="B259" s="4"/>
+      <c r="C259" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D259" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A260" s="4"/>
+      <c r="B260" s="4"/>
+      <c r="C260" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D260" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A261" s="4"/>
+      <c r="B261" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D261" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A262" s="4"/>
+      <c r="B262" s="4"/>
+      <c r="C262" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D262" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A263" s="4"/>
+      <c r="B263" s="4"/>
+      <c r="C263" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D263" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A264" s="4"/>
+      <c r="B264" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D264" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A265" s="4"/>
+      <c r="B265" s="4"/>
+      <c r="C265" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D265" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A266" s="4"/>
+      <c r="B266" s="4"/>
+      <c r="C266" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D266" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A267" s="4"/>
+      <c r="B267" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D267" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" s="4"/>
+      <c r="B268" s="4"/>
+      <c r="C268" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="D268" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" s="4"/>
+      <c r="B269" s="4"/>
+      <c r="C269" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D269" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" s="4"/>
+      <c r="B270" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C270" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D270" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="4"/>
+      <c r="B271" s="4"/>
+      <c r="C271" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="D271" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B272" s="4"/>
+      <c r="C272" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D272" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A273" s="4"/>
+      <c r="B273" s="4"/>
+      <c r="C273" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D273" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A274" s="4"/>
+      <c r="B274" s="4"/>
+      <c r="C274" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D274" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A275" s="4"/>
+      <c r="B275" s="4"/>
+      <c r="C275" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D275" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B276" s="4"/>
+      <c r="C276" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D276" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A277" s="4"/>
+      <c r="B277" s="4"/>
+      <c r="C277" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="D277" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A278" s="4"/>
+      <c r="B278" s="4"/>
+      <c r="C278" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D278" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A279" s="4"/>
+      <c r="B279" s="4"/>
+      <c r="C279" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D279" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A280" s="4"/>
+      <c r="B280" s="4"/>
+      <c r="C280" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="D280" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A281" s="4"/>
+      <c r="B281" s="4"/>
+      <c r="C281" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D281" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A282" s="4"/>
+      <c r="B282" s="4"/>
+      <c r="C282" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D282" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A283" s="4"/>
+      <c r="B283" s="4"/>
+      <c r="C283" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="D283" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A284" s="4"/>
+      <c r="B284" s="4"/>
+      <c r="C284" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D284" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A285" s="4"/>
+      <c r="B285" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C285" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="D285" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A286" s="4"/>
+      <c r="B286" s="4"/>
+      <c r="C286" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="D286" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A287" s="4"/>
+      <c r="B287" s="4"/>
+      <c r="C287" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D287" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A288" s="4"/>
+      <c r="B288" s="4"/>
+      <c r="C288" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="D288" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="4"/>
+      <c r="B289" s="4"/>
+      <c r="C289" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D289" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A290" s="4"/>
+      <c r="B290" s="4"/>
+      <c r="C290" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D290" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A291" s="4"/>
+      <c r="B291" s="4"/>
+      <c r="C291" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="D291" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A292" s="4"/>
+      <c r="B292" s="4"/>
+      <c r="C292" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="D292" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A293" s="4"/>
+      <c r="B293" s="4"/>
+      <c r="C293" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D293" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A294" s="4"/>
+      <c r="B294" s="4"/>
+      <c r="C294" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D294" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A295" s="4"/>
+      <c r="B295" s="4"/>
+      <c r="C295" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D295" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A296" s="4"/>
+      <c r="B296" s="4"/>
+      <c r="C296" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D296" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A297" s="4"/>
+      <c r="B297" s="4"/>
+      <c r="C297" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D297" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A298" s="4"/>
+      <c r="B298" s="4"/>
+      <c r="C298" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D298" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A299" s="4"/>
+      <c r="B299" s="4"/>
+      <c r="C299" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D299" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A300" s="4"/>
+      <c r="B300" s="4"/>
+      <c r="C300" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="D300" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A301" s="4"/>
+      <c r="B301" s="4"/>
+      <c r="C301" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="D301" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A302" s="4"/>
+      <c r="B302" s="4"/>
+      <c r="C302" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D302" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A303" s="4"/>
+      <c r="B303" s="4"/>
+      <c r="C303" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D303" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A304" s="4"/>
+      <c r="B304" s="4"/>
+      <c r="C304" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="D304" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A305" s="4"/>
+      <c r="B305" s="4"/>
+      <c r="C305" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="D305" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A306" s="4"/>
+      <c r="B306" s="4"/>
+      <c r="C306" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="D306" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A307" s="4"/>
+      <c r="B307" s="4"/>
+      <c r="C307" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="D307" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A308" s="4"/>
+      <c r="B308" s="4"/>
+      <c r="C308" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="D308" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A309" s="4"/>
+      <c r="B309" s="4"/>
+      <c r="C309" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D309" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A310" s="4"/>
+      <c r="B310" s="4"/>
+      <c r="C310" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D310" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B311" s="4"/>
+      <c r="C311" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="D311" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A312" s="4"/>
+      <c r="B312" s="4"/>
+      <c r="C312" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D312" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A313" s="4"/>
+      <c r="B313" s="4"/>
+      <c r="C313" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="D313" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A314" s="4"/>
+      <c r="B314" s="4"/>
+      <c r="C314" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D314" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A315" s="4"/>
+      <c r="B315" s="4"/>
+      <c r="C315" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="D315" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A316" s="4"/>
+      <c r="B316" s="4"/>
+      <c r="C316" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="D316" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A317" s="4"/>
+      <c r="B317" s="4"/>
+      <c r="C317" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D317" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A318" s="4"/>
+      <c r="B318" s="4"/>
+      <c r="C318" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D318" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A319" s="4"/>
+      <c r="B319" s="4"/>
+      <c r="C319" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D319" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A320" s="4"/>
+      <c r="B320" s="4"/>
+      <c r="C320" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="D320" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A321" s="4"/>
+      <c r="B321" s="4"/>
+      <c r="C321" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="D321" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A322" s="4"/>
+      <c r="B322" s="4"/>
+      <c r="C322" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D322" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A323" s="4"/>
+      <c r="B323" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C323" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="D323" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A324" s="4"/>
+      <c r="B324" s="4"/>
+      <c r="C324" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="D324" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A325" s="4"/>
+      <c r="B325" s="4"/>
+      <c r="C325" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D325" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A326" s="4"/>
+      <c r="B326" s="4"/>
+      <c r="C326" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="D326" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A327" s="4"/>
+      <c r="B327" s="4"/>
+      <c r="C327" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="D327" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A328" s="4"/>
+      <c r="B328" s="4"/>
+      <c r="C328" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D328" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A329" s="4"/>
+      <c r="B329" s="4"/>
+      <c r="C329" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="D329" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A330" s="4"/>
+      <c r="B330" s="4"/>
+      <c r="C330" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D330" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A331" s="4"/>
+      <c r="B331" s="4"/>
+      <c r="C331" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D331" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A332" s="4"/>
+      <c r="B332" s="4"/>
+      <c r="C332" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D332" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A333" s="4"/>
+      <c r="B333" s="4"/>
+      <c r="C333" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="D333" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A334" s="4"/>
+      <c r="B334" s="4"/>
+      <c r="C334" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D334" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B335" s="4"/>
+      <c r="C335" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="D335" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A336" s="4"/>
+      <c r="B336" s="4"/>
+      <c r="C336" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="D336" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" s="4"/>
+      <c r="B337" s="4"/>
+      <c r="C337" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D337" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" s="4"/>
+      <c r="B338" s="4"/>
+      <c r="C338" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D338" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" s="4"/>
+      <c r="B339" s="4"/>
+      <c r="C339" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D339" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" s="4"/>
+      <c r="B340" s="4"/>
+      <c r="C340" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="D340" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A341" s="4"/>
+      <c r="B341" s="4"/>
+      <c r="C341" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="D341" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A342" s="4"/>
+      <c r="B342" s="4"/>
+      <c r="C342" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D342" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A343" s="4"/>
+      <c r="B343" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C343" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D343" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A344" s="4"/>
+      <c r="B344" s="4"/>
+      <c r="C344" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="D344" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A345" s="4"/>
+      <c r="B345" s="4"/>
+      <c r="C345" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D345" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A346" s="4"/>
+      <c r="B346" s="4"/>
+      <c r="C346" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="D346" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A347" s="4"/>
+      <c r="B347" s="4"/>
+      <c r="C347" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="D347" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A348" s="4"/>
+      <c r="B348" s="4"/>
+      <c r="C348" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="D348" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B349" s="4"/>
+      <c r="C349" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="D349" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" s="4"/>
+      <c r="B350" s="4"/>
+      <c r="C350" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D350" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" s="4"/>
+      <c r="B351" s="4"/>
+      <c r="C351" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D351" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" s="4"/>
+      <c r="B352" s="4"/>
+      <c r="C352" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D352" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A353" s="4"/>
+      <c r="B353" s="4"/>
+      <c r="C353" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="D353" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A354" s="4"/>
+      <c r="B354" s="4"/>
+      <c r="C354" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="D354" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B355" s="4"/>
+      <c r="C355" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D355" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A356" s="4"/>
+      <c r="B356" s="4"/>
+      <c r="C356" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D356" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A357" s="4"/>
+      <c r="B357" s="4"/>
+      <c r="C357" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D357" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A358" s="4"/>
+      <c r="B358" s="4"/>
+      <c r="C358" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D358" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A359" s="4"/>
+      <c r="B359" s="4"/>
+      <c r="C359" s="10"/>
+      <c r="D359" s="5"/>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A360" s="4"/>
+      <c r="B360" s="4"/>
+      <c r="C360" s="10"/>
+      <c r="D360" s="5"/>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A361" s="4"/>
+      <c r="B361" s="4"/>
+      <c r="C361" s="10"/>
+      <c r="D361" s="5"/>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A362" s="4"/>
+      <c r="B362" s="4"/>
+      <c r="C362" s="10"/>
+      <c r="D362" s="5"/>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A363" s="4"/>
+      <c r="B363" s="4"/>
+      <c r="C363" s="10"/>
+      <c r="D363" s="5"/>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A364" s="4"/>
+      <c r="B364" s="4"/>
+      <c r="C364" s="10"/>
+      <c r="D364" s="5"/>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A365" s="4"/>
+      <c r="B365" s="4"/>
+      <c r="C365" s="10"/>
+      <c r="D365" s="5"/>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A366" s="4"/>
+      <c r="B366" s="4"/>
+      <c r="C366" s="10"/>
+      <c r="D366" s="5"/>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A367" s="4"/>
+      <c r="B367" s="4"/>
+      <c r="C367" s="10"/>
+      <c r="D367" s="5"/>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A368" s="4"/>
+      <c r="B368" s="4"/>
+      <c r="C368" s="10"/>
+      <c r="D368" s="5"/>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A369" s="4"/>
+      <c r="B369" s="4"/>
+      <c r="C369" s="10"/>
+      <c r="D369" s="5"/>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A370" s="4"/>
+      <c r="B370" s="4"/>
+      <c r="C370" s="10"/>
+      <c r="D370" s="5"/>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A371" s="4"/>
+      <c r="B371" s="4"/>
+      <c r="C371" s="10"/>
+      <c r="D371" s="5"/>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A372" s="4"/>
+      <c r="B372" s="4"/>
+      <c r="C372" s="10"/>
+      <c r="D372" s="5"/>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A373" s="4"/>
+      <c r="B373" s="4"/>
+      <c r="C373" s="10"/>
+      <c r="D373" s="5"/>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A374" s="4"/>
+      <c r="B374" s="4"/>
+      <c r="C374" s="10"/>
+      <c r="D374" s="5"/>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A375" s="4"/>
+      <c r="B375" s="4"/>
+      <c r="C375" s="10"/>
+      <c r="D375" s="5"/>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A376" s="4"/>
+      <c r="B376" s="4"/>
+      <c r="C376" s="10"/>
+      <c r="D376" s="5"/>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A377" s="4"/>
+      <c r="B377" s="4"/>
+      <c r="C377" s="9"/>
+      <c r="D377" s="5"/>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A378" s="4"/>
+      <c r="B378" s="4"/>
+      <c r="C378" s="9"/>
+      <c r="D378" s="5"/>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A379" s="4"/>
+      <c r="B379" s="4"/>
+      <c r="C379" s="9"/>
+      <c r="D379" s="5"/>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A380" s="4"/>
+      <c r="B380" s="4"/>
+      <c r="C380" s="9"/>
+      <c r="D380" s="5"/>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A381" s="4"/>
+      <c r="B381" s="4"/>
+      <c r="C381" s="9"/>
+      <c r="D381" s="5"/>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A382" s="4"/>
+      <c r="B382" s="7"/>
+      <c r="C382" s="9"/>
+      <c r="D382" s="5"/>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A383" s="4"/>
+      <c r="B383" s="4"/>
+      <c r="C383" s="9"/>
+      <c r="D383" s="5"/>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A384" s="4"/>
+      <c r="B384" s="4"/>
+      <c r="C384" s="9"/>
+      <c r="D384" s="5"/>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A385" s="4"/>
+      <c r="B385" s="4"/>
+      <c r="C385" s="7"/>
+      <c r="D385" s="5"/>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A386" s="4"/>
+      <c r="B386" s="4"/>
+      <c r="C386" s="7"/>
+      <c r="D386" s="5"/>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A387" s="4"/>
+      <c r="B387" s="4"/>
+      <c r="C387" s="7"/>
+      <c r="D387" s="5"/>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A388" s="4"/>
+      <c r="B388" s="4"/>
+      <c r="C388" s="7"/>
+      <c r="D388" s="5"/>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A389" s="4"/>
+      <c r="B389" s="4"/>
+      <c r="C389" s="4"/>
+      <c r="D389" s="5"/>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A390" s="4"/>
+      <c r="B390" s="4"/>
+      <c r="C390" s="4"/>
+      <c r="D390" s="5"/>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A391" s="4"/>
+      <c r="B391" s="4"/>
+      <c r="C391" s="4"/>
+      <c r="D391" s="5"/>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A392" s="4"/>
+      <c r="B392" s="4"/>
+      <c r="C392" s="4"/>
+      <c r="D392" s="5"/>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A393" s="4"/>
+      <c r="B393" s="4"/>
+      <c r="C393" s="4"/>
+      <c r="D393" s="5"/>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A394" s="4"/>
+      <c r="B394" s="4"/>
+      <c r="C394" s="4"/>
+      <c r="D394" s="5"/>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A395" s="4"/>
+      <c r="B395" s="4"/>
+      <c r="C395" s="4"/>
+      <c r="D395" s="5"/>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A396" s="4"/>
+      <c r="B396" s="4"/>
+      <c r="C396" s="4"/>
+      <c r="D396" s="5"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C8:C9" name="Tags_1_3_1"/>
-    <protectedRange sqref="C13" name="Tags_1_3_1_3"/>
+    <protectedRange sqref="C9:C10" name="Tags_1_3_1"/>
+    <protectedRange sqref="C14" name="Tags_1_3_1_3"/>
   </protectedRanges>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1652,11 +5708,11 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -1664,11 +5720,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -1676,11 +5732,11 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Michael\Desktop\Abnahmen_DGUV3_Lokal\10. Test\FlexPos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0052AF4-BDF7-43B2-A223-33231B1EBC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EFC793-4B2A-4A8D-B9E6-A3D2688C5D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="430">
   <si>
     <t>Oberordner</t>
   </si>
@@ -1293,6 +1293,24 @@
   </si>
   <si>
     <t>Netzwerkschrank 1</t>
+  </si>
+  <si>
+    <t>Allgemein / CCTV / Exit /Blitz</t>
+  </si>
+  <si>
+    <t>Allgemein / KV / Ports</t>
+  </si>
+  <si>
+    <t>Allgemein / Headset / Ports</t>
+  </si>
+  <si>
+    <t>NWS 1 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>NWS 2 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>NWS 3 Übersicht / Strom / PE / Codierung</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1399,9 +1417,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1730,7 +1745,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
@@ -1753,7 +1768,9 @@
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="8" t="s">
+        <v>424</v>
+      </c>
       <c r="C2" s="7" t="s">
         <v>76</v>
       </c>
@@ -2669,7 +2686,9 @@
       <c r="A89" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B89" s="4"/>
+      <c r="B89" s="4" t="s">
+        <v>425</v>
+      </c>
       <c r="C89" s="7" t="s">
         <v>114</v>
       </c>
@@ -2852,7 +2871,7 @@
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="7" t="s">
         <v>413</v>
       </c>
       <c r="D107" s="5">
@@ -2862,7 +2881,7 @@
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="7" t="s">
         <v>414</v>
       </c>
       <c r="D108" s="5">
@@ -4193,7 +4212,9 @@
       <c r="A237" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="B237" s="4"/>
+      <c r="B237" s="4" t="s">
+        <v>426</v>
+      </c>
       <c r="C237" s="7" t="s">
         <v>284</v>
       </c>
@@ -4540,7 +4561,7 @@
       <c r="B270" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="C270" s="11" t="s">
+      <c r="C270" s="7" t="s">
         <v>321</v>
       </c>
       <c r="D270" s="5">
@@ -4550,7 +4571,7 @@
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
-      <c r="C271" s="11" t="s">
+      <c r="C271" s="7" t="s">
         <v>322</v>
       </c>
       <c r="D271" s="5">
@@ -4562,7 +4583,7 @@
         <v>324</v>
       </c>
       <c r="B272" s="4"/>
-      <c r="C272" s="11" t="s">
+      <c r="C272" s="7" t="s">
         <v>325</v>
       </c>
       <c r="D272" s="5">
@@ -4572,7 +4593,7 @@
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="4"/>
-      <c r="C273" s="11" t="s">
+      <c r="C273" s="7" t="s">
         <v>326</v>
       </c>
       <c r="D273" s="5">
@@ -4582,7 +4603,7 @@
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
-      <c r="C274" s="12" t="s">
+      <c r="C274" s="9" t="s">
         <v>327</v>
       </c>
       <c r="D274" s="5">
@@ -4603,8 +4624,10 @@
       <c r="A276" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B276" s="4"/>
-      <c r="C276" s="11" t="s">
+      <c r="B276" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C276" s="7" t="s">
         <v>328</v>
       </c>
       <c r="D276" s="5">
@@ -4614,7 +4637,7 @@
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
-      <c r="C277" s="11" t="s">
+      <c r="C277" s="7" t="s">
         <v>329</v>
       </c>
       <c r="D277" s="5">
@@ -4624,7 +4647,7 @@
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
-      <c r="C278" s="11" t="s">
+      <c r="C278" s="7" t="s">
         <v>330</v>
       </c>
       <c r="D278" s="5">
@@ -4634,7 +4657,7 @@
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
-      <c r="C279" s="11" t="s">
+      <c r="C279" s="7" t="s">
         <v>331</v>
       </c>
       <c r="D279" s="5">
@@ -4644,7 +4667,7 @@
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
-      <c r="C280" s="11" t="s">
+      <c r="C280" s="7" t="s">
         <v>332</v>
       </c>
       <c r="D280" s="5">
@@ -4654,7 +4677,7 @@
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
-      <c r="C281" s="11" t="s">
+      <c r="C281" s="7" t="s">
         <v>333</v>
       </c>
       <c r="D281" s="5">
@@ -4664,7 +4687,7 @@
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
-      <c r="C282" s="11" t="s">
+      <c r="C282" s="7" t="s">
         <v>334</v>
       </c>
       <c r="D282" s="5">
@@ -4674,7 +4697,7 @@
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
-      <c r="C283" s="11" t="s">
+      <c r="C283" s="7" t="s">
         <v>335</v>
       </c>
       <c r="D283" s="5">
@@ -4684,7 +4707,7 @@
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
-      <c r="C284" s="11" t="s">
+      <c r="C284" s="7" t="s">
         <v>336</v>
       </c>
       <c r="D284" s="5">
@@ -4696,7 +4719,7 @@
       <c r="B285" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="C285" s="11" t="s">
+      <c r="C285" s="7" t="s">
         <v>337</v>
       </c>
       <c r="D285" s="5">
@@ -4706,7 +4729,7 @@
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
-      <c r="C286" s="11" t="s">
+      <c r="C286" s="7" t="s">
         <v>338</v>
       </c>
       <c r="D286" s="5">
@@ -4716,7 +4739,7 @@
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
-      <c r="C287" s="11" t="s">
+      <c r="C287" s="7" t="s">
         <v>339</v>
       </c>
       <c r="D287" s="5">
@@ -4726,7 +4749,7 @@
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
-      <c r="C288" s="11" t="s">
+      <c r="C288" s="7" t="s">
         <v>340</v>
       </c>
       <c r="D288" s="5">
@@ -4736,7 +4759,7 @@
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
-      <c r="C289" s="11" t="s">
+      <c r="C289" s="7" t="s">
         <v>341</v>
       </c>
       <c r="D289" s="5">
@@ -4746,7 +4769,7 @@
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
-      <c r="C290" s="11" t="s">
+      <c r="C290" s="7" t="s">
         <v>342</v>
       </c>
       <c r="D290" s="5">
@@ -4756,7 +4779,7 @@
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
-      <c r="C291" s="11" t="s">
+      <c r="C291" s="7" t="s">
         <v>343</v>
       </c>
       <c r="D291" s="5">
@@ -4766,7 +4789,7 @@
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
-      <c r="C292" s="11" t="s">
+      <c r="C292" s="7" t="s">
         <v>344</v>
       </c>
       <c r="D292" s="5">
@@ -4776,7 +4799,7 @@
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
-      <c r="C293" s="11" t="s">
+      <c r="C293" s="7" t="s">
         <v>345</v>
       </c>
       <c r="D293" s="5">
@@ -4786,7 +4809,7 @@
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
-      <c r="C294" s="11" t="s">
+      <c r="C294" s="7" t="s">
         <v>346</v>
       </c>
       <c r="D294" s="5">
@@ -4796,7 +4819,7 @@
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
-      <c r="C295" s="11" t="s">
+      <c r="C295" s="7" t="s">
         <v>347</v>
       </c>
       <c r="D295" s="5">
@@ -4806,7 +4829,7 @@
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
-      <c r="C296" s="11" t="s">
+      <c r="C296" s="7" t="s">
         <v>348</v>
       </c>
       <c r="D296" s="5">
@@ -4816,7 +4839,7 @@
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
-      <c r="C297" s="11" t="s">
+      <c r="C297" s="7" t="s">
         <v>349</v>
       </c>
       <c r="D297" s="5">
@@ -4826,7 +4849,7 @@
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
-      <c r="C298" s="11" t="s">
+      <c r="C298" s="7" t="s">
         <v>350</v>
       </c>
       <c r="D298" s="5">
@@ -4836,7 +4859,7 @@
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
-      <c r="C299" s="11" t="s">
+      <c r="C299" s="7" t="s">
         <v>351</v>
       </c>
       <c r="D299" s="5">
@@ -4846,7 +4869,7 @@
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
-      <c r="C300" s="11" t="s">
+      <c r="C300" s="7" t="s">
         <v>352</v>
       </c>
       <c r="D300" s="5">
@@ -4856,7 +4879,7 @@
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
-      <c r="C301" s="11" t="s">
+      <c r="C301" s="7" t="s">
         <v>353</v>
       </c>
       <c r="D301" s="5">
@@ -4866,7 +4889,7 @@
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
-      <c r="C302" s="11" t="s">
+      <c r="C302" s="7" t="s">
         <v>354</v>
       </c>
       <c r="D302" s="5">
@@ -4876,7 +4899,7 @@
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
-      <c r="C303" s="11" t="s">
+      <c r="C303" s="7" t="s">
         <v>355</v>
       </c>
       <c r="D303" s="5">
@@ -4886,7 +4909,7 @@
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
-      <c r="C304" s="11" t="s">
+      <c r="C304" s="7" t="s">
         <v>356</v>
       </c>
       <c r="D304" s="5">
@@ -4896,7 +4919,7 @@
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
-      <c r="C305" s="11" t="s">
+      <c r="C305" s="7" t="s">
         <v>357</v>
       </c>
       <c r="D305" s="5">
@@ -4906,7 +4929,7 @@
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
-      <c r="C306" s="11" t="s">
+      <c r="C306" s="7" t="s">
         <v>358</v>
       </c>
       <c r="D306" s="5">
@@ -4916,7 +4939,7 @@
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
-      <c r="C307" s="11" t="s">
+      <c r="C307" s="7" t="s">
         <v>373</v>
       </c>
       <c r="D307" s="5">
@@ -4926,7 +4949,7 @@
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
-      <c r="C308" s="11" t="s">
+      <c r="C308" s="7" t="s">
         <v>374</v>
       </c>
       <c r="D308" s="5">
@@ -4936,7 +4959,7 @@
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
-      <c r="C309" s="11" t="s">
+      <c r="C309" s="7" t="s">
         <v>375</v>
       </c>
       <c r="D309" s="5">
@@ -4946,7 +4969,7 @@
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
-      <c r="C310" s="11" t="s">
+      <c r="C310" s="7" t="s">
         <v>376</v>
       </c>
       <c r="D310" s="5">
@@ -4957,8 +4980,10 @@
       <c r="A311" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="B311" s="4"/>
-      <c r="C311" s="11" t="s">
+      <c r="B311" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C311" s="7" t="s">
         <v>361</v>
       </c>
       <c r="D311" s="5">
@@ -4968,7 +4993,7 @@
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
-      <c r="C312" s="11" t="s">
+      <c r="C312" s="7" t="s">
         <v>362</v>
       </c>
       <c r="D312" s="5">
@@ -4978,7 +5003,7 @@
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
-      <c r="C313" s="11" t="s">
+      <c r="C313" s="7" t="s">
         <v>363</v>
       </c>
       <c r="D313" s="5">
@@ -4988,7 +5013,7 @@
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
-      <c r="C314" s="11" t="s">
+      <c r="C314" s="7" t="s">
         <v>364</v>
       </c>
       <c r="D314" s="5">
@@ -4998,7 +5023,7 @@
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
-      <c r="C315" s="11" t="s">
+      <c r="C315" s="7" t="s">
         <v>365</v>
       </c>
       <c r="D315" s="5">
@@ -5008,7 +5033,7 @@
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
-      <c r="C316" s="11" t="s">
+      <c r="C316" s="7" t="s">
         <v>366</v>
       </c>
       <c r="D316" s="5">
@@ -5018,7 +5043,7 @@
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
-      <c r="C317" s="11" t="s">
+      <c r="C317" s="7" t="s">
         <v>367</v>
       </c>
       <c r="D317" s="5">
@@ -5028,7 +5053,7 @@
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
-      <c r="C318" s="11" t="s">
+      <c r="C318" s="7" t="s">
         <v>368</v>
       </c>
       <c r="D318" s="5">
@@ -5038,7 +5063,7 @@
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
-      <c r="C319" s="11" t="s">
+      <c r="C319" s="7" t="s">
         <v>369</v>
       </c>
       <c r="D319" s="5">
@@ -5048,7 +5073,7 @@
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
-      <c r="C320" s="11" t="s">
+      <c r="C320" s="7" t="s">
         <v>370</v>
       </c>
       <c r="D320" s="5">
@@ -5058,7 +5083,7 @@
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
-      <c r="C321" s="11" t="s">
+      <c r="C321" s="7" t="s">
         <v>371</v>
       </c>
       <c r="D321" s="5">
@@ -5068,7 +5093,7 @@
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
-      <c r="C322" s="11" t="s">
+      <c r="C322" s="7" t="s">
         <v>372</v>
       </c>
       <c r="D322" s="5">
@@ -5080,7 +5105,7 @@
       <c r="B323" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="C323" s="11" t="s">
+      <c r="C323" s="7" t="s">
         <v>379</v>
       </c>
       <c r="D323" s="5">
@@ -5090,7 +5115,7 @@
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
-      <c r="C324" s="11" t="s">
+      <c r="C324" s="7" t="s">
         <v>380</v>
       </c>
       <c r="D324" s="5">
@@ -5100,7 +5125,7 @@
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
-      <c r="C325" s="11" t="s">
+      <c r="C325" s="7" t="s">
         <v>381</v>
       </c>
       <c r="D325" s="5">
@@ -5110,7 +5135,7 @@
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
-      <c r="C326" s="11" t="s">
+      <c r="C326" s="7" t="s">
         <v>382</v>
       </c>
       <c r="D326" s="5">
@@ -5120,7 +5145,7 @@
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
-      <c r="C327" s="11" t="s">
+      <c r="C327" s="7" t="s">
         <v>383</v>
       </c>
       <c r="D327" s="5">
@@ -5130,7 +5155,7 @@
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
-      <c r="C328" s="11" t="s">
+      <c r="C328" s="7" t="s">
         <v>384</v>
       </c>
       <c r="D328" s="5">
@@ -5140,7 +5165,7 @@
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
-      <c r="C329" s="11" t="s">
+      <c r="C329" s="7" t="s">
         <v>385</v>
       </c>
       <c r="D329" s="5">
@@ -5150,7 +5175,7 @@
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
-      <c r="C330" s="11" t="s">
+      <c r="C330" s="7" t="s">
         <v>386</v>
       </c>
       <c r="D330" s="5">
@@ -5160,7 +5185,7 @@
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
-      <c r="C331" s="11" t="s">
+      <c r="C331" s="7" t="s">
         <v>387</v>
       </c>
       <c r="D331" s="5">
@@ -5170,7 +5195,7 @@
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
-      <c r="C332" s="11" t="s">
+      <c r="C332" s="7" t="s">
         <v>388</v>
       </c>
       <c r="D332" s="5">
@@ -5180,7 +5205,7 @@
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
-      <c r="C333" s="11" t="s">
+      <c r="C333" s="7" t="s">
         <v>389</v>
       </c>
       <c r="D333" s="5">
@@ -5190,7 +5215,7 @@
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
-      <c r="C334" s="11" t="s">
+      <c r="C334" s="7" t="s">
         <v>390</v>
       </c>
       <c r="D334" s="5">
@@ -5201,8 +5226,10 @@
       <c r="A335" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="B335" s="4"/>
-      <c r="C335" s="11" t="s">
+      <c r="B335" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C335" s="7" t="s">
         <v>392</v>
       </c>
       <c r="D335" s="5">
@@ -5212,7 +5239,7 @@
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
-      <c r="C336" s="11" t="s">
+      <c r="C336" s="7" t="s">
         <v>393</v>
       </c>
       <c r="D336" s="5">
@@ -5222,7 +5249,7 @@
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
-      <c r="C337" s="11" t="s">
+      <c r="C337" s="7" t="s">
         <v>394</v>
       </c>
       <c r="D337" s="5">
@@ -5232,7 +5259,7 @@
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
-      <c r="C338" s="11" t="s">
+      <c r="C338" s="7" t="s">
         <v>395</v>
       </c>
       <c r="D338" s="5">
@@ -5242,7 +5269,7 @@
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
-      <c r="C339" s="11" t="s">
+      <c r="C339" s="7" t="s">
         <v>396</v>
       </c>
       <c r="D339" s="5">
@@ -5252,7 +5279,7 @@
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
-      <c r="C340" s="11" t="s">
+      <c r="C340" s="7" t="s">
         <v>397</v>
       </c>
       <c r="D340" s="5">
@@ -5262,7 +5289,7 @@
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
-      <c r="C341" s="11" t="s">
+      <c r="C341" s="7" t="s">
         <v>398</v>
       </c>
       <c r="D341" s="5">
@@ -5272,7 +5299,7 @@
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
-      <c r="C342" s="11" t="s">
+      <c r="C342" s="7" t="s">
         <v>399</v>
       </c>
       <c r="D342" s="5">
@@ -5284,7 +5311,7 @@
       <c r="B343" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="C343" s="11" t="s">
+      <c r="C343" s="7" t="s">
         <v>401</v>
       </c>
       <c r="D343" s="5">
@@ -5294,7 +5321,7 @@
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
-      <c r="C344" s="11" t="s">
+      <c r="C344" s="7" t="s">
         <v>402</v>
       </c>
       <c r="D344" s="5">
@@ -5304,7 +5331,7 @@
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
-      <c r="C345" s="11" t="s">
+      <c r="C345" s="7" t="s">
         <v>403</v>
       </c>
       <c r="D345" s="5">
@@ -5314,7 +5341,7 @@
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
-      <c r="C346" s="11" t="s">
+      <c r="C346" s="7" t="s">
         <v>404</v>
       </c>
       <c r="D346" s="5">
@@ -5324,7 +5351,7 @@
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
-      <c r="C347" s="11" t="s">
+      <c r="C347" s="7" t="s">
         <v>375</v>
       </c>
       <c r="D347" s="5">
@@ -5334,7 +5361,7 @@
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
-      <c r="C348" s="11" t="s">
+      <c r="C348" s="7" t="s">
         <v>376</v>
       </c>
       <c r="D348" s="5">
@@ -5346,7 +5373,7 @@
         <v>405</v>
       </c>
       <c r="B349" s="4"/>
-      <c r="C349" s="11" t="s">
+      <c r="C349" s="7" t="s">
         <v>406</v>
       </c>
       <c r="D349" s="5">
@@ -5356,7 +5383,7 @@
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
-      <c r="C350" s="11" t="s">
+      <c r="C350" s="7" t="s">
         <v>407</v>
       </c>
       <c r="D350" s="5">
@@ -5366,7 +5393,7 @@
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
-      <c r="C351" s="11" t="s">
+      <c r="C351" s="7" t="s">
         <v>408</v>
       </c>
       <c r="D351" s="5">
@@ -5376,7 +5403,7 @@
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
-      <c r="C352" s="11" t="s">
+      <c r="C352" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D352" s="5">
@@ -5386,7 +5413,7 @@
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
-      <c r="C353" s="11" t="s">
+      <c r="C353" s="7" t="s">
         <v>410</v>
       </c>
       <c r="D353" s="5">
@@ -5396,7 +5423,7 @@
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
-      <c r="C354" s="11" t="s">
+      <c r="C354" s="7" t="s">
         <v>411</v>
       </c>
       <c r="D354" s="5">
@@ -5448,109 +5475,109 @@
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
-      <c r="C359" s="10"/>
+      <c r="C359" s="9"/>
       <c r="D359" s="5"/>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
-      <c r="C360" s="10"/>
+      <c r="C360" s="9"/>
       <c r="D360" s="5"/>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
-      <c r="C361" s="10"/>
+      <c r="C361" s="9"/>
       <c r="D361" s="5"/>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
-      <c r="C362" s="10"/>
+      <c r="C362" s="9"/>
       <c r="D362" s="5"/>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
-      <c r="C363" s="10"/>
+      <c r="C363" s="9"/>
       <c r="D363" s="5"/>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
-      <c r="C364" s="10"/>
+      <c r="C364" s="9"/>
       <c r="D364" s="5"/>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
-      <c r="C365" s="10"/>
+      <c r="C365" s="9"/>
       <c r="D365" s="5"/>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
-      <c r="C366" s="10"/>
+      <c r="C366" s="9"/>
       <c r="D366" s="5"/>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
-      <c r="C367" s="10"/>
+      <c r="C367" s="9"/>
       <c r="D367" s="5"/>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
-      <c r="C368" s="10"/>
+      <c r="C368" s="9"/>
       <c r="D368" s="5"/>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
-      <c r="C369" s="10"/>
+      <c r="C369" s="9"/>
       <c r="D369" s="5"/>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
-      <c r="C370" s="10"/>
+      <c r="C370" s="9"/>
       <c r="D370" s="5"/>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
-      <c r="C371" s="10"/>
+      <c r="C371" s="9"/>
       <c r="D371" s="5"/>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
-      <c r="C372" s="10"/>
+      <c r="C372" s="9"/>
       <c r="D372" s="5"/>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
-      <c r="C373" s="10"/>
+      <c r="C373" s="9"/>
       <c r="D373" s="5"/>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" s="4"/>
       <c r="B374" s="4"/>
-      <c r="C374" s="10"/>
+      <c r="C374" s="9"/>
       <c r="D374" s="5"/>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
-      <c r="C375" s="10"/>
+      <c r="C375" s="9"/>
       <c r="D375" s="5"/>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
-      <c r="C376" s="10"/>
+      <c r="C376" s="9"/>
       <c r="D376" s="5"/>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\_deploy\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EFC793-4B2A-4A8D-B9E6-A3D2688C5D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155A9F04-7A87-4030-A659-55A19D18B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="457">
   <si>
     <t>Oberordner</t>
   </si>
@@ -347,12 +347,6 @@
     <t>BA 05 + 06 Totale</t>
   </si>
   <si>
-    <t>BA 07 + 08 Dose</t>
-  </si>
-  <si>
-    <t>BA 07 + 08 Totale</t>
-  </si>
-  <si>
     <t>BA Totale</t>
   </si>
   <si>
@@ -890,12 +884,6 @@
     <t>PZE gesamt</t>
   </si>
   <si>
-    <t>Perso 1 + Perso 2 Dose</t>
-  </si>
-  <si>
-    <t>Perso 1 + Perso 2Totale</t>
-  </si>
-  <si>
     <t>Headset Strom</t>
   </si>
   <si>
@@ -914,15 +902,6 @@
     <t>SN Headsets</t>
   </si>
   <si>
-    <t>LIN Headset 2</t>
-  </si>
-  <si>
-    <t>LIN Headset 3</t>
-  </si>
-  <si>
-    <t>LIN Headset 4</t>
-  </si>
-  <si>
     <t>09_Vocovo</t>
   </si>
   <si>
@@ -1094,12 +1073,6 @@
     <t>LIN Server</t>
   </si>
   <si>
-    <t>LIN HGA-Kasse 1</t>
-  </si>
-  <si>
-    <t>SN HGA-Kasse 1</t>
-  </si>
-  <si>
     <t>SN PZE</t>
   </si>
   <si>
@@ -1226,12 +1199,6 @@
     <t>NWS 3 - Beschriftung / SN / LIN</t>
   </si>
   <si>
-    <t>SN AcessA</t>
-  </si>
-  <si>
-    <t>SN AcessB</t>
-  </si>
-  <si>
     <t>SN LTE-Router Access A</t>
   </si>
   <si>
@@ -1262,12 +1229,6 @@
     <t>Digitales Backschema</t>
   </si>
   <si>
-    <t>SN_KVM Switch</t>
-  </si>
-  <si>
-    <t>LIN_KVM Switch</t>
-  </si>
-  <si>
     <t>Plantasche NWS</t>
   </si>
   <si>
@@ -1311,6 +1272,126 @@
   </si>
   <si>
     <t>NWS 3 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>Lautsprecher Monitor</t>
+  </si>
+  <si>
+    <t>SN Main Unit 1</t>
+  </si>
+  <si>
+    <t>SN Main Unit 2</t>
+  </si>
+  <si>
+    <t>SN Bosch Verstärker</t>
+  </si>
+  <si>
+    <t>SN SMC</t>
+  </si>
+  <si>
+    <t>SN Kundenterminal</t>
+  </si>
+  <si>
+    <t>HGA Dose Detail</t>
+  </si>
+  <si>
+    <t>HGA Dose Totale</t>
+  </si>
+  <si>
+    <t>SCO 89 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 89 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 1</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 2</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 3</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 4</t>
+  </si>
+  <si>
+    <t>SN Vocovo Repeater 5</t>
+  </si>
+  <si>
+    <t>SN Digitales Backschema</t>
+  </si>
+  <si>
+    <t>SN KVM Switch</t>
+  </si>
+  <si>
+    <t>LIN KVM Switch</t>
+  </si>
+  <si>
+    <t>SN Telefon 1</t>
+  </si>
+  <si>
+    <t>SN Telefon 2</t>
+  </si>
+  <si>
+    <t>SN MDE</t>
+  </si>
+  <si>
+    <t>SN Ladeschalen MDE</t>
+  </si>
+  <si>
+    <t>SN MRED</t>
+  </si>
+  <si>
+    <t>SN Ladeschalen MRED</t>
+  </si>
+  <si>
+    <t>SN Front Reader</t>
+  </si>
+  <si>
+    <t>SN Thin Client</t>
+  </si>
+  <si>
+    <t>LIN Thin Client</t>
+  </si>
+  <si>
+    <t>SN Lautsprecherleiste</t>
+  </si>
+  <si>
+    <t>SN Registrierungsmodul</t>
+  </si>
+  <si>
+    <t>SN Festplatte 2</t>
+  </si>
+  <si>
+    <t>SN Festplatte 3</t>
+  </si>
+  <si>
+    <t>SN Safebag Festplatten</t>
+  </si>
+  <si>
+    <t>SN AccessA</t>
+  </si>
+  <si>
+    <t>SN AccessB</t>
+  </si>
+  <si>
+    <t>SDP Lieferung + Lieferscheine</t>
+  </si>
+  <si>
+    <t>Besprechung Dose Detail</t>
+  </si>
+  <si>
+    <t>Besprechung Dose Totale</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2 Totale</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2 Detail</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D396"/>
+  <dimension ref="A1:D421"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1769,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>76</v>
@@ -1835,36 +1916,36 @@
         <v>418</v>
       </c>
       <c r="D8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D10" s="8">
         <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="C11" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -1872,11 +1953,9 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
+      <c r="B12" s="4"/>
       <c r="C12" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -1886,7 +1965,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -1894,9 +1973,11 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
+      <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="C14" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -1904,11 +1985,9 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="B15" s="4"/>
       <c r="C15" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -1918,7 +1997,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -1926,9 +2005,11 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="C17" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1936,11 +2017,9 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="B18" s="4"/>
       <c r="C18" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -1950,7 +2029,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -1958,9 +2037,11 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="C20" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -1968,11 +2049,9 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
-        <v>41</v>
-      </c>
+      <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -1982,7 +2061,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -1990,9 +2069,11 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="C23" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -2000,11 +2081,9 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -2014,7 +2093,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -2022,9 +2101,11 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="C26" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D26" s="5">
         <v>1</v>
@@ -2032,11 +2113,9 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="B27" s="4"/>
       <c r="C27" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -2046,7 +2125,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -2054,9 +2133,11 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="C29" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -2064,11 +2145,9 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
-      <c r="B30" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="B30" s="4"/>
       <c r="C30" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D30" s="5">
         <v>1</v>
@@ -2078,7 +2157,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
@@ -2086,9 +2165,11 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="C32" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D32" s="5">
         <v>1</v>
@@ -2096,11 +2177,9 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
-        <v>45</v>
-      </c>
+      <c r="B33" s="4"/>
       <c r="C33" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -2110,7 +2189,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -2118,9 +2197,11 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="C35" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
@@ -2128,11 +2209,9 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B36" s="4"/>
       <c r="C36" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
@@ -2142,7 +2221,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -2151,10 +2230,10 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
@@ -2164,7 +2243,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
@@ -2173,10 +2252,10 @@
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
@@ -2186,7 +2265,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -2195,10 +2274,10 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
@@ -2208,7 +2287,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
@@ -2217,10 +2296,10 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -2230,7 +2309,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
@@ -2239,10 +2318,10 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D46" s="5">
         <v>1</v>
@@ -2252,7 +2331,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D47" s="5">
         <v>1</v>
@@ -2261,10 +2340,10 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -2274,7 +2353,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D49" s="5">
         <v>1</v>
@@ -2283,10 +2362,10 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D50" s="5">
         <v>1</v>
@@ -2296,7 +2375,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -2305,7 +2384,7 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>61</v>
@@ -2327,10 +2406,10 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>72</v>
+        <v>425</v>
       </c>
       <c r="D54" s="5">
         <v>1</v>
@@ -2340,7 +2419,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7" t="s">
-        <v>73</v>
+        <v>426</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -2348,9 +2427,11 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
+      <c r="B56" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="C56" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
@@ -2360,7 +2441,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D57" s="5">
         <v>1</v>
@@ -2368,11 +2449,9 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4"/>
-      <c r="B58" s="4" t="s">
-        <v>92</v>
-      </c>
+      <c r="B58" s="4"/>
       <c r="C58" s="7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -2382,7 +2461,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D59" s="5">
         <v>1</v>
@@ -2390,9 +2469,11 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
+      <c r="B60" s="4" t="s">
+        <v>92</v>
+      </c>
       <c r="C60" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
@@ -2402,7 +2483,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
@@ -2412,7 +2493,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>
@@ -2422,7 +2503,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D63" s="5">
         <v>1</v>
@@ -2432,7 +2513,7 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
@@ -2442,7 +2523,7 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D65" s="5">
         <v>1</v>
@@ -2452,7 +2533,7 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
@@ -2462,19 +2543,17 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>93</v>
-      </c>
+      <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
@@ -2484,17 +2563,19 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4"/>
+      <c r="A70" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="B70" s="4"/>
       <c r="C70" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
@@ -2504,7 +2585,7 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D71" s="5">
         <v>1</v>
@@ -2514,7 +2595,7 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D72" s="5">
         <v>1</v>
@@ -2524,7 +2605,7 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D73" s="5">
         <v>1</v>
@@ -2534,7 +2615,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D74" s="5">
         <v>1</v>
@@ -2544,19 +2625,17 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="7" t="s">
-        <v>416</v>
+        <v>99</v>
       </c>
       <c r="D75" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
@@ -2566,7 +2645,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="7" t="s">
-        <v>103</v>
+        <v>423</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
@@ -2576,7 +2655,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="7" t="s">
-        <v>104</v>
+        <v>424</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -2586,17 +2665,19 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="7" t="s">
-        <v>105</v>
+        <v>403</v>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4"/>
+      <c r="A80" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="B80" s="4"/>
       <c r="C80" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D80" s="5">
         <v>1</v>
@@ -2606,7 +2687,7 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
@@ -2616,7 +2697,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -2626,7 +2707,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="7" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D83" s="5">
         <v>1</v>
@@ -2636,7 +2717,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D84" s="5">
         <v>1</v>
@@ -2646,7 +2727,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
@@ -2656,7 +2737,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D86" s="5">
         <v>1</v>
@@ -2666,31 +2747,27 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="7" t="s">
-        <v>412</v>
+        <v>109</v>
       </c>
       <c r="D87" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="7" t="s">
-        <v>417</v>
+        <v>110</v>
       </c>
       <c r="D88" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>425</v>
-      </c>
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
       <c r="C89" s="7" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D89" s="5">
         <v>1</v>
@@ -2700,7 +2777,7 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="7" t="s">
-        <v>115</v>
+        <v>433</v>
       </c>
       <c r="D90" s="5">
         <v>1</v>
@@ -2710,7 +2787,7 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="7" t="s">
-        <v>116</v>
+        <v>422</v>
       </c>
       <c r="D91" s="5">
         <v>1</v>
@@ -2720,17 +2797,21 @@
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="7" t="s">
-        <v>117</v>
+        <v>404</v>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
+      <c r="A93" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>412</v>
+      </c>
       <c r="C93" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D93" s="5">
         <v>1</v>
@@ -2740,7 +2821,7 @@
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
@@ -2750,7 +2831,7 @@
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
@@ -2760,7 +2841,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D96" s="5">
         <v>1</v>
@@ -2770,7 +2851,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="7" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D97" s="5">
         <v>1</v>
@@ -2780,7 +2861,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="7" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2790,7 +2871,7 @@
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
@@ -2800,7 +2881,7 @@
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
@@ -2810,19 +2891,17 @@
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="7" t="s">
-        <v>419</v>
+        <v>120</v>
       </c>
       <c r="D101" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="4"/>
-      <c r="B102" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="B102" s="4"/>
       <c r="C102" s="7" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
@@ -2832,7 +2911,7 @@
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D103" s="5">
         <v>1</v>
@@ -2842,7 +2921,7 @@
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D104" s="5">
         <v>1</v>
@@ -2852,7 +2931,7 @@
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="7" t="s">
-        <v>130</v>
+        <v>417</v>
       </c>
       <c r="D105" s="5">
         <v>1</v>
@@ -2862,17 +2941,19 @@
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="7" t="s">
-        <v>131</v>
+        <v>406</v>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
+      <c r="B107" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="C107" s="7" t="s">
-        <v>413</v>
+        <v>125</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
@@ -2882,7 +2963,7 @@
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="7" t="s">
-        <v>414</v>
+        <v>126</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
@@ -2890,11 +2971,9 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="4"/>
-      <c r="B109" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="B109" s="4"/>
       <c r="C109" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
@@ -2904,7 +2983,7 @@
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
@@ -2914,7 +2993,7 @@
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
@@ -2924,19 +3003,17 @@
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="7" t="s">
-        <v>136</v>
+        <v>434</v>
       </c>
       <c r="D112" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>142</v>
-      </c>
+      <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="7" t="s">
-        <v>143</v>
+        <v>435</v>
       </c>
       <c r="D113" s="5">
         <v>1</v>
@@ -2946,7 +3023,7 @@
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="7" t="s">
-        <v>144</v>
+        <v>436</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
@@ -2956,7 +3033,7 @@
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="7" t="s">
-        <v>145</v>
+        <v>437</v>
       </c>
       <c r="D115" s="5">
         <v>1</v>
@@ -2966,7 +3043,7 @@
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="7" t="s">
-        <v>146</v>
+        <v>438</v>
       </c>
       <c r="D116" s="5">
         <v>1</v>
@@ -2976,7 +3053,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
-        <v>147</v>
+        <v>439</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
@@ -2986,7 +3063,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>148</v>
+        <v>440</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
@@ -2996,19 +3073,17 @@
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="7" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D119" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>149</v>
-      </c>
+      <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="7" t="s">
-        <v>150</v>
+        <v>442</v>
       </c>
       <c r="D120" s="5">
         <v>1</v>
@@ -3018,7 +3093,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="7" t="s">
-        <v>151</v>
+        <v>443</v>
       </c>
       <c r="D121" s="5">
         <v>1</v>
@@ -3028,7 +3103,7 @@
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="7" t="s">
-        <v>152</v>
+        <v>444</v>
       </c>
       <c r="D122" s="5">
         <v>1</v>
@@ -3038,7 +3113,7 @@
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="7" t="s">
-        <v>153</v>
+        <v>445</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
@@ -3046,23 +3121,21 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
+      <c r="B124" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="C124" s="7" t="s">
-        <v>421</v>
+        <v>131</v>
       </c>
       <c r="D124" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B125" s="4" t="s">
-        <v>203</v>
-      </c>
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
       <c r="C125" s="7" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D125" s="5">
         <v>1</v>
@@ -3072,7 +3145,7 @@
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="7" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="D126" s="5">
         <v>1</v>
@@ -3082,7 +3155,7 @@
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="7" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="D127" s="5">
         <v>1</v>
@@ -3092,17 +3165,19 @@
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="7" t="s">
-        <v>219</v>
+        <v>452</v>
       </c>
       <c r="D128" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="4"/>
+      <c r="A129" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="B129" s="4"/>
       <c r="C129" s="7" t="s">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="D129" s="5">
         <v>1</v>
@@ -3112,7 +3187,7 @@
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="7" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="D130" s="5">
         <v>1</v>
@@ -3122,7 +3197,7 @@
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="7" t="s">
-        <v>222</v>
+        <v>143</v>
       </c>
       <c r="D131" s="5">
         <v>1</v>
@@ -3130,11 +3205,9 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="4"/>
-      <c r="B132" s="4" t="s">
-        <v>204</v>
-      </c>
+      <c r="B132" s="4"/>
       <c r="C132" s="7" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
@@ -3144,7 +3217,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="7" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
@@ -3154,7 +3227,7 @@
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="7" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
@@ -3164,17 +3237,19 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="7" t="s">
-        <v>223</v>
+        <v>407</v>
       </c>
       <c r="D135" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="4"/>
+      <c r="A136" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="B136" s="4"/>
       <c r="C136" s="7" t="s">
-        <v>224</v>
+        <v>148</v>
       </c>
       <c r="D136" s="5">
         <v>1</v>
@@ -3184,7 +3259,7 @@
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="7" t="s">
-        <v>225</v>
+        <v>149</v>
       </c>
       <c r="D137" s="5">
         <v>1</v>
@@ -3194,7 +3269,7 @@
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="7" t="s">
-        <v>226</v>
+        <v>150</v>
       </c>
       <c r="D138" s="5">
         <v>1</v>
@@ -3202,11 +3277,9 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="4"/>
-      <c r="B139" s="4" t="s">
-        <v>205</v>
-      </c>
+      <c r="B139" s="4"/>
       <c r="C139" s="7" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D139" s="5">
         <v>1</v>
@@ -3216,17 +3289,21 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="7" t="s">
-        <v>161</v>
+        <v>408</v>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
+      <c r="A141" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="C141" s="7" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D141" s="5">
         <v>1</v>
@@ -3236,7 +3313,7 @@
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="7" t="s">
-        <v>227</v>
+        <v>153</v>
       </c>
       <c r="D142" s="5">
         <v>1</v>
@@ -3246,7 +3323,7 @@
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="7" t="s">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="D143" s="5">
         <v>1</v>
@@ -3256,7 +3333,7 @@
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="7" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="D144" s="5">
         <v>1</v>
@@ -3266,7 +3343,7 @@
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D145" s="5">
         <v>1</v>
@@ -3274,11 +3351,9 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="4"/>
-      <c r="B146" s="4" t="s">
-        <v>206</v>
-      </c>
+      <c r="B146" s="4"/>
       <c r="C146" s="7" t="s">
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="D146" s="5">
         <v>1</v>
@@ -3288,7 +3363,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="7" t="s">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="D147" s="5">
         <v>1</v>
@@ -3296,9 +3371,11 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
+      <c r="B148" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="C148" s="7" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D148" s="5">
         <v>1</v>
@@ -3308,7 +3385,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="7" t="s">
-        <v>231</v>
+        <v>156</v>
       </c>
       <c r="D149" s="5">
         <v>1</v>
@@ -3318,7 +3395,7 @@
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="7" t="s">
-        <v>232</v>
+        <v>157</v>
       </c>
       <c r="D150" s="5">
         <v>1</v>
@@ -3328,7 +3405,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="7" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D151" s="5">
         <v>1</v>
@@ -3338,7 +3415,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="7" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D152" s="5">
         <v>1</v>
@@ -3346,11 +3423,9 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="4"/>
-      <c r="B153" s="4" t="s">
-        <v>207</v>
-      </c>
+      <c r="B153" s="4"/>
       <c r="C153" s="7" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="D153" s="5">
         <v>1</v>
@@ -3360,7 +3435,7 @@
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="7" t="s">
-        <v>167</v>
+        <v>224</v>
       </c>
       <c r="D154" s="5">
         <v>1</v>
@@ -3368,9 +3443,11 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
+      <c r="B155" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="C155" s="7" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D155" s="5">
         <v>1</v>
@@ -3380,7 +3457,7 @@
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="7" t="s">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="D156" s="5">
         <v>1</v>
@@ -3390,7 +3467,7 @@
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="7" t="s">
-        <v>236</v>
+        <v>160</v>
       </c>
       <c r="D157" s="5">
         <v>1</v>
@@ -3400,7 +3477,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="7" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D158" s="5">
         <v>1</v>
@@ -3410,7 +3487,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="7" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D159" s="5">
         <v>1</v>
@@ -3418,11 +3495,9 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="4"/>
-      <c r="B160" s="4" t="s">
-        <v>208</v>
-      </c>
+      <c r="B160" s="4"/>
       <c r="C160" s="7" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="D160" s="5">
         <v>1</v>
@@ -3432,7 +3507,7 @@
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="7" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="D161" s="5">
         <v>1</v>
@@ -3440,9 +3515,11 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
+      <c r="B162" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="C162" s="7" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D162" s="5">
         <v>1</v>
@@ -3452,7 +3529,7 @@
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="7" t="s">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c r="D163" s="5">
         <v>1</v>
@@ -3462,7 +3539,7 @@
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="7" t="s">
-        <v>240</v>
+        <v>163</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
@@ -3472,7 +3549,7 @@
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="7" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D165" s="5">
         <v>1</v>
@@ -3482,7 +3559,7 @@
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="7" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D166" s="5">
         <v>1</v>
@@ -3490,11 +3567,9 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
-      <c r="B167" s="4" t="s">
-        <v>209</v>
-      </c>
+      <c r="B167" s="4"/>
       <c r="C167" s="7" t="s">
-        <v>172</v>
+        <v>231</v>
       </c>
       <c r="D167" s="5">
         <v>1</v>
@@ -3504,7 +3579,7 @@
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="7" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
       <c r="D168" s="5">
         <v>1</v>
@@ -3512,9 +3587,11 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
-      <c r="B169" s="4"/>
+      <c r="B169" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="C169" s="7" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="D169" s="5">
         <v>1</v>
@@ -3524,7 +3601,7 @@
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="7" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
       <c r="D170" s="5">
         <v>1</v>
@@ -3534,7 +3611,7 @@
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="7" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="D171" s="5">
         <v>1</v>
@@ -3544,7 +3621,7 @@
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="7" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D172" s="5">
         <v>1</v>
@@ -3554,7 +3631,7 @@
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="7" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D173" s="5">
         <v>1</v>
@@ -3562,11 +3639,9 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="4"/>
-      <c r="B174" s="4" t="s">
-        <v>210</v>
-      </c>
+      <c r="B174" s="4"/>
       <c r="C174" s="7" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="D174" s="5">
         <v>1</v>
@@ -3576,7 +3651,7 @@
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="7" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D175" s="5">
         <v>1</v>
@@ -3584,9 +3659,11 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
+      <c r="B176" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="C176" s="7" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D176" s="5">
         <v>1</v>
@@ -3596,7 +3673,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="7" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="D177" s="5">
         <v>1</v>
@@ -3606,7 +3683,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="7" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="D178" s="5">
         <v>1</v>
@@ -3616,7 +3693,7 @@
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="7" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D179" s="5">
         <v>1</v>
@@ -3626,7 +3703,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="7" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D180" s="5">
         <v>1</v>
@@ -3634,11 +3711,9 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="4"/>
-      <c r="B181" s="4" t="s">
-        <v>211</v>
-      </c>
+      <c r="B181" s="4"/>
       <c r="C181" s="7" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="D181" s="5">
         <v>1</v>
@@ -3648,7 +3723,7 @@
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="7" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="D182" s="5">
         <v>1</v>
@@ -3656,9 +3731,11 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
+      <c r="B183" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="C183" s="7" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D183" s="5">
         <v>1</v>
@@ -3668,7 +3745,7 @@
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="7" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
@@ -3678,7 +3755,7 @@
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="7" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="D185" s="5">
         <v>1</v>
@@ -3688,7 +3765,7 @@
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="7" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D186" s="5">
         <v>1</v>
@@ -3698,7 +3775,7 @@
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D187" s="5">
         <v>1</v>
@@ -3706,11 +3783,9 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="4"/>
-      <c r="B188" s="4" t="s">
-        <v>212</v>
-      </c>
+      <c r="B188" s="4"/>
       <c r="C188" s="7" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="D188" s="5">
         <v>1</v>
@@ -3720,7 +3795,7 @@
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="7" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="D189" s="5">
         <v>1</v>
@@ -3728,9 +3803,11 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
-      <c r="B190" s="4"/>
+      <c r="B190" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="C190" s="7" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D190" s="5">
         <v>1</v>
@@ -3740,7 +3817,7 @@
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="7" t="s">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="D191" s="5">
         <v>1</v>
@@ -3750,7 +3827,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="7" t="s">
-        <v>256</v>
+        <v>175</v>
       </c>
       <c r="D192" s="5">
         <v>1</v>
@@ -3760,7 +3837,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="7" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D193" s="5">
         <v>1</v>
@@ -3770,7 +3847,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="7" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D194" s="5">
         <v>1</v>
@@ -3778,11 +3855,9 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="4"/>
-      <c r="B195" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="B195" s="4"/>
       <c r="C195" s="7" t="s">
-        <v>184</v>
+        <v>247</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -3792,7 +3867,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="7" t="s">
-        <v>185</v>
+        <v>248</v>
       </c>
       <c r="D196" s="5">
         <v>1</v>
@@ -3800,9 +3875,11 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
-      <c r="B197" s="4"/>
+      <c r="B197" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="C197" s="7" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D197" s="5">
         <v>1</v>
@@ -3812,7 +3889,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="7" t="s">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="D198" s="5">
         <v>1</v>
@@ -3822,7 +3899,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="7" t="s">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="D199" s="5">
         <v>1</v>
@@ -3832,7 +3909,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="7" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D200" s="5">
         <v>1</v>
@@ -3842,7 +3919,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="7" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D201" s="5">
         <v>1</v>
@@ -3850,11 +3927,9 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="4"/>
-      <c r="B202" s="4" t="s">
-        <v>214</v>
-      </c>
+      <c r="B202" s="4"/>
       <c r="C202" s="7" t="s">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="D202" s="5">
         <v>1</v>
@@ -3864,7 +3939,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="7" t="s">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="D203" s="5">
         <v>1</v>
@@ -3872,9 +3947,11 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="4"/>
+      <c r="B204" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="C204" s="7" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D204" s="5">
         <v>1</v>
@@ -3884,7 +3961,7 @@
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="7" t="s">
-        <v>263</v>
+        <v>180</v>
       </c>
       <c r="D205" s="5">
         <v>1</v>
@@ -3894,7 +3971,7 @@
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="7" t="s">
-        <v>264</v>
+        <v>181</v>
       </c>
       <c r="D206" s="5">
         <v>1</v>
@@ -3904,7 +3981,7 @@
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="7" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D207" s="5">
         <v>1</v>
@@ -3914,7 +3991,7 @@
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="7" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D208" s="5">
         <v>1</v>
@@ -3922,11 +3999,9 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" s="4"/>
-      <c r="B209" s="4" t="s">
-        <v>215</v>
-      </c>
+      <c r="B209" s="4"/>
       <c r="C209" s="7" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="D209" s="5">
         <v>1</v>
@@ -3936,7 +4011,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="7" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="D210" s="5">
         <v>1</v>
@@ -3944,9 +4019,11 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="4"/>
-      <c r="B211" s="4"/>
+      <c r="B211" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="C211" s="7" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D211" s="5">
         <v>1</v>
@@ -3956,7 +4033,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>267</v>
+        <v>183</v>
       </c>
       <c r="D212" s="5">
         <v>1</v>
@@ -3966,7 +4043,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="7" t="s">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="D213" s="5">
         <v>1</v>
@@ -3976,7 +4053,7 @@
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="7" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D214" s="5">
         <v>1</v>
@@ -3986,7 +4063,7 @@
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="7" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D215" s="5">
         <v>1</v>
@@ -3994,11 +4071,9 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" s="4"/>
-      <c r="B216" s="4" t="s">
-        <v>216</v>
-      </c>
+      <c r="B216" s="4"/>
       <c r="C216" s="7" t="s">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="D216" s="5">
         <v>1</v>
@@ -4008,7 +4083,7 @@
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="D217" s="5">
         <v>1</v>
@@ -4016,9 +4091,11 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
+      <c r="B218" s="4" t="s">
+        <v>212</v>
+      </c>
       <c r="C218" s="7" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D218" s="5">
         <v>1</v>
@@ -4028,7 +4105,7 @@
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="7" t="s">
-        <v>271</v>
+        <v>186</v>
       </c>
       <c r="D219" s="5">
         <v>1</v>
@@ -4038,7 +4115,7 @@
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
-        <v>272</v>
+        <v>187</v>
       </c>
       <c r="D220" s="5">
         <v>1</v>
@@ -4048,7 +4125,7 @@
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="7" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D221" s="5">
         <v>1</v>
@@ -4058,7 +4135,7 @@
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
       <c r="C222" s="7" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D222" s="5">
         <v>1</v>
@@ -4066,11 +4143,9 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" s="4"/>
-      <c r="B223" s="4" t="s">
-        <v>217</v>
-      </c>
+      <c r="B223" s="4"/>
       <c r="C223" s="7" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="D223" s="5">
         <v>1</v>
@@ -4080,7 +4155,7 @@
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="7" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="D224" s="5">
         <v>1</v>
@@ -4088,9 +4163,11 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="4"/>
-      <c r="B225" s="4"/>
+      <c r="B225" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="C225" s="7" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D225" s="5">
         <v>1</v>
@@ -4100,7 +4177,7 @@
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="7" t="s">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="D226" s="5">
         <v>1</v>
@@ -4110,7 +4187,7 @@
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="7" t="s">
-        <v>276</v>
+        <v>190</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -4120,7 +4197,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="7" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D228" s="5">
         <v>1</v>
@@ -4130,7 +4207,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="7" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D229" s="5">
         <v>1</v>
@@ -4138,11 +4215,9 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" s="4"/>
-      <c r="B230" s="4" t="s">
-        <v>218</v>
-      </c>
+      <c r="B230" s="4"/>
       <c r="C230" s="7" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="D230" s="5">
         <v>1</v>
@@ -4152,7 +4227,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="7" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="D231" s="5">
         <v>1</v>
@@ -4160,9 +4235,11 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
-      <c r="B232" s="4"/>
+      <c r="B232" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="C232" s="7" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D232" s="5">
         <v>1</v>
@@ -4171,8 +4248,8 @@
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
-      <c r="C233" s="9" t="s">
-        <v>279</v>
+      <c r="C233" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="D233" s="5">
         <v>1</v>
@@ -4181,8 +4258,8 @@
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
-      <c r="C234" s="9" t="s">
-        <v>280</v>
+      <c r="C234" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="D234" s="5">
         <v>1</v>
@@ -4191,8 +4268,8 @@
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
-      <c r="C235" s="9" t="s">
-        <v>281</v>
+      <c r="C235" s="7" t="s">
+        <v>269</v>
       </c>
       <c r="D235" s="5">
         <v>1</v>
@@ -4201,22 +4278,18 @@
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
-      <c r="C236" s="9" t="s">
-        <v>282</v>
+      <c r="C236" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="D236" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A237" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B237" s="4" t="s">
-        <v>426</v>
-      </c>
+      <c r="A237" s="4"/>
+      <c r="B237" s="4"/>
       <c r="C237" s="7" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="D237" s="5">
         <v>1</v>
@@ -4226,7 +4299,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="7" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="D238" s="5">
         <v>1</v>
@@ -4234,9 +4307,11 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
-      <c r="B239" s="4"/>
+      <c r="B239" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="C239" s="7" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="D239" s="5">
         <v>1</v>
@@ -4246,7 +4321,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="7" t="s">
-        <v>287</v>
+        <v>195</v>
       </c>
       <c r="D240" s="5">
         <v>1</v>
@@ -4256,7 +4331,7 @@
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="7" t="s">
-        <v>288</v>
+        <v>196</v>
       </c>
       <c r="D241" s="5">
         <v>1</v>
@@ -4266,7 +4341,7 @@
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="7" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="D242" s="5">
         <v>1</v>
@@ -4276,7 +4351,7 @@
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
       <c r="C243" s="7" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D243" s="5">
         <v>1</v>
@@ -4286,7 +4361,7 @@
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="7" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="D244" s="5">
         <v>1</v>
@@ -4296,7 +4371,7 @@
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="7" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D245" s="5">
         <v>1</v>
@@ -4304,21 +4379,21 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="4"/>
-      <c r="B246" s="4"/>
+      <c r="B246" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="C246" s="7" t="s">
-        <v>422</v>
+        <v>197</v>
       </c>
       <c r="D246" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" s="4"/>
-      <c r="B247" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="B247" s="4"/>
       <c r="C247" s="7" t="s">
-        <v>293</v>
+        <v>198</v>
       </c>
       <c r="D247" s="5">
         <v>1</v>
@@ -4328,7 +4403,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="7" t="s">
-        <v>294</v>
+        <v>199</v>
       </c>
       <c r="D248" s="5">
         <v>1</v>
@@ -4337,8 +4412,8 @@
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
-      <c r="C249" s="7" t="s">
-        <v>359</v>
+      <c r="C249" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="D249" s="5">
         <v>1</v>
@@ -4347,8 +4422,8 @@
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
-      <c r="C250" s="7" t="s">
-        <v>295</v>
+      <c r="C250" s="9" t="s">
+        <v>278</v>
       </c>
       <c r="D250" s="5">
         <v>1</v>
@@ -4357,8 +4432,8 @@
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
-      <c r="C251" s="7" t="s">
-        <v>296</v>
+      <c r="C251" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="D251" s="5">
         <v>1</v>
@@ -4367,18 +4442,22 @@
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
-      <c r="C252" s="7" t="s">
-        <v>297</v>
+      <c r="C252" s="9" t="s">
+        <v>280</v>
       </c>
       <c r="D252" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="4"/>
-      <c r="B253" s="4"/>
+      <c r="A253" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>413</v>
+      </c>
       <c r="C253" s="7" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D253" s="5">
         <v>1</v>
@@ -4388,21 +4467,17 @@
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="7" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="D254" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B255" s="4" t="s">
-        <v>301</v>
-      </c>
+      <c r="A255" s="4"/>
+      <c r="B255" s="4"/>
       <c r="C255" s="7" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D255" s="5">
         <v>1</v>
@@ -4412,7 +4487,7 @@
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="7" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D256" s="5">
         <v>1</v>
@@ -4422,7 +4497,7 @@
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="7" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="D257" s="5">
         <v>1</v>
@@ -4430,11 +4505,9 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="4"/>
-      <c r="B258" s="4" t="s">
-        <v>317</v>
-      </c>
+      <c r="B258" s="4"/>
       <c r="C258" s="7" t="s">
-        <v>305</v>
+        <v>456</v>
       </c>
       <c r="D258" s="5">
         <v>1</v>
@@ -4444,7 +4517,7 @@
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="7" t="s">
-        <v>306</v>
+        <v>455</v>
       </c>
       <c r="D259" s="5">
         <v>1</v>
@@ -4454,7 +4527,7 @@
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="7" t="s">
-        <v>307</v>
+        <v>453</v>
       </c>
       <c r="D260" s="5">
         <v>1</v>
@@ -4462,11 +4535,9 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="4"/>
-      <c r="B261" s="4" t="s">
-        <v>318</v>
-      </c>
+      <c r="B261" s="4"/>
       <c r="C261" s="7" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="D261" s="5">
         <v>1</v>
@@ -4476,7 +4547,7 @@
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="7" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="D262" s="5">
         <v>1</v>
@@ -4486,7 +4557,7 @@
       <c r="A263" s="4"/>
       <c r="B263" s="4"/>
       <c r="C263" s="7" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D263" s="5">
         <v>1</v>
@@ -4494,21 +4565,21 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="4"/>
-      <c r="B264" s="4" t="s">
-        <v>319</v>
-      </c>
+      <c r="B264" s="4"/>
       <c r="C264" s="7" t="s">
-        <v>311</v>
+        <v>409</v>
       </c>
       <c r="D264" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
-      <c r="B265" s="4"/>
+      <c r="B265" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="C265" s="7" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="D265" s="5">
         <v>1</v>
@@ -4518,7 +4589,7 @@
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="7" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="D266" s="5">
         <v>1</v>
@@ -4526,11 +4597,9 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="4"/>
-      <c r="B267" s="4" t="s">
-        <v>320</v>
-      </c>
+      <c r="B267" s="4"/>
       <c r="C267" s="7" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="D267" s="5">
         <v>1</v>
@@ -4540,7 +4609,7 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="7" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="D268" s="5">
         <v>1</v>
@@ -4550,7 +4619,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="7" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="D269" s="5">
         <v>1</v>
@@ -4558,11 +4627,9 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="4"/>
-      <c r="B270" s="4" t="s">
-        <v>323</v>
-      </c>
+      <c r="B270" s="4"/>
       <c r="C270" s="7" t="s">
-        <v>321</v>
+        <v>446</v>
       </c>
       <c r="D270" s="5">
         <v>1</v>
@@ -4572,29 +4639,31 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="7" t="s">
-        <v>322</v>
+        <v>434</v>
       </c>
       <c r="D271" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A272" s="4" t="s">
-        <v>324</v>
-      </c>
+      <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="7" t="s">
-        <v>325</v>
+        <v>445</v>
       </c>
       <c r="D272" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="4"/>
-      <c r="B273" s="4"/>
+      <c r="A273" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B273" s="4" t="s">
+        <v>294</v>
+      </c>
       <c r="C273" s="7" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="D273" s="5">
         <v>1</v>
@@ -4603,32 +4672,28 @@
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
-      <c r="C274" s="9" t="s">
-        <v>327</v>
+      <c r="C274" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="D274" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="7" t="s">
-        <v>415</v>
+        <v>297</v>
       </c>
       <c r="D275" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A276" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="B276" s="4" t="s">
-        <v>427</v>
-      </c>
+      <c r="A276" s="4"/>
+      <c r="B276" s="4"/>
       <c r="C276" s="7" t="s">
-        <v>328</v>
+        <v>428</v>
       </c>
       <c r="D276" s="5">
         <v>1</v>
@@ -4636,9 +4701,11 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
-      <c r="B277" s="4"/>
+      <c r="B277" s="4" t="s">
+        <v>310</v>
+      </c>
       <c r="C277" s="7" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="D277" s="5">
         <v>1</v>
@@ -4648,7 +4715,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="7" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="D278" s="5">
         <v>1</v>
@@ -4658,7 +4725,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="7" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
       <c r="D279" s="5">
         <v>1</v>
@@ -4668,7 +4735,7 @@
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="7" t="s">
-        <v>332</v>
+        <v>429</v>
       </c>
       <c r="D280" s="5">
         <v>1</v>
@@ -4676,9 +4743,11 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
-      <c r="B281" s="4"/>
+      <c r="B281" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="C281" s="7" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="D281" s="5">
         <v>1</v>
@@ -4688,7 +4757,7 @@
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="7" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="D282" s="5">
         <v>1</v>
@@ -4698,7 +4767,7 @@
       <c r="A283" s="4"/>
       <c r="B283" s="4"/>
       <c r="C283" s="7" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="D283" s="5">
         <v>1</v>
@@ -4708,7 +4777,7 @@
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="7" t="s">
-        <v>336</v>
+        <v>430</v>
       </c>
       <c r="D284" s="5">
         <v>1</v>
@@ -4717,10 +4786,10 @@
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="4"/>
       <c r="B285" s="4" t="s">
-        <v>377</v>
+        <v>312</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="D285" s="5">
         <v>1</v>
@@ -4730,7 +4799,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="7" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="D286" s="5">
         <v>1</v>
@@ -4740,7 +4809,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="7" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="D287" s="5">
         <v>1</v>
@@ -4750,7 +4819,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="7" t="s">
-        <v>340</v>
+        <v>431</v>
       </c>
       <c r="D288" s="5">
         <v>1</v>
@@ -4758,9 +4827,11 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="4"/>
-      <c r="B289" s="4"/>
+      <c r="B289" s="4" t="s">
+        <v>313</v>
+      </c>
       <c r="C289" s="7" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="D289" s="5">
         <v>1</v>
@@ -4770,7 +4841,7 @@
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="7" t="s">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="D290" s="5">
         <v>1</v>
@@ -4780,7 +4851,7 @@
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="7" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="D291" s="5">
         <v>1</v>
@@ -4790,7 +4861,7 @@
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="7" t="s">
-        <v>344</v>
+        <v>432</v>
       </c>
       <c r="D292" s="5">
         <v>1</v>
@@ -4798,9 +4869,11 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
-      <c r="B293" s="4"/>
+      <c r="B293" s="4" t="s">
+        <v>316</v>
+      </c>
       <c r="C293" s="7" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="D293" s="5">
         <v>1</v>
@@ -4810,17 +4883,19 @@
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="7" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="D294" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="4"/>
+      <c r="A295" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="B295" s="4"/>
       <c r="C295" s="7" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -4830,7 +4905,7 @@
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="7" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="D296" s="5">
         <v>1</v>
@@ -4839,28 +4914,32 @@
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
-      <c r="C297" s="7" t="s">
-        <v>349</v>
+      <c r="C297" s="9" t="s">
+        <v>320</v>
       </c>
       <c r="D297" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4"/>
       <c r="C298" s="7" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="D298" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="4"/>
-      <c r="B299" s="4"/>
+      <c r="A299" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>414</v>
+      </c>
       <c r="C299" s="7" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="D299" s="5">
         <v>1</v>
@@ -4870,7 +4949,7 @@
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="7" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="D300" s="5">
         <v>1</v>
@@ -4880,7 +4959,7 @@
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="7" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="D301" s="5">
         <v>1</v>
@@ -4890,7 +4969,7 @@
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="7" t="s">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="D302" s="5">
         <v>1</v>
@@ -4900,7 +4979,7 @@
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="7" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="D303" s="5">
         <v>1</v>
@@ -4910,7 +4989,7 @@
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="7" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="D304" s="5">
         <v>1</v>
@@ -4920,7 +4999,7 @@
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="7" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="D305" s="5">
         <v>1</v>
@@ -4930,7 +5009,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="7" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="D306" s="5">
         <v>1</v>
@@ -4940,7 +5019,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="7" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="D307" s="5">
         <v>1</v>
@@ -4950,7 +5029,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="7" t="s">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="D308" s="5">
         <v>1</v>
@@ -4960,7 +5039,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="7" t="s">
-        <v>375</v>
+        <v>448</v>
       </c>
       <c r="D309" s="5">
         <v>1</v>
@@ -4970,21 +5049,19 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="7" t="s">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="D310" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A311" s="4" t="s">
-        <v>360</v>
-      </c>
+      <c r="A311" s="4"/>
       <c r="B311" s="4" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
       <c r="D311" s="5">
         <v>1</v>
@@ -4994,7 +5071,7 @@
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="7" t="s">
-        <v>362</v>
+        <v>331</v>
       </c>
       <c r="D312" s="5">
         <v>1</v>
@@ -5004,7 +5081,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="7" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="D313" s="5">
         <v>1</v>
@@ -5014,7 +5091,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="7" t="s">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="D314" s="5">
         <v>1</v>
@@ -5024,7 +5101,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="7" t="s">
-        <v>365</v>
+        <v>334</v>
       </c>
       <c r="D315" s="5">
         <v>1</v>
@@ -5034,7 +5111,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="7" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="D316" s="5">
         <v>1</v>
@@ -5044,7 +5121,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="7" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="D317" s="5">
         <v>1</v>
@@ -5054,7 +5131,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="7" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="D318" s="5">
         <v>1</v>
@@ -5064,7 +5141,7 @@
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="7" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="D319" s="5">
         <v>1</v>
@@ -5074,7 +5151,7 @@
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="7" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="D320" s="5">
         <v>1</v>
@@ -5084,7 +5161,7 @@
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="7" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="D321" s="5">
         <v>1</v>
@@ -5094,7 +5171,7 @@
       <c r="A322" s="4"/>
       <c r="B322" s="4"/>
       <c r="C322" s="7" t="s">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="D322" s="5">
         <v>1</v>
@@ -5102,11 +5179,9 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" s="4"/>
-      <c r="B323" s="4" t="s">
-        <v>378</v>
-      </c>
+      <c r="B323" s="4"/>
       <c r="C323" s="7" t="s">
-        <v>379</v>
+        <v>342</v>
       </c>
       <c r="D323" s="5">
         <v>1</v>
@@ -5116,7 +5191,7 @@
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="7" t="s">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="D324" s="5">
         <v>1</v>
@@ -5126,7 +5201,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="7" t="s">
-        <v>381</v>
+        <v>344</v>
       </c>
       <c r="D325" s="5">
         <v>1</v>
@@ -5136,7 +5211,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="7" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="D326" s="5">
         <v>1</v>
@@ -5146,7 +5221,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="7" t="s">
-        <v>383</v>
+        <v>346</v>
       </c>
       <c r="D327" s="5">
         <v>1</v>
@@ -5156,7 +5231,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="7" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="D328" s="5">
         <v>1</v>
@@ -5166,7 +5241,7 @@
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="7" t="s">
-        <v>385</v>
+        <v>348</v>
       </c>
       <c r="D329" s="5">
         <v>1</v>
@@ -5176,7 +5251,7 @@
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="7" t="s">
-        <v>386</v>
+        <v>349</v>
       </c>
       <c r="D330" s="5">
         <v>1</v>
@@ -5186,7 +5261,7 @@
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="7" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="D331" s="5">
         <v>1</v>
@@ -5196,7 +5271,7 @@
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="7" t="s">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="D332" s="5">
         <v>1</v>
@@ -5206,7 +5281,7 @@
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="7" t="s">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="D333" s="5">
         <v>1</v>
@@ -5216,7 +5291,7 @@
       <c r="A334" s="4"/>
       <c r="B334" s="4"/>
       <c r="C334" s="7" t="s">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="D334" s="5">
         <v>1</v>
@@ -5224,13 +5299,13 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>392</v>
+        <v>352</v>
       </c>
       <c r="D335" s="5">
         <v>1</v>
@@ -5240,7 +5315,7 @@
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="7" t="s">
-        <v>393</v>
+        <v>353</v>
       </c>
       <c r="D336" s="5">
         <v>1</v>
@@ -5250,7 +5325,7 @@
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="7" t="s">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="D337" s="5">
         <v>1</v>
@@ -5260,7 +5335,7 @@
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="7" t="s">
-        <v>395</v>
+        <v>355</v>
       </c>
       <c r="D338" s="5">
         <v>1</v>
@@ -5270,7 +5345,7 @@
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="7" t="s">
-        <v>396</v>
+        <v>356</v>
       </c>
       <c r="D339" s="5">
         <v>1</v>
@@ -5280,7 +5355,7 @@
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="7" t="s">
-        <v>397</v>
+        <v>357</v>
       </c>
       <c r="D340" s="5">
         <v>1</v>
@@ -5290,7 +5365,7 @@
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="7" t="s">
-        <v>398</v>
+        <v>358</v>
       </c>
       <c r="D341" s="5">
         <v>1</v>
@@ -5300,7 +5375,7 @@
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="7" t="s">
-        <v>399</v>
+        <v>359</v>
       </c>
       <c r="D342" s="5">
         <v>1</v>
@@ -5308,11 +5383,9 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="4"/>
-      <c r="B343" s="4" t="s">
-        <v>400</v>
-      </c>
+      <c r="B343" s="4"/>
       <c r="C343" s="7" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="D343" s="5">
         <v>1</v>
@@ -5322,7 +5395,7 @@
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="7" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="D344" s="5">
         <v>1</v>
@@ -5332,7 +5405,7 @@
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="7" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="D345" s="5">
         <v>1</v>
@@ -5342,7 +5415,7 @@
       <c r="A346" s="4"/>
       <c r="B346" s="4"/>
       <c r="C346" s="7" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="D346" s="5">
         <v>1</v>
@@ -5350,9 +5423,11 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
-      <c r="B347" s="4"/>
+      <c r="B347" s="4" t="s">
+        <v>369</v>
+      </c>
       <c r="C347" s="7" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D347" s="5">
         <v>1</v>
@@ -5362,19 +5437,17 @@
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="7" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D348" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A349" s="4" t="s">
-        <v>405</v>
-      </c>
+      <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="7" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="D349" s="5">
         <v>1</v>
@@ -5384,7 +5457,7 @@
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="7" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="D350" s="5">
         <v>1</v>
@@ -5394,7 +5467,7 @@
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="7" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="D351" s="5">
         <v>1</v>
@@ -5404,7 +5477,7 @@
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="7" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="D352" s="5">
         <v>1</v>
@@ -5414,7 +5487,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="7" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="D353" s="5">
         <v>1</v>
@@ -5424,19 +5497,17 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="7" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="D354" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A355" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="7" t="s">
-        <v>138</v>
+        <v>378</v>
       </c>
       <c r="D355" s="5">
         <v>1</v>
@@ -5446,7 +5517,7 @@
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="7" t="s">
-        <v>139</v>
+        <v>379</v>
       </c>
       <c r="D356" s="5">
         <v>1</v>
@@ -5456,7 +5527,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="7" t="s">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="D357" s="5">
         <v>1</v>
@@ -5466,161 +5537,271 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="7" t="s">
-        <v>141</v>
+        <v>381</v>
       </c>
       <c r="D358" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="4"/>
-      <c r="B359" s="4"/>
-      <c r="C359" s="9"/>
-      <c r="D359" s="5"/>
+      <c r="A359" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="C359" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D359" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
-      <c r="C360" s="9"/>
-      <c r="D360" s="5"/>
+      <c r="C360" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D360" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
-      <c r="C361" s="9"/>
-      <c r="D361" s="5"/>
+      <c r="C361" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D361" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="4"/>
       <c r="B362" s="4"/>
-      <c r="C362" s="9"/>
-      <c r="D362" s="5"/>
+      <c r="C362" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D362" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
-      <c r="C363" s="9"/>
-      <c r="D363" s="5"/>
+      <c r="C363" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D363" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
-      <c r="C364" s="9"/>
-      <c r="D364" s="5"/>
+      <c r="C364" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="D364" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
-      <c r="C365" s="9"/>
-      <c r="D365" s="5"/>
+      <c r="C365" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D365" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
-      <c r="C366" s="9"/>
-      <c r="D366" s="5"/>
+      <c r="C366" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D366" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
-      <c r="B367" s="4"/>
-      <c r="C367" s="9"/>
-      <c r="D367" s="5"/>
+      <c r="B367" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C367" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D367" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="4"/>
       <c r="B368" s="4"/>
-      <c r="C368" s="9"/>
-      <c r="D368" s="5"/>
+      <c r="C368" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="D368" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
-      <c r="C369" s="9"/>
-      <c r="D369" s="5"/>
+      <c r="C369" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D369" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
-      <c r="C370" s="9"/>
-      <c r="D370" s="5"/>
+      <c r="C370" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D370" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
-      <c r="C371" s="9"/>
-      <c r="D371" s="5"/>
+      <c r="C371" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D371" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
-      <c r="C372" s="9"/>
-      <c r="D372" s="5"/>
+      <c r="C372" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D372" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
-      <c r="C373" s="9"/>
-      <c r="D373" s="5"/>
+      <c r="C373" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D373" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A374" s="4"/>
+      <c r="A374" s="4" t="s">
+        <v>394</v>
+      </c>
       <c r="B374" s="4"/>
-      <c r="C374" s="9"/>
-      <c r="D374" s="5"/>
+      <c r="C374" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D374" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
-      <c r="C375" s="9"/>
-      <c r="D375" s="5"/>
+      <c r="C375" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D375" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
-      <c r="C376" s="9"/>
-      <c r="D376" s="5"/>
+      <c r="C376" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="D376" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
-      <c r="C377" s="9"/>
-      <c r="D377" s="5"/>
+      <c r="C377" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D377" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
-      <c r="C378" s="9"/>
-      <c r="D378" s="5"/>
+      <c r="C378" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D378" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
-      <c r="C379" s="9"/>
-      <c r="D379" s="5"/>
+      <c r="C379" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D379" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A380" s="4"/>
+      <c r="A380" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B380" s="4"/>
-      <c r="C380" s="9"/>
-      <c r="D380" s="5"/>
+      <c r="C380" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D380" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
-      <c r="C381" s="9"/>
-      <c r="D381" s="5"/>
+      <c r="C381" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D381" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
-      <c r="B382" s="7"/>
-      <c r="C382" s="9"/>
-      <c r="D382" s="5"/>
+      <c r="B382" s="4"/>
+      <c r="C382" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D382" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
-      <c r="C383" s="9"/>
-      <c r="D383" s="5"/>
+      <c r="C383" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D383" s="5">
+        <v>1</v>
+      </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
@@ -5631,79 +5812,229 @@
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" s="4"/>
       <c r="B385" s="4"/>
-      <c r="C385" s="7"/>
+      <c r="C385" s="9"/>
       <c r="D385" s="5"/>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" s="4"/>
       <c r="B386" s="4"/>
-      <c r="C386" s="7"/>
+      <c r="C386" s="9"/>
       <c r="D386" s="5"/>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="4"/>
       <c r="B387" s="4"/>
-      <c r="C387" s="7"/>
+      <c r="C387" s="9"/>
       <c r="D387" s="5"/>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="4"/>
       <c r="B388" s="4"/>
-      <c r="C388" s="7"/>
+      <c r="C388" s="9"/>
       <c r="D388" s="5"/>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="4"/>
       <c r="B389" s="4"/>
-      <c r="C389" s="4"/>
+      <c r="C389" s="9"/>
       <c r="D389" s="5"/>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" s="4"/>
       <c r="B390" s="4"/>
-      <c r="C390" s="4"/>
+      <c r="C390" s="9"/>
       <c r="D390" s="5"/>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" s="4"/>
       <c r="B391" s="4"/>
-      <c r="C391" s="4"/>
+      <c r="C391" s="9"/>
       <c r="D391" s="5"/>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" s="4"/>
       <c r="B392" s="4"/>
-      <c r="C392" s="4"/>
+      <c r="C392" s="9"/>
       <c r="D392" s="5"/>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
-      <c r="C393" s="4"/>
+      <c r="C393" s="9"/>
       <c r="D393" s="5"/>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
-      <c r="C394" s="4"/>
+      <c r="C394" s="9"/>
       <c r="D394" s="5"/>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
       <c r="B395" s="4"/>
-      <c r="C395" s="4"/>
+      <c r="C395" s="9"/>
       <c r="D395" s="5"/>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
-      <c r="C396" s="4"/>
+      <c r="C396" s="9"/>
       <c r="D396" s="5"/>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A397" s="4"/>
+      <c r="B397" s="4"/>
+      <c r="C397" s="9"/>
+      <c r="D397" s="5"/>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A398" s="4"/>
+      <c r="B398" s="4"/>
+      <c r="C398" s="9"/>
+      <c r="D398" s="5"/>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A399" s="4"/>
+      <c r="B399" s="4"/>
+      <c r="C399" s="9"/>
+      <c r="D399" s="5"/>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A400" s="4"/>
+      <c r="B400" s="4"/>
+      <c r="C400" s="9"/>
+      <c r="D400" s="5"/>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A401" s="4"/>
+      <c r="B401" s="4"/>
+      <c r="C401" s="9"/>
+      <c r="D401" s="5"/>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A402" s="4"/>
+      <c r="B402" s="4"/>
+      <c r="C402" s="9"/>
+      <c r="D402" s="5"/>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A403" s="4"/>
+      <c r="B403" s="4"/>
+      <c r="C403" s="9"/>
+      <c r="D403" s="5"/>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A404" s="4"/>
+      <c r="B404" s="4"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="5"/>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A405" s="4"/>
+      <c r="B405" s="4"/>
+      <c r="C405" s="9"/>
+      <c r="D405" s="5"/>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A406" s="4"/>
+      <c r="B406" s="4"/>
+      <c r="C406" s="9"/>
+      <c r="D406" s="5"/>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A407" s="4"/>
+      <c r="B407" s="7"/>
+      <c r="C407" s="9"/>
+      <c r="D407" s="5"/>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A408" s="4"/>
+      <c r="B408" s="4"/>
+      <c r="C408" s="9"/>
+      <c r="D408" s="5"/>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A409" s="4"/>
+      <c r="B409" s="4"/>
+      <c r="C409" s="9"/>
+      <c r="D409" s="5"/>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A410" s="4"/>
+      <c r="B410" s="4"/>
+      <c r="C410" s="7"/>
+      <c r="D410" s="5"/>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A411" s="4"/>
+      <c r="B411" s="4"/>
+      <c r="C411" s="7"/>
+      <c r="D411" s="5"/>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A412" s="4"/>
+      <c r="B412" s="4"/>
+      <c r="C412" s="7"/>
+      <c r="D412" s="5"/>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A413" s="4"/>
+      <c r="B413" s="4"/>
+      <c r="C413" s="7"/>
+      <c r="D413" s="5"/>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A414" s="4"/>
+      <c r="B414" s="4"/>
+      <c r="C414" s="4"/>
+      <c r="D414" s="5"/>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A415" s="4"/>
+      <c r="B415" s="4"/>
+      <c r="C415" s="4"/>
+      <c r="D415" s="5"/>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A416" s="4"/>
+      <c r="B416" s="4"/>
+      <c r="C416" s="4"/>
+      <c r="D416" s="5"/>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A417" s="4"/>
+      <c r="B417" s="4"/>
+      <c r="C417" s="4"/>
+      <c r="D417" s="5"/>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A418" s="4"/>
+      <c r="B418" s="4"/>
+      <c r="C418" s="4"/>
+      <c r="D418" s="5"/>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A419" s="4"/>
+      <c r="B419" s="4"/>
+      <c r="C419" s="4"/>
+      <c r="D419" s="5"/>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A420" s="4"/>
+      <c r="B420" s="4"/>
+      <c r="C420" s="4"/>
+      <c r="D420" s="5"/>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A421" s="4"/>
+      <c r="B421" s="4"/>
+      <c r="C421" s="4"/>
+      <c r="D421" s="5"/>
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C9:C10" name="Tags_1_3_1"/>
-    <protectedRange sqref="C14" name="Tags_1_3_1_3"/>
+    <protectedRange sqref="C11:C12" name="Tags_1_3_1"/>
+    <protectedRange sqref="C16" name="Tags_1_3_1_3"/>
   </protectedRanges>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\_deploy\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155A9F04-7A87-4030-A659-55A19D18B8AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0E2A6C-6219-4430-8898-F0552E6B10FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25905" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="443">
   <si>
     <t>Oberordner</t>
   </si>
@@ -884,6 +884,12 @@
     <t>PZE gesamt</t>
   </si>
   <si>
+    <t>Perso 1 + Perso 2 Dose</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2Totale</t>
+  </si>
+  <si>
     <t>Headset Strom</t>
   </si>
   <si>
@@ -1199,6 +1205,12 @@
     <t>NWS 3 - Beschriftung / SN / LIN</t>
   </si>
   <si>
+    <t>SN AcessA</t>
+  </si>
+  <si>
+    <t>SN AcessB</t>
+  </si>
+  <si>
     <t>SN LTE-Router Access A</t>
   </si>
   <si>
@@ -1229,6 +1241,12 @@
     <t>Digitales Backschema</t>
   </si>
   <si>
+    <t>SN_KVM Switch</t>
+  </si>
+  <si>
+    <t>LIN_KVM Switch</t>
+  </si>
+  <si>
     <t>Plantasche NWS</t>
   </si>
   <si>
@@ -1274,6 +1292,12 @@
     <t>NWS 3 Übersicht / Strom / PE / Codierung</t>
   </si>
   <si>
+    <t>SN_Telefon 1</t>
+  </si>
+  <si>
+    <t>SN_Telefon 2</t>
+  </si>
+  <si>
     <t>Lautsprecher Monitor</t>
   </si>
   <si>
@@ -1289,6 +1313,36 @@
     <t>SN SMC</t>
   </si>
   <si>
+    <t>SN Vocovo Controller 2</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 2</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 5</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 5</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 4</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 4</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 3</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 3</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 1</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 1</t>
+  </si>
+  <si>
     <t>SN Kundenterminal</t>
   </si>
   <si>
@@ -1296,102 +1350,6 @@
   </si>
   <si>
     <t>HGA Dose Totale</t>
-  </si>
-  <si>
-    <t>SCO 89 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 89 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller</t>
-  </si>
-  <si>
-    <t>SN Vocovo Repeater 1</t>
-  </si>
-  <si>
-    <t>SN Vocovo Repeater 2</t>
-  </si>
-  <si>
-    <t>SN Vocovo Repeater 3</t>
-  </si>
-  <si>
-    <t>SN Vocovo Repeater 4</t>
-  </si>
-  <si>
-    <t>SN Vocovo Repeater 5</t>
-  </si>
-  <si>
-    <t>SN Digitales Backschema</t>
-  </si>
-  <si>
-    <t>SN KVM Switch</t>
-  </si>
-  <si>
-    <t>LIN KVM Switch</t>
-  </si>
-  <si>
-    <t>SN Telefon 1</t>
-  </si>
-  <si>
-    <t>SN Telefon 2</t>
-  </si>
-  <si>
-    <t>SN MDE</t>
-  </si>
-  <si>
-    <t>SN Ladeschalen MDE</t>
-  </si>
-  <si>
-    <t>SN MRED</t>
-  </si>
-  <si>
-    <t>SN Ladeschalen MRED</t>
-  </si>
-  <si>
-    <t>SN Front Reader</t>
-  </si>
-  <si>
-    <t>SN Thin Client</t>
-  </si>
-  <si>
-    <t>LIN Thin Client</t>
-  </si>
-  <si>
-    <t>SN Lautsprecherleiste</t>
-  </si>
-  <si>
-    <t>SN Registrierungsmodul</t>
-  </si>
-  <si>
-    <t>SN Festplatte 2</t>
-  </si>
-  <si>
-    <t>SN Festplatte 3</t>
-  </si>
-  <si>
-    <t>SN Safebag Festplatten</t>
-  </si>
-  <si>
-    <t>SN AccessA</t>
-  </si>
-  <si>
-    <t>SN AccessB</t>
-  </si>
-  <si>
-    <t>SDP Lieferung + Lieferscheine</t>
-  </si>
-  <si>
-    <t>Besprechung Dose Detail</t>
-  </si>
-  <si>
-    <t>Besprechung Dose Totale</t>
-  </si>
-  <si>
-    <t>Perso 1 + Perso 2 Totale</t>
-  </si>
-  <si>
-    <t>Perso 1 + Perso 2 Detail</t>
   </si>
 </sst>
 </file>
@@ -1822,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D421"/>
+  <dimension ref="A1:D409"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -1850,7 +1808,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>76</v>
@@ -1913,7 +1871,7 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -1923,7 +1881,7 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
@@ -1933,7 +1891,7 @@
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D10" s="8">
         <v>3</v>
@@ -2409,7 +2367,7 @@
         <v>70</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>425</v>
+        <v>61</v>
       </c>
       <c r="D54" s="5">
         <v>1</v>
@@ -2419,7 +2377,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7" t="s">
-        <v>426</v>
+        <v>62</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -2645,7 +2603,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="7" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
@@ -2655,7 +2613,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="7" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -2665,7 +2623,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="7" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D79" s="5">
         <v>3</v>
@@ -2767,17 +2725,17 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="7" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D90" s="5">
         <v>1</v>
@@ -2787,31 +2745,31 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="7" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
+      <c r="A92" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>418</v>
+      </c>
       <c r="C92" s="7" t="s">
-        <v>404</v>
+        <v>112</v>
       </c>
       <c r="D92" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>412</v>
-      </c>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
       <c r="C93" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D93" s="5">
         <v>1</v>
@@ -2821,7 +2779,7 @@
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
@@ -2831,7 +2789,7 @@
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
@@ -2841,7 +2799,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D96" s="5">
         <v>1</v>
@@ -2851,7 +2809,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D97" s="5">
         <v>1</v>
@@ -2861,7 +2819,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2871,7 +2829,7 @@
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
@@ -2881,7 +2839,7 @@
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
@@ -2891,7 +2849,7 @@
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
@@ -2901,7 +2859,7 @@
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
@@ -2911,7 +2869,7 @@
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D103" s="5">
         <v>1</v>
@@ -2921,7 +2879,7 @@
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="7" t="s">
-        <v>124</v>
+        <v>425</v>
       </c>
       <c r="D104" s="5">
         <v>1</v>
@@ -2931,29 +2889,29 @@
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="7" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
+      <c r="B106" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="C106" s="7" t="s">
-        <v>406</v>
+        <v>125</v>
       </c>
       <c r="D106" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="4"/>
-      <c r="B107" s="4" t="s">
-        <v>123</v>
-      </c>
+      <c r="B107" s="4"/>
       <c r="C107" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
@@ -2963,7 +2921,7 @@
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
@@ -2973,7 +2931,7 @@
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
@@ -2983,7 +2941,7 @@
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
@@ -2993,7 +2951,7 @@
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="7" t="s">
-        <v>129</v>
+        <v>406</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
@@ -3003,7 +2961,7 @@
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="7" t="s">
-        <v>434</v>
+        <v>407</v>
       </c>
       <c r="D112" s="5">
         <v>1</v>
@@ -3013,7 +2971,7 @@
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="7" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="D113" s="5">
         <v>1</v>
@@ -3023,7 +2981,7 @@
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="7" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
@@ -3031,9 +2989,11 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
+      <c r="B115" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="C115" s="7" t="s">
-        <v>437</v>
+        <v>131</v>
       </c>
       <c r="D115" s="5">
         <v>1</v>
@@ -3043,7 +3003,7 @@
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="7" t="s">
-        <v>438</v>
+        <v>132</v>
       </c>
       <c r="D116" s="5">
         <v>1</v>
@@ -3053,7 +3013,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
-        <v>439</v>
+        <v>133</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
@@ -3063,17 +3023,19 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>440</v>
+        <v>134</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="4"/>
+      <c r="A119" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="B119" s="4"/>
       <c r="C119" s="7" t="s">
-        <v>441</v>
+        <v>141</v>
       </c>
       <c r="D119" s="5">
         <v>1</v>
@@ -3083,7 +3045,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="7" t="s">
-        <v>442</v>
+        <v>142</v>
       </c>
       <c r="D120" s="5">
         <v>1</v>
@@ -3093,7 +3055,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="7" t="s">
-        <v>443</v>
+        <v>143</v>
       </c>
       <c r="D121" s="5">
         <v>1</v>
@@ -3103,7 +3065,7 @@
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="7" t="s">
-        <v>444</v>
+        <v>144</v>
       </c>
       <c r="D122" s="5">
         <v>1</v>
@@ -3113,7 +3075,7 @@
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="7" t="s">
-        <v>445</v>
+        <v>145</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
@@ -3121,11 +3083,9 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="4"/>
-      <c r="B124" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="B124" s="4"/>
       <c r="C124" s="7" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="D124" s="5">
         <v>1</v>
@@ -3135,17 +3095,19 @@
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="7" t="s">
-        <v>132</v>
+        <v>413</v>
       </c>
       <c r="D125" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="4"/>
+      <c r="A126" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="B126" s="4"/>
       <c r="C126" s="7" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D126" s="5">
         <v>1</v>
@@ -3155,7 +3117,7 @@
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="7" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="D127" s="5">
         <v>1</v>
@@ -3165,19 +3127,17 @@
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="7" t="s">
-        <v>452</v>
+        <v>150</v>
       </c>
       <c r="D128" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D129" s="5">
         <v>1</v>
@@ -3187,17 +3147,21 @@
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="7" t="s">
-        <v>142</v>
+        <v>414</v>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="4"/>
-      <c r="B131" s="4"/>
+      <c r="A131" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="C131" s="7" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D131" s="5">
         <v>1</v>
@@ -3207,7 +3171,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="7" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
@@ -3217,7 +3181,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="7" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
@@ -3227,7 +3191,7 @@
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="7" t="s">
-        <v>146</v>
+        <v>217</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
@@ -3237,19 +3201,17 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="7" t="s">
-        <v>407</v>
+        <v>219</v>
       </c>
       <c r="D135" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="7" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="D136" s="5">
         <v>1</v>
@@ -3259,7 +3221,7 @@
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="7" t="s">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="D137" s="5">
         <v>1</v>
@@ -3267,9 +3229,11 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
+      <c r="B138" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="C138" s="7" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D138" s="5">
         <v>1</v>
@@ -3279,7 +3243,7 @@
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D139" s="5">
         <v>1</v>
@@ -3289,21 +3253,17 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="7" t="s">
-        <v>408</v>
+        <v>157</v>
       </c>
       <c r="D140" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>201</v>
-      </c>
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
       <c r="C141" s="7" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="D141" s="5">
         <v>1</v>
@@ -3313,7 +3273,7 @@
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="7" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="D142" s="5">
         <v>1</v>
@@ -3323,7 +3283,7 @@
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="7" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="D143" s="5">
         <v>1</v>
@@ -3333,7 +3293,7 @@
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="7" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D144" s="5">
         <v>1</v>
@@ -3341,9 +3301,11 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
+      <c r="B145" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="C145" s="7" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
       <c r="D145" s="5">
         <v>1</v>
@@ -3353,7 +3315,7 @@
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="7" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="D146" s="5">
         <v>1</v>
@@ -3363,7 +3325,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="7" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="D147" s="5">
         <v>1</v>
@@ -3371,11 +3333,9 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="4"/>
-      <c r="B148" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="B148" s="4"/>
       <c r="C148" s="7" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="D148" s="5">
         <v>1</v>
@@ -3385,7 +3345,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="7" t="s">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="D149" s="5">
         <v>1</v>
@@ -3395,7 +3355,7 @@
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="7" t="s">
-        <v>157</v>
+        <v>227</v>
       </c>
       <c r="D150" s="5">
         <v>1</v>
@@ -3405,7 +3365,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="7" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D151" s="5">
         <v>1</v>
@@ -3413,9 +3373,11 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
+      <c r="B152" s="4" t="s">
+        <v>204</v>
+      </c>
       <c r="C152" s="7" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="D152" s="5">
         <v>1</v>
@@ -3425,7 +3387,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="7" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="D153" s="5">
         <v>1</v>
@@ -3435,7 +3397,7 @@
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="7" t="s">
-        <v>224</v>
+        <v>163</v>
       </c>
       <c r="D154" s="5">
         <v>1</v>
@@ -3443,11 +3405,9 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="4"/>
-      <c r="B155" s="4" t="s">
-        <v>203</v>
-      </c>
+      <c r="B155" s="4"/>
       <c r="C155" s="7" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="D155" s="5">
         <v>1</v>
@@ -3457,7 +3417,7 @@
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="7" t="s">
-        <v>159</v>
+        <v>230</v>
       </c>
       <c r="D156" s="5">
         <v>1</v>
@@ -3467,7 +3427,7 @@
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="7" t="s">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="D157" s="5">
         <v>1</v>
@@ -3477,7 +3437,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="D158" s="5">
         <v>1</v>
@@ -3485,9 +3445,11 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="B159" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="C159" s="7" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="D159" s="5">
         <v>1</v>
@@ -3497,7 +3459,7 @@
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="7" t="s">
-        <v>227</v>
+        <v>165</v>
       </c>
       <c r="D160" s="5">
         <v>1</v>
@@ -3507,7 +3469,7 @@
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="7" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="D161" s="5">
         <v>1</v>
@@ -3515,11 +3477,9 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="4"/>
-      <c r="B162" s="4" t="s">
-        <v>204</v>
-      </c>
+      <c r="B162" s="4"/>
       <c r="C162" s="7" t="s">
-        <v>161</v>
+        <v>233</v>
       </c>
       <c r="D162" s="5">
         <v>1</v>
@@ -3529,7 +3489,7 @@
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="7" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="D163" s="5">
         <v>1</v>
@@ -3539,7 +3499,7 @@
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="7" t="s">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
@@ -3549,7 +3509,7 @@
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D165" s="5">
         <v>1</v>
@@ -3557,9 +3517,11 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
-      <c r="B166" s="4"/>
+      <c r="B166" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="C166" s="7" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="D166" s="5">
         <v>1</v>
@@ -3569,7 +3531,7 @@
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="7" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="D167" s="5">
         <v>1</v>
@@ -3579,7 +3541,7 @@
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="7" t="s">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="D168" s="5">
         <v>1</v>
@@ -3587,11 +3549,9 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
-      <c r="B169" s="4" t="s">
-        <v>205</v>
-      </c>
+      <c r="B169" s="4"/>
       <c r="C169" s="7" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="D169" s="5">
         <v>1</v>
@@ -3601,7 +3561,7 @@
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="7" t="s">
-        <v>165</v>
+        <v>238</v>
       </c>
       <c r="D170" s="5">
         <v>1</v>
@@ -3611,7 +3571,7 @@
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="7" t="s">
-        <v>166</v>
+        <v>239</v>
       </c>
       <c r="D171" s="5">
         <v>1</v>
@@ -3621,7 +3581,7 @@
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D172" s="5">
         <v>1</v>
@@ -3629,9 +3589,11 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
-      <c r="B173" s="4"/>
+      <c r="B173" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="C173" s="7" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="D173" s="5">
         <v>1</v>
@@ -3641,7 +3603,7 @@
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="7" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="D174" s="5">
         <v>1</v>
@@ -3651,7 +3613,7 @@
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="7" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="D175" s="5">
         <v>1</v>
@@ -3659,11 +3621,9 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="4"/>
-      <c r="B176" s="4" t="s">
-        <v>206</v>
-      </c>
+      <c r="B176" s="4"/>
       <c r="C176" s="7" t="s">
-        <v>167</v>
+        <v>241</v>
       </c>
       <c r="D176" s="5">
         <v>1</v>
@@ -3673,7 +3633,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="7" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="D177" s="5">
         <v>1</v>
@@ -3683,7 +3643,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="7" t="s">
-        <v>169</v>
+        <v>243</v>
       </c>
       <c r="D178" s="5">
         <v>1</v>
@@ -3693,7 +3653,7 @@
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="7" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="D179" s="5">
         <v>1</v>
@@ -3701,9 +3661,11 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
+      <c r="B180" s="4" t="s">
+        <v>208</v>
+      </c>
       <c r="C180" s="7" t="s">
-        <v>238</v>
+        <v>173</v>
       </c>
       <c r="D180" s="5">
         <v>1</v>
@@ -3713,7 +3675,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="7" t="s">
-        <v>239</v>
+        <v>174</v>
       </c>
       <c r="D181" s="5">
         <v>1</v>
@@ -3723,7 +3685,7 @@
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="7" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="D182" s="5">
         <v>1</v>
@@ -3731,11 +3693,9 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="4"/>
-      <c r="B183" s="4" t="s">
-        <v>207</v>
-      </c>
+      <c r="B183" s="4"/>
       <c r="C183" s="7" t="s">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="D183" s="5">
         <v>1</v>
@@ -3745,7 +3705,7 @@
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="7" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
@@ -3755,7 +3715,7 @@
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="7" t="s">
-        <v>172</v>
+        <v>247</v>
       </c>
       <c r="D185" s="5">
         <v>1</v>
@@ -3765,7 +3725,7 @@
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="7" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="D186" s="5">
         <v>1</v>
@@ -3773,9 +3733,11 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
+      <c r="B187" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="C187" s="7" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="D187" s="5">
         <v>1</v>
@@ -3785,7 +3747,7 @@
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="7" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="D188" s="5">
         <v>1</v>
@@ -3795,7 +3757,7 @@
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="7" t="s">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="D189" s="5">
         <v>1</v>
@@ -3803,11 +3765,9 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="4"/>
-      <c r="B190" s="4" t="s">
-        <v>208</v>
-      </c>
+      <c r="B190" s="4"/>
       <c r="C190" s="7" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="D190" s="5">
         <v>1</v>
@@ -3817,7 +3777,7 @@
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="7" t="s">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="D191" s="5">
         <v>1</v>
@@ -3827,7 +3787,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="7" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="D192" s="5">
         <v>1</v>
@@ -3837,7 +3797,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="7" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D193" s="5">
         <v>1</v>
@@ -3845,9 +3805,11 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
-      <c r="B194" s="4"/>
+      <c r="B194" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="C194" s="7" t="s">
-        <v>246</v>
+        <v>179</v>
       </c>
       <c r="D194" s="5">
         <v>1</v>
@@ -3857,7 +3819,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="7" t="s">
-        <v>247</v>
+        <v>180</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -3867,7 +3829,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="7" t="s">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="D196" s="5">
         <v>1</v>
@@ -3875,11 +3837,9 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="4"/>
-      <c r="B197" s="4" t="s">
-        <v>209</v>
-      </c>
+      <c r="B197" s="4"/>
       <c r="C197" s="7" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="D197" s="5">
         <v>1</v>
@@ -3889,7 +3849,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="7" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="D198" s="5">
         <v>1</v>
@@ -3899,7 +3859,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="7" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="D199" s="5">
         <v>1</v>
@@ -3909,7 +3869,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="7" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D200" s="5">
         <v>1</v>
@@ -3917,9 +3877,11 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
+      <c r="B201" s="4" t="s">
+        <v>211</v>
+      </c>
       <c r="C201" s="7" t="s">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="D201" s="5">
         <v>1</v>
@@ -3929,7 +3891,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="7" t="s">
-        <v>251</v>
+        <v>183</v>
       </c>
       <c r="D202" s="5">
         <v>1</v>
@@ -3939,7 +3901,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="7" t="s">
-        <v>252</v>
+        <v>184</v>
       </c>
       <c r="D203" s="5">
         <v>1</v>
@@ -3947,11 +3909,9 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" s="4"/>
-      <c r="B204" s="4" t="s">
-        <v>210</v>
-      </c>
+      <c r="B204" s="4"/>
       <c r="C204" s="7" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="D204" s="5">
         <v>1</v>
@@ -3961,7 +3921,7 @@
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="7" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="D205" s="5">
         <v>1</v>
@@ -3971,7 +3931,7 @@
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="7" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="D206" s="5">
         <v>1</v>
@@ -3981,7 +3941,7 @@
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="7" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D207" s="5">
         <v>1</v>
@@ -3989,9 +3949,11 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
+      <c r="B208" s="4" t="s">
+        <v>212</v>
+      </c>
       <c r="C208" s="7" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="D208" s="5">
         <v>1</v>
@@ -4001,7 +3963,7 @@
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="7" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="D209" s="5">
         <v>1</v>
@@ -4011,7 +3973,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="7" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="D210" s="5">
         <v>1</v>
@@ -4019,11 +3981,9 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" s="4"/>
-      <c r="B211" s="4" t="s">
-        <v>211</v>
-      </c>
+      <c r="B211" s="4"/>
       <c r="C211" s="7" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="D211" s="5">
         <v>1</v>
@@ -4033,7 +3993,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="D212" s="5">
         <v>1</v>
@@ -4043,7 +4003,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="7" t="s">
-        <v>184</v>
+        <v>263</v>
       </c>
       <c r="D213" s="5">
         <v>1</v>
@@ -4053,7 +4013,7 @@
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="7" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D214" s="5">
         <v>1</v>
@@ -4061,9 +4021,11 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
-      <c r="B215" s="4"/>
+      <c r="B215" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="C215" s="7" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="D215" s="5">
         <v>1</v>
@@ -4073,7 +4035,7 @@
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="7" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="D216" s="5">
         <v>1</v>
@@ -4083,7 +4045,7 @@
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="D217" s="5">
         <v>1</v>
@@ -4091,11 +4053,9 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" s="4"/>
-      <c r="B218" s="4" t="s">
-        <v>212</v>
-      </c>
+      <c r="B218" s="4"/>
       <c r="C218" s="7" t="s">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="D218" s="5">
         <v>1</v>
@@ -4105,7 +4065,7 @@
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="7" t="s">
-        <v>186</v>
+        <v>266</v>
       </c>
       <c r="D219" s="5">
         <v>1</v>
@@ -4115,7 +4075,7 @@
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
-        <v>187</v>
+        <v>267</v>
       </c>
       <c r="D220" s="5">
         <v>1</v>
@@ -4125,7 +4085,7 @@
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D221" s="5">
         <v>1</v>
@@ -4133,9 +4093,11 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
-      <c r="B222" s="4"/>
+      <c r="B222" s="4" t="s">
+        <v>214</v>
+      </c>
       <c r="C222" s="7" t="s">
-        <v>262</v>
+        <v>191</v>
       </c>
       <c r="D222" s="5">
         <v>1</v>
@@ -4145,7 +4107,7 @@
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="7" t="s">
-        <v>263</v>
+        <v>192</v>
       </c>
       <c r="D223" s="5">
         <v>1</v>
@@ -4155,7 +4117,7 @@
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="7" t="s">
-        <v>264</v>
+        <v>193</v>
       </c>
       <c r="D224" s="5">
         <v>1</v>
@@ -4163,11 +4125,9 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" s="4"/>
-      <c r="B225" s="4" t="s">
-        <v>213</v>
-      </c>
+      <c r="B225" s="4"/>
       <c r="C225" s="7" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
       <c r="D225" s="5">
         <v>1</v>
@@ -4177,7 +4137,7 @@
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="7" t="s">
-        <v>189</v>
+        <v>270</v>
       </c>
       <c r="D226" s="5">
         <v>1</v>
@@ -4187,7 +4147,7 @@
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="7" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -4197,7 +4157,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="7" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D228" s="5">
         <v>1</v>
@@ -4205,9 +4165,11 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
-      <c r="B229" s="4"/>
+      <c r="B229" s="4" t="s">
+        <v>215</v>
+      </c>
       <c r="C229" s="7" t="s">
-        <v>266</v>
+        <v>194</v>
       </c>
       <c r="D229" s="5">
         <v>1</v>
@@ -4217,7 +4179,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="7" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="D230" s="5">
         <v>1</v>
@@ -4227,7 +4189,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="7" t="s">
-        <v>268</v>
+        <v>196</v>
       </c>
       <c r="D231" s="5">
         <v>1</v>
@@ -4235,11 +4197,9 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" s="4"/>
-      <c r="B232" s="4" t="s">
-        <v>214</v>
-      </c>
+      <c r="B232" s="4"/>
       <c r="C232" s="7" t="s">
-        <v>191</v>
+        <v>273</v>
       </c>
       <c r="D232" s="5">
         <v>1</v>
@@ -4249,7 +4209,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="7" t="s">
-        <v>192</v>
+        <v>274</v>
       </c>
       <c r="D233" s="5">
         <v>1</v>
@@ -4259,7 +4219,7 @@
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="7" t="s">
-        <v>193</v>
+        <v>275</v>
       </c>
       <c r="D234" s="5">
         <v>1</v>
@@ -4269,7 +4229,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="7" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D235" s="5">
         <v>1</v>
@@ -4277,9 +4237,11 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
-      <c r="B236" s="4"/>
+      <c r="B236" s="4" t="s">
+        <v>216</v>
+      </c>
       <c r="C236" s="7" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="D236" s="5">
         <v>1</v>
@@ -4289,7 +4251,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="7" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="D237" s="5">
         <v>1</v>
@@ -4299,7 +4261,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="7" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
       <c r="D238" s="5">
         <v>1</v>
@@ -4307,11 +4269,9 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" s="4"/>
-      <c r="B239" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C239" s="7" t="s">
-        <v>194</v>
+      <c r="B239" s="4"/>
+      <c r="C239" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="D239" s="5">
         <v>1</v>
@@ -4320,8 +4280,8 @@
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
-      <c r="C240" s="7" t="s">
-        <v>195</v>
+      <c r="C240" s="9" t="s">
+        <v>278</v>
       </c>
       <c r="D240" s="5">
         <v>1</v>
@@ -4330,8 +4290,8 @@
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
-      <c r="C241" s="7" t="s">
-        <v>196</v>
+      <c r="C241" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="D241" s="5">
         <v>1</v>
@@ -4340,18 +4300,22 @@
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
-      <c r="C242" s="7" t="s">
-        <v>273</v>
+      <c r="C242" s="9" t="s">
+        <v>280</v>
       </c>
       <c r="D242" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" s="4"/>
-      <c r="B243" s="4"/>
+      <c r="A243" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>419</v>
+      </c>
       <c r="C243" s="7" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D243" s="5">
         <v>1</v>
@@ -4361,7 +4325,7 @@
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D244" s="5">
         <v>1</v>
@@ -4371,7 +4335,7 @@
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="7" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D245" s="5">
         <v>1</v>
@@ -4379,11 +4343,9 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" s="4"/>
-      <c r="B246" s="4" t="s">
-        <v>216</v>
-      </c>
+      <c r="B246" s="4"/>
       <c r="C246" s="7" t="s">
-        <v>197</v>
+        <v>285</v>
       </c>
       <c r="D246" s="5">
         <v>1</v>
@@ -4393,7 +4355,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="7" t="s">
-        <v>198</v>
+        <v>286</v>
       </c>
       <c r="D247" s="5">
         <v>1</v>
@@ -4403,7 +4365,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="7" t="s">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="D248" s="5">
         <v>1</v>
@@ -4412,8 +4374,8 @@
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
-      <c r="C249" s="9" t="s">
-        <v>277</v>
+      <c r="C249" s="7" t="s">
+        <v>288</v>
       </c>
       <c r="D249" s="5">
         <v>1</v>
@@ -4422,8 +4384,8 @@
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
-      <c r="C250" s="9" t="s">
-        <v>278</v>
+      <c r="C250" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="D250" s="5">
         <v>1</v>
@@ -4432,8 +4394,8 @@
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
-      <c r="C251" s="9" t="s">
-        <v>279</v>
+      <c r="C251" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="D251" s="5">
         <v>1</v>
@@ -4442,22 +4404,20 @@
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
-      <c r="C252" s="9" t="s">
-        <v>280</v>
+      <c r="C252" s="7" t="s">
+        <v>415</v>
       </c>
       <c r="D252" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" s="4" t="s">
-        <v>281</v>
-      </c>
+      <c r="A253" s="4"/>
       <c r="B253" s="4" t="s">
-        <v>413</v>
+        <v>123</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D253" s="5">
         <v>1</v>
@@ -4467,7 +4427,7 @@
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D254" s="5">
         <v>1</v>
@@ -4477,7 +4437,7 @@
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="7" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="D255" s="5">
         <v>1</v>
@@ -4487,7 +4447,7 @@
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D256" s="5">
         <v>1</v>
@@ -4497,17 +4457,21 @@
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="7" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D257" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A258" s="4"/>
-      <c r="B258" s="4"/>
+      <c r="A258" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B258" s="4" t="s">
+        <v>296</v>
+      </c>
       <c r="C258" s="7" t="s">
-        <v>456</v>
+        <v>297</v>
       </c>
       <c r="D258" s="5">
         <v>1</v>
@@ -4517,7 +4481,7 @@
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="7" t="s">
-        <v>455</v>
+        <v>298</v>
       </c>
       <c r="D259" s="5">
         <v>1</v>
@@ -4527,7 +4491,7 @@
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="7" t="s">
-        <v>453</v>
+        <v>299</v>
       </c>
       <c r="D260" s="5">
         <v>1</v>
@@ -4537,7 +4501,7 @@
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="7" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="D261" s="5">
         <v>1</v>
@@ -4547,7 +4511,7 @@
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="7" t="s">
-        <v>287</v>
+        <v>438</v>
       </c>
       <c r="D262" s="5">
         <v>1</v>
@@ -4555,9 +4519,11 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
-      <c r="B263" s="4"/>
+      <c r="B263" s="4" t="s">
+        <v>312</v>
+      </c>
       <c r="C263" s="7" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="D263" s="5">
         <v>1</v>
@@ -4567,19 +4533,17 @@
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="7" t="s">
-        <v>409</v>
+        <v>301</v>
       </c>
       <c r="D264" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="4"/>
-      <c r="B265" s="4" t="s">
-        <v>123</v>
-      </c>
+      <c r="B265" s="4"/>
       <c r="C265" s="7" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D265" s="5">
         <v>1</v>
@@ -4589,7 +4553,7 @@
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="7" t="s">
-        <v>290</v>
+        <v>430</v>
       </c>
       <c r="D266" s="5">
         <v>1</v>
@@ -4599,7 +4563,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="7" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="D267" s="5">
         <v>1</v>
@@ -4607,9 +4571,11 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
-      <c r="B268" s="4"/>
+      <c r="B268" s="4" t="s">
+        <v>313</v>
+      </c>
       <c r="C268" s="7" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D268" s="5">
         <v>1</v>
@@ -4619,7 +4585,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="7" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D269" s="5">
         <v>1</v>
@@ -4629,7 +4595,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="7" t="s">
-        <v>446</v>
+        <v>305</v>
       </c>
       <c r="D270" s="5">
         <v>1</v>
@@ -4639,7 +4605,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D271" s="5">
         <v>1</v>
@@ -4649,21 +4615,19 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="7" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D272" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="4" t="s">
-        <v>293</v>
-      </c>
+      <c r="A273" s="4"/>
       <c r="B273" s="4" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D273" s="5">
         <v>1</v>
@@ -4673,7 +4637,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="7" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D274" s="5">
         <v>1</v>
@@ -4683,7 +4647,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="7" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="D275" s="5">
         <v>1</v>
@@ -4693,7 +4657,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="7" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="D276" s="5">
         <v>1</v>
@@ -4701,11 +4665,9 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="4"/>
-      <c r="B277" s="4" t="s">
-        <v>310</v>
-      </c>
+      <c r="B277" s="4"/>
       <c r="C277" s="7" t="s">
-        <v>298</v>
+        <v>434</v>
       </c>
       <c r="D277" s="5">
         <v>1</v>
@@ -4713,9 +4675,11 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
-      <c r="B278" s="4"/>
+      <c r="B278" s="4" t="s">
+        <v>315</v>
+      </c>
       <c r="C278" s="7" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D278" s="5">
         <v>1</v>
@@ -4725,7 +4689,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="7" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D279" s="5">
         <v>1</v>
@@ -4735,7 +4699,7 @@
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="7" t="s">
-        <v>429</v>
+        <v>311</v>
       </c>
       <c r="D280" s="5">
         <v>1</v>
@@ -4743,11 +4707,9 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="4"/>
-      <c r="B281" s="4" t="s">
-        <v>311</v>
-      </c>
+      <c r="B281" s="4"/>
       <c r="C281" s="7" t="s">
-        <v>301</v>
+        <v>432</v>
       </c>
       <c r="D281" s="5">
         <v>1</v>
@@ -4757,7 +4719,7 @@
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="7" t="s">
-        <v>302</v>
+        <v>433</v>
       </c>
       <c r="D282" s="5">
         <v>1</v>
@@ -4765,9 +4727,11 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
-      <c r="B283" s="4"/>
+      <c r="B283" s="4" t="s">
+        <v>318</v>
+      </c>
       <c r="C283" s="7" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="D283" s="5">
         <v>1</v>
@@ -4777,19 +4741,19 @@
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="7" t="s">
-        <v>430</v>
+        <v>317</v>
       </c>
       <c r="D284" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A285" s="4"/>
-      <c r="B285" s="4" t="s">
-        <v>312</v>
-      </c>
+      <c r="A285" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B285" s="4"/>
       <c r="C285" s="7" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="D285" s="5">
         <v>1</v>
@@ -4799,7 +4763,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="7" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="D286" s="5">
         <v>1</v>
@@ -4808,30 +4772,32 @@
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
-      <c r="C287" s="7" t="s">
-        <v>306</v>
+      <c r="C287" s="9" t="s">
+        <v>322</v>
       </c>
       <c r="D287" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="7" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="D288" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A289" s="4"/>
+      <c r="A289" s="4" t="s">
+        <v>416</v>
+      </c>
       <c r="B289" s="4" t="s">
-        <v>313</v>
+        <v>420</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="D289" s="5">
         <v>1</v>
@@ -4841,7 +4807,7 @@
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="7" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="D290" s="5">
         <v>1</v>
@@ -4851,7 +4817,7 @@
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="7" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D291" s="5">
         <v>1</v>
@@ -4861,7 +4827,7 @@
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="7" t="s">
-        <v>432</v>
+        <v>326</v>
       </c>
       <c r="D292" s="5">
         <v>1</v>
@@ -4869,11 +4835,9 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="4"/>
-      <c r="B293" s="4" t="s">
-        <v>316</v>
-      </c>
+      <c r="B293" s="4"/>
       <c r="C293" s="7" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="D293" s="5">
         <v>1</v>
@@ -4883,19 +4847,17 @@
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="7" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="D294" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A295" s="4" t="s">
-        <v>317</v>
-      </c>
+      <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="7" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -4905,7 +4867,7 @@
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="7" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D296" s="5">
         <v>1</v>
@@ -4914,32 +4876,30 @@
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
-      <c r="C297" s="9" t="s">
-        <v>320</v>
+      <c r="C297" s="7" t="s">
+        <v>331</v>
       </c>
       <c r="D297" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
-      <c r="B298" s="4"/>
+      <c r="B298" s="4" t="s">
+        <v>370</v>
+      </c>
       <c r="C298" s="7" t="s">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="D298" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A299" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>414</v>
-      </c>
+      <c r="A299" s="4"/>
+      <c r="B299" s="4"/>
       <c r="C299" s="7" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="D299" s="5">
         <v>1</v>
@@ -4949,7 +4909,7 @@
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="7" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D300" s="5">
         <v>1</v>
@@ -4959,7 +4919,7 @@
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="7" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="D301" s="5">
         <v>1</v>
@@ -4969,7 +4929,7 @@
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="7" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D302" s="5">
         <v>1</v>
@@ -4979,7 +4939,7 @@
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="7" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D303" s="5">
         <v>1</v>
@@ -4989,7 +4949,7 @@
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="7" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D304" s="5">
         <v>1</v>
@@ -4999,7 +4959,7 @@
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="7" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="D305" s="5">
         <v>1</v>
@@ -5009,7 +4969,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="7" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D306" s="5">
         <v>1</v>
@@ -5019,7 +4979,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="7" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="D307" s="5">
         <v>1</v>
@@ -5029,7 +4989,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="7" t="s">
-        <v>447</v>
+        <v>342</v>
       </c>
       <c r="D308" s="5">
         <v>1</v>
@@ -5039,7 +4999,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="7" t="s">
-        <v>448</v>
+        <v>343</v>
       </c>
       <c r="D309" s="5">
         <v>1</v>
@@ -5049,7 +5009,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="7" t="s">
-        <v>449</v>
+        <v>344</v>
       </c>
       <c r="D310" s="5">
         <v>1</v>
@@ -5057,11 +5017,9 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" s="4"/>
-      <c r="B311" s="4" t="s">
-        <v>368</v>
-      </c>
+      <c r="B311" s="4"/>
       <c r="C311" s="7" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="D311" s="5">
         <v>1</v>
@@ -5071,7 +5029,7 @@
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="7" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="D312" s="5">
         <v>1</v>
@@ -5081,7 +5039,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="7" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="D313" s="5">
         <v>1</v>
@@ -5091,7 +5049,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="7" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="D314" s="5">
         <v>1</v>
@@ -5101,7 +5059,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="7" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D315" s="5">
         <v>1</v>
@@ -5111,7 +5069,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="7" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="D316" s="5">
         <v>1</v>
@@ -5121,7 +5079,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="7" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D317" s="5">
         <v>1</v>
@@ -5131,7 +5089,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="7" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="D318" s="5">
         <v>1</v>
@@ -5141,7 +5099,7 @@
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="7" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="D319" s="5">
         <v>1</v>
@@ -5151,7 +5109,7 @@
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="7" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="D320" s="5">
         <v>1</v>
@@ -5161,17 +5119,21 @@
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="7" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="D321" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A322" s="4"/>
-      <c r="B322" s="4"/>
+      <c r="A322" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>421</v>
+      </c>
       <c r="C322" s="7" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="D322" s="5">
         <v>1</v>
@@ -5181,7 +5143,7 @@
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="7" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D323" s="5">
         <v>1</v>
@@ -5191,7 +5153,7 @@
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="7" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="D324" s="5">
         <v>1</v>
@@ -5201,7 +5163,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="7" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="D325" s="5">
         <v>1</v>
@@ -5211,7 +5173,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="7" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="D326" s="5">
         <v>1</v>
@@ -5221,7 +5183,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="7" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D327" s="5">
         <v>1</v>
@@ -5231,7 +5193,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="7" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="D328" s="5">
         <v>1</v>
@@ -5241,7 +5203,7 @@
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="7" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="D329" s="5">
         <v>1</v>
@@ -5251,7 +5213,7 @@
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="7" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="D330" s="5">
         <v>1</v>
@@ -5261,7 +5223,7 @@
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D331" s="5">
         <v>1</v>
@@ -5271,7 +5233,7 @@
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D332" s="5">
         <v>1</v>
@@ -5281,7 +5243,7 @@
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D333" s="5">
         <v>1</v>
@@ -5289,23 +5251,21 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
-      <c r="B334" s="4"/>
+      <c r="B334" s="4" t="s">
+        <v>371</v>
+      </c>
       <c r="C334" s="7" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D334" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A335" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>415</v>
-      </c>
+      <c r="A335" s="4"/>
+      <c r="B335" s="4"/>
       <c r="C335" s="7" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="D335" s="5">
         <v>1</v>
@@ -5315,7 +5275,7 @@
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="7" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="D336" s="5">
         <v>1</v>
@@ -5325,7 +5285,7 @@
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="7" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="D337" s="5">
         <v>1</v>
@@ -5335,7 +5295,7 @@
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="7" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D338" s="5">
         <v>1</v>
@@ -5345,7 +5305,7 @@
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="7" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="D339" s="5">
         <v>1</v>
@@ -5355,7 +5315,7 @@
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="7" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="D340" s="5">
         <v>1</v>
@@ -5365,7 +5325,7 @@
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="7" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="D341" s="5">
         <v>1</v>
@@ -5375,7 +5335,7 @@
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="7" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="D342" s="5">
         <v>1</v>
@@ -5385,7 +5345,7 @@
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="7" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="D343" s="5">
         <v>1</v>
@@ -5395,7 +5355,7 @@
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="7" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="D344" s="5">
         <v>1</v>
@@ -5405,17 +5365,21 @@
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="7" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="D345" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A346" s="4"/>
-      <c r="B346" s="4"/>
+      <c r="A346" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>422</v>
+      </c>
       <c r="C346" s="7" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="D346" s="5">
         <v>1</v>
@@ -5423,11 +5387,9 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" s="4"/>
-      <c r="B347" s="4" t="s">
-        <v>369</v>
-      </c>
+      <c r="B347" s="4"/>
       <c r="C347" s="7" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="D347" s="5">
         <v>1</v>
@@ -5437,7 +5399,7 @@
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="7" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="D348" s="5">
         <v>1</v>
@@ -5447,7 +5409,7 @@
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="7" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="D349" s="5">
         <v>1</v>
@@ -5457,7 +5419,7 @@
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="7" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="D350" s="5">
         <v>1</v>
@@ -5467,7 +5429,7 @@
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="7" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="D351" s="5">
         <v>1</v>
@@ -5477,7 +5439,7 @@
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="7" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="D352" s="5">
         <v>1</v>
@@ -5487,7 +5449,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="7" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="D353" s="5">
         <v>1</v>
@@ -5495,9 +5457,11 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
-      <c r="B354" s="4"/>
+      <c r="B354" s="4" t="s">
+        <v>393</v>
+      </c>
       <c r="C354" s="7" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="D354" s="5">
         <v>1</v>
@@ -5507,7 +5471,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="7" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="D355" s="5">
         <v>1</v>
@@ -5517,7 +5481,7 @@
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="7" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="D356" s="5">
         <v>1</v>
@@ -5527,7 +5491,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="7" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="D357" s="5">
         <v>1</v>
@@ -5537,21 +5501,17 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="7" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="D358" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A359" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B359" s="4" t="s">
-        <v>416</v>
-      </c>
+      <c r="A359" s="4"/>
+      <c r="B359" s="4"/>
       <c r="C359" s="7" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="D359" s="5">
         <v>1</v>
@@ -5561,7 +5521,7 @@
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="7" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="D360" s="5">
         <v>1</v>
@@ -5571,17 +5531,19 @@
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="7" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="D361" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A362" s="4"/>
+      <c r="A362" s="4" t="s">
+        <v>398</v>
+      </c>
       <c r="B362" s="4"/>
       <c r="C362" s="7" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="D362" s="5">
         <v>1</v>
@@ -5591,7 +5553,7 @@
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="7" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D363" s="5">
         <v>1</v>
@@ -5601,7 +5563,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="7" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="D364" s="5">
         <v>1</v>
@@ -5611,7 +5573,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="7" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="D365" s="5">
         <v>1</v>
@@ -5621,7 +5583,7 @@
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="7" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="D366" s="5">
         <v>1</v>
@@ -5629,21 +5591,21 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A367" s="4"/>
-      <c r="B367" s="4" t="s">
-        <v>391</v>
-      </c>
+      <c r="B367" s="4"/>
       <c r="C367" s="7" t="s">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="D367" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A368" s="4"/>
+      <c r="A368" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="B368" s="4"/>
       <c r="C368" s="7" t="s">
-        <v>451</v>
+        <v>136</v>
       </c>
       <c r="D368" s="5">
         <v>1</v>
@@ -5653,7 +5615,7 @@
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="7" t="s">
-        <v>392</v>
+        <v>137</v>
       </c>
       <c r="D369" s="5">
         <v>1</v>
@@ -5663,7 +5625,7 @@
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="7" t="s">
-        <v>393</v>
+        <v>138</v>
       </c>
       <c r="D370" s="5">
         <v>1</v>
@@ -5673,7 +5635,7 @@
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="7" t="s">
-        <v>420</v>
+        <v>139</v>
       </c>
       <c r="D371" s="5">
         <v>1</v>
@@ -5682,126 +5644,74 @@
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="4"/>
       <c r="B372" s="4"/>
-      <c r="C372" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="D372" s="5">
-        <v>1</v>
-      </c>
+      <c r="C372" s="9"/>
+      <c r="D372" s="5"/>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" s="4"/>
       <c r="B373" s="4"/>
-      <c r="C373" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="D373" s="5">
-        <v>1</v>
-      </c>
+      <c r="C373" s="9"/>
+      <c r="D373" s="5"/>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A374" s="4" t="s">
-        <v>394</v>
-      </c>
+      <c r="A374" s="4"/>
       <c r="B374" s="4"/>
-      <c r="C374" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D374" s="5">
-        <v>1</v>
-      </c>
+      <c r="C374" s="9"/>
+      <c r="D374" s="5"/>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" s="4"/>
       <c r="B375" s="4"/>
-      <c r="C375" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="D375" s="5">
-        <v>1</v>
-      </c>
+      <c r="C375" s="9"/>
+      <c r="D375" s="5"/>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
-      <c r="C376" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="D376" s="5">
-        <v>1</v>
-      </c>
+      <c r="C376" s="9"/>
+      <c r="D376" s="5"/>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
-      <c r="C377" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D377" s="5">
-        <v>1</v>
-      </c>
+      <c r="C377" s="9"/>
+      <c r="D377" s="5"/>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" s="4"/>
       <c r="B378" s="4"/>
-      <c r="C378" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="D378" s="5">
-        <v>1</v>
-      </c>
+      <c r="C378" s="9"/>
+      <c r="D378" s="5"/>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
-      <c r="C379" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="D379" s="5">
-        <v>1</v>
-      </c>
+      <c r="C379" s="9"/>
+      <c r="D379" s="5"/>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A380" s="4" t="s">
-        <v>135</v>
-      </c>
+      <c r="A380" s="4"/>
       <c r="B380" s="4"/>
-      <c r="C380" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D380" s="5">
-        <v>1</v>
-      </c>
+      <c r="C380" s="9"/>
+      <c r="D380" s="5"/>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" s="4"/>
       <c r="B381" s="4"/>
-      <c r="C381" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D381" s="5">
-        <v>1</v>
-      </c>
+      <c r="C381" s="9"/>
+      <c r="D381" s="5"/>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" s="4"/>
       <c r="B382" s="4"/>
-      <c r="C382" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D382" s="5">
-        <v>1</v>
-      </c>
+      <c r="C382" s="9"/>
+      <c r="D382" s="5"/>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" s="4"/>
       <c r="B383" s="4"/>
-      <c r="C383" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D383" s="5">
-        <v>1</v>
-      </c>
+      <c r="C383" s="9"/>
+      <c r="D383" s="5"/>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" s="4"/>
@@ -5871,7 +5781,7 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="4"/>
-      <c r="B395" s="4"/>
+      <c r="B395" s="7"/>
       <c r="C395" s="9"/>
       <c r="D395" s="5"/>
     </row>
@@ -5890,146 +5800,74 @@
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" s="4"/>
       <c r="B398" s="4"/>
-      <c r="C398" s="9"/>
+      <c r="C398" s="7"/>
       <c r="D398" s="5"/>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" s="4"/>
       <c r="B399" s="4"/>
-      <c r="C399" s="9"/>
+      <c r="C399" s="7"/>
       <c r="D399" s="5"/>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" s="4"/>
       <c r="B400" s="4"/>
-      <c r="C400" s="9"/>
+      <c r="C400" s="7"/>
       <c r="D400" s="5"/>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
-      <c r="C401" s="9"/>
+      <c r="C401" s="7"/>
       <c r="D401" s="5"/>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" s="4"/>
       <c r="B402" s="4"/>
-      <c r="C402" s="9"/>
+      <c r="C402" s="4"/>
       <c r="D402" s="5"/>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" s="4"/>
       <c r="B403" s="4"/>
-      <c r="C403" s="9"/>
+      <c r="C403" s="4"/>
       <c r="D403" s="5"/>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" s="4"/>
       <c r="B404" s="4"/>
-      <c r="C404" s="9"/>
+      <c r="C404" s="4"/>
       <c r="D404" s="5"/>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" s="4"/>
       <c r="B405" s="4"/>
-      <c r="C405" s="9"/>
+      <c r="C405" s="4"/>
       <c r="D405" s="5"/>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" s="4"/>
       <c r="B406" s="4"/>
-      <c r="C406" s="9"/>
+      <c r="C406" s="4"/>
       <c r="D406" s="5"/>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" s="4"/>
-      <c r="B407" s="7"/>
-      <c r="C407" s="9"/>
+      <c r="B407" s="4"/>
+      <c r="C407" s="4"/>
       <c r="D407" s="5"/>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" s="4"/>
       <c r="B408" s="4"/>
-      <c r="C408" s="9"/>
+      <c r="C408" s="4"/>
       <c r="D408" s="5"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
-      <c r="C409" s="9"/>
+      <c r="C409" s="4"/>
       <c r="D409" s="5"/>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A410" s="4"/>
-      <c r="B410" s="4"/>
-      <c r="C410" s="7"/>
-      <c r="D410" s="5"/>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A411" s="4"/>
-      <c r="B411" s="4"/>
-      <c r="C411" s="7"/>
-      <c r="D411" s="5"/>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A412" s="4"/>
-      <c r="B412" s="4"/>
-      <c r="C412" s="7"/>
-      <c r="D412" s="5"/>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A413" s="4"/>
-      <c r="B413" s="4"/>
-      <c r="C413" s="7"/>
-      <c r="D413" s="5"/>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A414" s="4"/>
-      <c r="B414" s="4"/>
-      <c r="C414" s="4"/>
-      <c r="D414" s="5"/>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A415" s="4"/>
-      <c r="B415" s="4"/>
-      <c r="C415" s="4"/>
-      <c r="D415" s="5"/>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A416" s="4"/>
-      <c r="B416" s="4"/>
-      <c r="C416" s="4"/>
-      <c r="D416" s="5"/>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A417" s="4"/>
-      <c r="B417" s="4"/>
-      <c r="C417" s="4"/>
-      <c r="D417" s="5"/>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A418" s="4"/>
-      <c r="B418" s="4"/>
-      <c r="C418" s="4"/>
-      <c r="D418" s="5"/>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A419" s="4"/>
-      <c r="B419" s="4"/>
-      <c r="C419" s="4"/>
-      <c r="D419" s="5"/>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A420" s="4"/>
-      <c r="B420" s="4"/>
-      <c r="C420" s="4"/>
-      <c r="D420" s="5"/>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A421" s="4"/>
-      <c r="B421" s="4"/>
-      <c r="C421" s="4"/>
-      <c r="D421" s="5"/>
     </row>
   </sheetData>
   <protectedRanges>

--- a/assets/templates.xlsx
+++ b/assets/templates.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Claude\Claude Code\Auftragsdoku FlexPos NFK + BBA\_deploy\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0E2A6C-6219-4430-8898-F0552E6B10FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E5F2D2-40DC-489E-A4A3-7A0000027D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25905" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NFK Vollverkabelung" sheetId="1" r:id="rId1"/>
@@ -35,1321 +35,1321 @@
     <t>Pflichtanzahl</t>
   </si>
   <si>
+    <t>01_Maengel</t>
+  </si>
+  <si>
+    <t>Maengel_vorher</t>
+  </si>
+  <si>
+    <t>Maengel_behoben</t>
+  </si>
+  <si>
+    <t>02_Abnahme</t>
+  </si>
+  <si>
+    <t>Abnahme_Unterschrift</t>
+  </si>
+  <si>
+    <t>Kasse 1</t>
+  </si>
+  <si>
+    <t>Kasse 1 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 1 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 1 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 2 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 2 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 2 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 2</t>
+  </si>
+  <si>
+    <t>Kasse 3 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 3 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 3 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 4 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 4 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 4 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 5 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 5 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 5 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 6 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 6 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 6 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 7 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 7 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 7 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 8 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 8 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 8 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 9 Beschriftung Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 9 Sammelpunkt</t>
+  </si>
+  <si>
+    <t>Kasse 9 Kabelweg in der Kasse</t>
+  </si>
+  <si>
+    <t>Kasse 3</t>
+  </si>
+  <si>
+    <t>Kasse 4</t>
+  </si>
+  <si>
+    <t>Kasse 5</t>
+  </si>
+  <si>
+    <t>Kasse 6</t>
+  </si>
+  <si>
+    <t>Kasse 7</t>
+  </si>
+  <si>
+    <t>Kasse 8</t>
+  </si>
+  <si>
+    <t>Kasse 9</t>
+  </si>
+  <si>
+    <t>SCO Kasse 1</t>
+  </si>
+  <si>
+    <t>SCO 81 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 81 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 82 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 82 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 83 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 83 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 84 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 84 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 85 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 85 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 86 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 86 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 87 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 87 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO 88 Module im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO 88 Kabelreserve</t>
+  </si>
+  <si>
+    <t>SCO Kasse 2</t>
+  </si>
+  <si>
+    <t>SCO Kasse 3</t>
+  </si>
+  <si>
+    <t>SCO Kasse 4</t>
+  </si>
+  <si>
+    <t>SCO Kasse 5</t>
+  </si>
+  <si>
+    <t>SCO Kasse 6</t>
+  </si>
+  <si>
+    <t>SCO Kasse 7</t>
+  </si>
+  <si>
+    <t>SCO Kasse 8</t>
+  </si>
+  <si>
+    <t>SCO Kasse 9</t>
+  </si>
+  <si>
+    <t>SCO Service Kasse</t>
+  </si>
+  <si>
+    <t>SCO Service Kasse Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO Service Kasse Terminal Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO Service Kasse reserve Port Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>SCO Service Kasse Reserve</t>
+  </si>
+  <si>
+    <t>Kassen Totale</t>
+  </si>
+  <si>
+    <t>CCTV 1 Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>CCTV 2 Modul im Kassentisch</t>
+  </si>
+  <si>
+    <t>Exit Gate Modul</t>
+  </si>
+  <si>
+    <t>Blitzleuchte Klemmen</t>
+  </si>
+  <si>
+    <t>Blitzleuchte Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 2 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 2 Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 3 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 3 Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 4 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 4 Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 5 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 5 Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 6 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 6 Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage</t>
+  </si>
+  <si>
+    <t>02_Pfandraum</t>
+  </si>
+  <si>
+    <t>Pfand 1 Dose</t>
+  </si>
+  <si>
+    <t>Pfand 2 Dose</t>
+  </si>
+  <si>
+    <t>Pfand 3 Dose</t>
+  </si>
+  <si>
+    <t>Pfand Reserve Dose</t>
+  </si>
+  <si>
+    <t>Pfand gesamt Totale</t>
+  </si>
+  <si>
+    <t>Digital Signage 1 Dose</t>
+  </si>
+  <si>
+    <t>Digital Signage 1 Totale</t>
+  </si>
+  <si>
+    <t>03_Backnische</t>
+  </si>
+  <si>
+    <t>BA 01 + 02 Dose</t>
+  </si>
+  <si>
+    <t>BA 01 + 02 Totale</t>
+  </si>
+  <si>
+    <t>BA 03 + 04 Dose</t>
+  </si>
+  <si>
+    <t>BA 03 + 04 Totale</t>
+  </si>
+  <si>
+    <t>BA 05 + 06 Dose</t>
+  </si>
+  <si>
+    <t>BA 05 + 06 Totale</t>
+  </si>
+  <si>
+    <t>BA Totale</t>
+  </si>
+  <si>
+    <t>BakeOff 1 + BakeOff 2 Dose</t>
+  </si>
+  <si>
+    <t>BakeOff 1 + BakeOff2 Totale</t>
+  </si>
+  <si>
+    <t>04_Aktenraum</t>
+  </si>
+  <si>
+    <t>Thin Client + Res</t>
+  </si>
+  <si>
+    <t>Drucker + FAX</t>
+  </si>
+  <si>
+    <t>TEL + Res</t>
+  </si>
+  <si>
+    <t>Aktenraum Totale</t>
+  </si>
+  <si>
+    <t>Cashmaschine</t>
+  </si>
+  <si>
+    <t>Cashmaschine Totale</t>
+  </si>
+  <si>
+    <t>Kleinverteiler Ports</t>
+  </si>
+  <si>
+    <t>Kleinverteiler offen</t>
+  </si>
+  <si>
+    <t>Kleinverteiler Totale</t>
+  </si>
+  <si>
+    <t>Kabelcodierung Aktenraum</t>
+  </si>
+  <si>
+    <t>Geldwage</t>
+  </si>
+  <si>
+    <t>Serien-/LIN-Nummern</t>
+  </si>
+  <si>
+    <t>ELO</t>
+  </si>
+  <si>
+    <t>SN ELO</t>
+  </si>
+  <si>
+    <t>LIN ELO</t>
+  </si>
+  <si>
+    <t>SN Geldwage</t>
+  </si>
+  <si>
+    <t>LIN Geldwage</t>
+  </si>
+  <si>
+    <t>SN Drucker</t>
+  </si>
+  <si>
+    <t>Nachweis</t>
+  </si>
+  <si>
+    <t>Anmeldemaske BO</t>
+  </si>
+  <si>
+    <t>PZE online</t>
+  </si>
+  <si>
+    <t>KWLAN</t>
+  </si>
+  <si>
+    <t>Registrierung Vocovo Telefone</t>
+  </si>
+  <si>
+    <t>FTTH</t>
+  </si>
+  <si>
+    <t>FTTH Anschluß Dose</t>
+  </si>
+  <si>
+    <t>FTTH Anschluß Totale</t>
+  </si>
+  <si>
+    <t>FTTH Modem</t>
+  </si>
+  <si>
+    <t>FTTH Modem Totale</t>
+  </si>
+  <si>
+    <t>05_Filiallager</t>
+  </si>
+  <si>
+    <t>1. Lager + 2. Lager</t>
+  </si>
+  <si>
+    <t>1. Lager + 2. Lager Totale</t>
+  </si>
+  <si>
+    <t>3. Lager + 4. Lager</t>
+  </si>
+  <si>
+    <t>3. Lager + 4. Lager Totale</t>
+  </si>
+  <si>
+    <t>Xweb Dose</t>
+  </si>
+  <si>
+    <t>Xweb Totale</t>
+  </si>
+  <si>
+    <t>06_Technikebene</t>
+  </si>
+  <si>
+    <t>L-Box Dose</t>
+  </si>
+  <si>
+    <t>L-Box Totale</t>
+  </si>
+  <si>
+    <t>Integral / Wago Dose</t>
+  </si>
+  <si>
+    <t>Integral / Wago Totale</t>
+  </si>
+  <si>
+    <t>AP1 Dose</t>
+  </si>
+  <si>
+    <t>AP1 Totale</t>
+  </si>
+  <si>
+    <t>AP1 Brandschott</t>
+  </si>
+  <si>
+    <t>AP2 Dose</t>
+  </si>
+  <si>
+    <t>AP2 Totale</t>
+  </si>
+  <si>
+    <t>AP2 Brandschott</t>
+  </si>
+  <si>
+    <t>AP3 Dose</t>
+  </si>
+  <si>
+    <t>AP3 Totale</t>
+  </si>
+  <si>
+    <t>AP3 Brandschott</t>
+  </si>
+  <si>
+    <t>AP4 Dose</t>
+  </si>
+  <si>
+    <t>AP4 Totale</t>
+  </si>
+  <si>
+    <t>AP4 Brandschott</t>
+  </si>
+  <si>
+    <t>AP5 Dose</t>
+  </si>
+  <si>
+    <t>AP5 Totale</t>
+  </si>
+  <si>
+    <t>AP5 Brandschott</t>
+  </si>
+  <si>
+    <t>AP6 Dose</t>
+  </si>
+  <si>
+    <t>AP6 Totale</t>
+  </si>
+  <si>
+    <t>AP6 Brandschott</t>
+  </si>
+  <si>
+    <t>AP7 Dose</t>
+  </si>
+  <si>
+    <t>AP7 Totale</t>
+  </si>
+  <si>
+    <t>AP7 Brandschott</t>
+  </si>
+  <si>
+    <t>AP8 Dose</t>
+  </si>
+  <si>
+    <t>AP8 Totale</t>
+  </si>
+  <si>
+    <t>AP8 Brandschott</t>
+  </si>
+  <si>
+    <t>AP9 Dose</t>
+  </si>
+  <si>
+    <t>AP9 Totale</t>
+  </si>
+  <si>
+    <t>AP9 Brandschott</t>
+  </si>
+  <si>
+    <t>AP10 Dose</t>
+  </si>
+  <si>
+    <t>AP10 Totale</t>
+  </si>
+  <si>
+    <t>AP10 Brandschott</t>
+  </si>
+  <si>
+    <t>AP11 Dose</t>
+  </si>
+  <si>
+    <t>AP11 Totale</t>
+  </si>
+  <si>
+    <t>AP11 Brandschott</t>
+  </si>
+  <si>
+    <t>AP12 Dose</t>
+  </si>
+  <si>
+    <t>AP12 Totale</t>
+  </si>
+  <si>
+    <t>AP12 Brandschott</t>
+  </si>
+  <si>
+    <t>AP13 Dose</t>
+  </si>
+  <si>
+    <t>AP13 Totale</t>
+  </si>
+  <si>
+    <t>AP13 Brandschott</t>
+  </si>
+  <si>
+    <t>AP14 Dose</t>
+  </si>
+  <si>
+    <t>AP14 Totale</t>
+  </si>
+  <si>
+    <t>AP14 Brandschott</t>
+  </si>
+  <si>
+    <t>AP15 Dose</t>
+  </si>
+  <si>
+    <t>AP15 Totale</t>
+  </si>
+  <si>
+    <t>AP15 Brandschott</t>
+  </si>
+  <si>
+    <t>AP16 Dose</t>
+  </si>
+  <si>
+    <t>AP16 Totale</t>
+  </si>
+  <si>
+    <t>AP16 Brandschott</t>
+  </si>
+  <si>
+    <t>07_Accesspoints</t>
+  </si>
+  <si>
+    <t>AP1</t>
+  </si>
+  <si>
+    <t>AP2</t>
+  </si>
+  <si>
+    <t>AP3</t>
+  </si>
+  <si>
+    <t>AP4</t>
+  </si>
+  <si>
+    <t>AP5</t>
+  </si>
+  <si>
+    <t>AP6</t>
+  </si>
+  <si>
+    <t>AP7</t>
+  </si>
+  <si>
+    <t>AP8</t>
+  </si>
+  <si>
+    <t>AP9</t>
+  </si>
+  <si>
+    <t>AP10</t>
+  </si>
+  <si>
+    <t>AP11</t>
+  </si>
+  <si>
+    <t>AP12</t>
+  </si>
+  <si>
+    <t>AP13</t>
+  </si>
+  <si>
+    <t>AP14</t>
+  </si>
+  <si>
+    <t>AP15</t>
+  </si>
+  <si>
+    <t>AP16</t>
+  </si>
+  <si>
+    <t>SN AP1</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP1</t>
+  </si>
+  <si>
+    <t>LIN AP1</t>
+  </si>
+  <si>
+    <t>IoT AP1</t>
+  </si>
+  <si>
+    <t>SN AP2</t>
+  </si>
+  <si>
+    <t>LIN AP2</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP2</t>
+  </si>
+  <si>
+    <t>IoT AP2</t>
+  </si>
+  <si>
+    <t>SN AP3</t>
+  </si>
+  <si>
+    <t>LIN AP3</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP3</t>
+  </si>
+  <si>
+    <t>IoT AP3</t>
+  </si>
+  <si>
+    <t>SN AP4</t>
+  </si>
+  <si>
+    <t>LIN AP4</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP4</t>
+  </si>
+  <si>
+    <t>IoT AP4</t>
+  </si>
+  <si>
+    <t>SN AP5</t>
+  </si>
+  <si>
+    <t>LIN AP5</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP5</t>
+  </si>
+  <si>
+    <t>IoT AP5</t>
+  </si>
+  <si>
+    <t>SN AP6</t>
+  </si>
+  <si>
+    <t>LIN AP6</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP6</t>
+  </si>
+  <si>
+    <t>IoT AP6</t>
+  </si>
+  <si>
+    <t>SN AP7</t>
+  </si>
+  <si>
+    <t>LIN AP7</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP7</t>
+  </si>
+  <si>
+    <t>IoT AP7</t>
+  </si>
+  <si>
+    <t>SN AP8</t>
+  </si>
+  <si>
+    <t>LIN AP8</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP8</t>
+  </si>
+  <si>
+    <t>IoT AP8</t>
+  </si>
+  <si>
+    <t>SN AP9</t>
+  </si>
+  <si>
+    <t>LIN AP9</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP9</t>
+  </si>
+  <si>
+    <t>IoT AP9</t>
+  </si>
+  <si>
+    <t>SN AP10</t>
+  </si>
+  <si>
+    <t>LIN AP10</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP10</t>
+  </si>
+  <si>
+    <t>IoT AP10</t>
+  </si>
+  <si>
+    <t>SN AP11</t>
+  </si>
+  <si>
+    <t>LIN AP11</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP11</t>
+  </si>
+  <si>
+    <t>IoT AP11</t>
+  </si>
+  <si>
+    <t>SN AP12</t>
+  </si>
+  <si>
+    <t>LIN AP12</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP12</t>
+  </si>
+  <si>
+    <t>IoT AP12</t>
+  </si>
+  <si>
+    <t>SN AP13</t>
+  </si>
+  <si>
+    <t>LIN AP13</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP13</t>
+  </si>
+  <si>
+    <t>IoT AP13</t>
+  </si>
+  <si>
+    <t>SN AP14</t>
+  </si>
+  <si>
+    <t>LIN AP14</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP14</t>
+  </si>
+  <si>
+    <t>IoT AP14</t>
+  </si>
+  <si>
+    <t>SN AP15</t>
+  </si>
+  <si>
+    <t>LIN AP15</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP15</t>
+  </si>
+  <si>
+    <t>IoT AP15</t>
+  </si>
+  <si>
+    <t>SN AP16</t>
+  </si>
+  <si>
+    <t>LIN AP16</t>
+  </si>
+  <si>
+    <t>Beschriftung SN + MAC AP16</t>
+  </si>
+  <si>
+    <t>IoT AP16</t>
+  </si>
+  <si>
+    <t>08_Sozialräume</t>
+  </si>
+  <si>
+    <t>Lili Dose</t>
+  </si>
+  <si>
+    <t>Lili Totale</t>
+  </si>
+  <si>
+    <t>PZE Dose</t>
+  </si>
+  <si>
+    <t>PZE Totale</t>
+  </si>
+  <si>
+    <t>PZE gesamt</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2 Dose</t>
+  </si>
+  <si>
+    <t>Perso 1 + Perso 2Totale</t>
+  </si>
+  <si>
+    <t>Headset Strom</t>
+  </si>
+  <si>
+    <t>Headset Totale</t>
+  </si>
+  <si>
+    <t>SN MAT</t>
+  </si>
+  <si>
+    <t>LIN MAT</t>
+  </si>
+  <si>
+    <t>LIN PZE</t>
+  </si>
+  <si>
+    <t>SN Headsets</t>
+  </si>
+  <si>
+    <t>09_Vocovo</t>
+  </si>
+  <si>
+    <t>Vocovo 1</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 1 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 2 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 3 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 4 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Dose</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Totale</t>
+  </si>
+  <si>
+    <t>Vocovo 5 Brandschott</t>
+  </si>
+  <si>
+    <t>Vocovo 2</t>
+  </si>
+  <si>
+    <t>Vocovo 3</t>
+  </si>
+  <si>
+    <t>Vocovo 4</t>
+  </si>
+  <si>
+    <t>Vocovo 5</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal Headsets Modul</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal Headsets Totale</t>
+  </si>
+  <si>
+    <t>Vocovo BR Kanal</t>
+  </si>
+  <si>
+    <t>10_Serverraum</t>
+  </si>
+  <si>
+    <t>Netzwerkschränke Vorderseite</t>
+  </si>
+  <si>
+    <t>Netzwerkschränke Rückseite</t>
+  </si>
+  <si>
+    <t>Kabelverlegung Serverraum</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail mitte Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 1 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 1 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 1 Erdung</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 1</t>
+  </si>
+  <si>
+    <t>SN Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>LIN Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>Beschriftung Cisco 01_Router_VPN11_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>SN Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>LIN Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>Beschriftung Cisco 02_Router_VPN12_(C1111-8P)</t>
+  </si>
+  <si>
+    <t>SN Huawei S5735-12P WAN-Switche 1</t>
+  </si>
+  <si>
+    <t>LIN + Beschr Huawei S5735-12P WAN-Switche 1</t>
+  </si>
+  <si>
+    <t>SN Huawei S5735-12P WAN-Switche 2</t>
+  </si>
+  <si>
+    <t>LIN + Besch Huawei S5735-12P WAN-Switche 2</t>
+  </si>
+  <si>
+    <t>SN Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>LIN Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
+  </si>
+  <si>
+    <t>SN Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>LIN Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
+  </si>
+  <si>
+    <t>SN Server</t>
+  </si>
+  <si>
+    <t>LIN Server</t>
+  </si>
+  <si>
+    <t>SN PZE</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 2</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail mitte Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 2 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 2 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 2 Erdung</t>
+  </si>
+  <si>
+    <t>Switch 1 gepatcht</t>
+  </si>
+  <si>
+    <t>Switch 2 gepatcht</t>
+  </si>
+  <si>
+    <t>Switch 3 gepatcht</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 2</t>
+  </si>
+  <si>
+    <t>SN Frederix</t>
+  </si>
+  <si>
+    <t>LIN Frederix</t>
+  </si>
+  <si>
+    <t>SN Baracuda</t>
+  </si>
+  <si>
+    <t>LIN Baracuda</t>
+  </si>
+  <si>
+    <t>NWS 1 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>NWS 2 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>SN Switch 1</t>
+  </si>
+  <si>
+    <t>LIN Switch 1</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 1</t>
+  </si>
+  <si>
+    <t>SN Switch 2</t>
+  </si>
+  <si>
+    <t>LIN Switch 2</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 2</t>
+  </si>
+  <si>
+    <t>SN Switch 3</t>
+  </si>
+  <si>
+    <t>LIN Switch 3</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 3</t>
+  </si>
+  <si>
+    <t>SN Switch 4</t>
+  </si>
+  <si>
+    <t>LIN Switch 4</t>
+  </si>
+  <si>
+    <t>Beschriftung Switch 4</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 3</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail oben Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail unten Vorderseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail oben Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Detail unten Rückseite</t>
+  </si>
+  <si>
+    <t>NWS 3 Kabelweg</t>
+  </si>
+  <si>
+    <t>NWS 3 Abzweigdose Strom</t>
+  </si>
+  <si>
+    <t>NWS 3 Erdung</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS 3</t>
+  </si>
+  <si>
+    <t>NWS 3 - Beschriftung / SN / LIN</t>
+  </si>
+  <si>
+    <t>SN AcessA</t>
+  </si>
+  <si>
+    <t>SN AcessB</t>
+  </si>
+  <si>
+    <t>SN LTE-Router Access A</t>
+  </si>
+  <si>
+    <t>SN LTE-Router Access B</t>
+  </si>
+  <si>
+    <t>NWS-UV</t>
+  </si>
+  <si>
+    <t>NWS-UV Front</t>
+  </si>
+  <si>
+    <t>Kabelführung Datenkabel NWS-UV</t>
+  </si>
+  <si>
+    <t>Erdung im NWS-UV</t>
+  </si>
+  <si>
+    <t>Abzweigdose + Potischiene überm NWS-UV</t>
+  </si>
+  <si>
+    <t>NWS-UV geschlossen Totale</t>
+  </si>
+  <si>
+    <t>Kabelcodierung NWS-UV</t>
+  </si>
+  <si>
+    <t>Digitales Backschema</t>
+  </si>
+  <si>
+    <t>SN_KVM Switch</t>
+  </si>
+  <si>
+    <t>LIN_KVM Switch</t>
+  </si>
+  <si>
+    <t>Plantasche NWS</t>
+  </si>
+  <si>
+    <t>Kabelwege Pfand</t>
+  </si>
+  <si>
+    <t>Kabelwege Backnische</t>
+  </si>
+  <si>
+    <t>Kabelwege Kassenzone</t>
+  </si>
+  <si>
+    <t>Kabelwege Aktenraum</t>
+  </si>
+  <si>
+    <t>Kabelwege Filiallager</t>
+  </si>
+  <si>
+    <t>Kabelwege Technikebene</t>
+  </si>
+  <si>
+    <t>Kabelwege Sozialräume</t>
+  </si>
+  <si>
+    <t>Netzwerkschrank 1</t>
+  </si>
+  <si>
+    <t>Allgemein / CCTV / Exit /Blitz</t>
+  </si>
+  <si>
+    <t>Allgemein / KV / Ports</t>
+  </si>
+  <si>
+    <t>Allgemein / Headset / Ports</t>
+  </si>
+  <si>
+    <t>NWS 1 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>NWS 2 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>NWS 3 Übersicht / Strom / PE / Codierung</t>
+  </si>
+  <si>
+    <t>SN_Telefon 1</t>
+  </si>
+  <si>
+    <t>SN_Telefon 2</t>
+  </si>
+  <si>
+    <t>Lautsprecher Monitor</t>
+  </si>
+  <si>
+    <t>SN Main Unit 1</t>
+  </si>
+  <si>
+    <t>SN Main Unit 2</t>
+  </si>
+  <si>
+    <t>SN Bosch Verstärker</t>
+  </si>
+  <si>
+    <t>SN SMC</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 2</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 2</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 5</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 5</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 4</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 4</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 3</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 3</t>
+  </si>
+  <si>
+    <t>LIN Vocovo Controller 1</t>
+  </si>
+  <si>
+    <t>SN Vocovo Controller 1</t>
+  </si>
+  <si>
+    <t>SN Kundenterminal</t>
+  </si>
+  <si>
+    <t>HGA Dose Detail</t>
+  </si>
+  <si>
+    <t>HGA Dose Totale</t>
+  </si>
+  <si>
     <t>Kassenzone</t>
-  </si>
-  <si>
-    <t>01_Maengel</t>
-  </si>
-  <si>
-    <t>Maengel_vorher</t>
-  </si>
-  <si>
-    <t>Maengel_behoben</t>
-  </si>
-  <si>
-    <t>02_Abnahme</t>
-  </si>
-  <si>
-    <t>Abnahme_Unterschrift</t>
-  </si>
-  <si>
-    <t>Kasse 1</t>
-  </si>
-  <si>
-    <t>Kasse 1 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 1 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 1 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 2 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 2 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 2 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 2</t>
-  </si>
-  <si>
-    <t>Kasse 3 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 3 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 3 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 4 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 4 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 4 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 5 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 5 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 5 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 6 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 6 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 6 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 7 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 7 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 7 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 8 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 8 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 8 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 9 Beschriftung Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 9 Sammelpunkt</t>
-  </si>
-  <si>
-    <t>Kasse 9 Kabelweg in der Kasse</t>
-  </si>
-  <si>
-    <t>Kasse 3</t>
-  </si>
-  <si>
-    <t>Kasse 4</t>
-  </si>
-  <si>
-    <t>Kasse 5</t>
-  </si>
-  <si>
-    <t>Kasse 6</t>
-  </si>
-  <si>
-    <t>Kasse 7</t>
-  </si>
-  <si>
-    <t>Kasse 8</t>
-  </si>
-  <si>
-    <t>Kasse 9</t>
-  </si>
-  <si>
-    <t>SCO Kasse 1</t>
-  </si>
-  <si>
-    <t>SCO 81 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 81 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 82 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 82 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 83 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 83 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 84 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 84 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 85 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 85 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 86 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 86 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 87 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 87 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO 88 Module im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO 88 Kabelreserve</t>
-  </si>
-  <si>
-    <t>SCO Kasse 2</t>
-  </si>
-  <si>
-    <t>SCO Kasse 3</t>
-  </si>
-  <si>
-    <t>SCO Kasse 4</t>
-  </si>
-  <si>
-    <t>SCO Kasse 5</t>
-  </si>
-  <si>
-    <t>SCO Kasse 6</t>
-  </si>
-  <si>
-    <t>SCO Kasse 7</t>
-  </si>
-  <si>
-    <t>SCO Kasse 8</t>
-  </si>
-  <si>
-    <t>SCO Kasse 9</t>
-  </si>
-  <si>
-    <t>SCO Service Kasse</t>
-  </si>
-  <si>
-    <t>SCO Service Kasse Modul im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO Service Kasse Terminal Modul im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO Service Kasse reserve Port Modul im Kassentisch</t>
-  </si>
-  <si>
-    <t>SCO Service Kasse Reserve</t>
-  </si>
-  <si>
-    <t>Kassen Totale</t>
-  </si>
-  <si>
-    <t>CCTV 1 Modul im Kassentisch</t>
-  </si>
-  <si>
-    <t>CCTV 2 Modul im Kassentisch</t>
-  </si>
-  <si>
-    <t>Exit Gate Modul</t>
-  </si>
-  <si>
-    <t>Blitzleuchte Klemmen</t>
-  </si>
-  <si>
-    <t>Blitzleuchte Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 2 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 2 Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 3 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 3 Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 4 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 4 Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 5 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 5 Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 6 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 6 Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage</t>
-  </si>
-  <si>
-    <t>02_Pfandraum</t>
-  </si>
-  <si>
-    <t>Pfand 1 Dose</t>
-  </si>
-  <si>
-    <t>Pfand 2 Dose</t>
-  </si>
-  <si>
-    <t>Pfand 3 Dose</t>
-  </si>
-  <si>
-    <t>Pfand Reserve Dose</t>
-  </si>
-  <si>
-    <t>Pfand gesamt Totale</t>
-  </si>
-  <si>
-    <t>Digital Signage 1 Dose</t>
-  </si>
-  <si>
-    <t>Digital Signage 1 Totale</t>
-  </si>
-  <si>
-    <t>03_Backnische</t>
-  </si>
-  <si>
-    <t>BA 01 + 02 Dose</t>
-  </si>
-  <si>
-    <t>BA 01 + 02 Totale</t>
-  </si>
-  <si>
-    <t>BA 03 + 04 Dose</t>
-  </si>
-  <si>
-    <t>BA 03 + 04 Totale</t>
-  </si>
-  <si>
-    <t>BA 05 + 06 Dose</t>
-  </si>
-  <si>
-    <t>BA 05 + 06 Totale</t>
-  </si>
-  <si>
-    <t>BA Totale</t>
-  </si>
-  <si>
-    <t>BakeOff 1 + BakeOff 2 Dose</t>
-  </si>
-  <si>
-    <t>BakeOff 1 + BakeOff2 Totale</t>
-  </si>
-  <si>
-    <t>04_Aktenraum</t>
-  </si>
-  <si>
-    <t>Thin Client + Res</t>
-  </si>
-  <si>
-    <t>Drucker + FAX</t>
-  </si>
-  <si>
-    <t>TEL + Res</t>
-  </si>
-  <si>
-    <t>Aktenraum Totale</t>
-  </si>
-  <si>
-    <t>Cashmaschine</t>
-  </si>
-  <si>
-    <t>Cashmaschine Totale</t>
-  </si>
-  <si>
-    <t>Kleinverteiler Ports</t>
-  </si>
-  <si>
-    <t>Kleinverteiler offen</t>
-  </si>
-  <si>
-    <t>Kleinverteiler Totale</t>
-  </si>
-  <si>
-    <t>Kabelcodierung Aktenraum</t>
-  </si>
-  <si>
-    <t>Geldwage</t>
-  </si>
-  <si>
-    <t>Serien-/LIN-Nummern</t>
-  </si>
-  <si>
-    <t>ELO</t>
-  </si>
-  <si>
-    <t>SN ELO</t>
-  </si>
-  <si>
-    <t>LIN ELO</t>
-  </si>
-  <si>
-    <t>SN Geldwage</t>
-  </si>
-  <si>
-    <t>LIN Geldwage</t>
-  </si>
-  <si>
-    <t>SN Drucker</t>
-  </si>
-  <si>
-    <t>Nachweis</t>
-  </si>
-  <si>
-    <t>Anmeldemaske BO</t>
-  </si>
-  <si>
-    <t>PZE online</t>
-  </si>
-  <si>
-    <t>KWLAN</t>
-  </si>
-  <si>
-    <t>Registrierung Vocovo Telefone</t>
-  </si>
-  <si>
-    <t>FTTH</t>
-  </si>
-  <si>
-    <t>FTTH Anschluß Dose</t>
-  </si>
-  <si>
-    <t>FTTH Anschluß Totale</t>
-  </si>
-  <si>
-    <t>FTTH Modem</t>
-  </si>
-  <si>
-    <t>FTTH Modem Totale</t>
-  </si>
-  <si>
-    <t>05_Filiallager</t>
-  </si>
-  <si>
-    <t>1. Lager + 2. Lager</t>
-  </si>
-  <si>
-    <t>1. Lager + 2. Lager Totale</t>
-  </si>
-  <si>
-    <t>3. Lager + 4. Lager</t>
-  </si>
-  <si>
-    <t>3. Lager + 4. Lager Totale</t>
-  </si>
-  <si>
-    <t>Xweb Dose</t>
-  </si>
-  <si>
-    <t>Xweb Totale</t>
-  </si>
-  <si>
-    <t>06_Technikebene</t>
-  </si>
-  <si>
-    <t>L-Box Dose</t>
-  </si>
-  <si>
-    <t>L-Box Totale</t>
-  </si>
-  <si>
-    <t>Integral / Wago Dose</t>
-  </si>
-  <si>
-    <t>Integral / Wago Totale</t>
-  </si>
-  <si>
-    <t>AP1 Dose</t>
-  </si>
-  <si>
-    <t>AP1 Totale</t>
-  </si>
-  <si>
-    <t>AP1 Brandschott</t>
-  </si>
-  <si>
-    <t>AP2 Dose</t>
-  </si>
-  <si>
-    <t>AP2 Totale</t>
-  </si>
-  <si>
-    <t>AP2 Brandschott</t>
-  </si>
-  <si>
-    <t>AP3 Dose</t>
-  </si>
-  <si>
-    <t>AP3 Totale</t>
-  </si>
-  <si>
-    <t>AP3 Brandschott</t>
-  </si>
-  <si>
-    <t>AP4 Dose</t>
-  </si>
-  <si>
-    <t>AP4 Totale</t>
-  </si>
-  <si>
-    <t>AP4 Brandschott</t>
-  </si>
-  <si>
-    <t>AP5 Dose</t>
-  </si>
-  <si>
-    <t>AP5 Totale</t>
-  </si>
-  <si>
-    <t>AP5 Brandschott</t>
-  </si>
-  <si>
-    <t>AP6 Dose</t>
-  </si>
-  <si>
-    <t>AP6 Totale</t>
-  </si>
-  <si>
-    <t>AP6 Brandschott</t>
-  </si>
-  <si>
-    <t>AP7 Dose</t>
-  </si>
-  <si>
-    <t>AP7 Totale</t>
-  </si>
-  <si>
-    <t>AP7 Brandschott</t>
-  </si>
-  <si>
-    <t>AP8 Dose</t>
-  </si>
-  <si>
-    <t>AP8 Totale</t>
-  </si>
-  <si>
-    <t>AP8 Brandschott</t>
-  </si>
-  <si>
-    <t>AP9 Dose</t>
-  </si>
-  <si>
-    <t>AP9 Totale</t>
-  </si>
-  <si>
-    <t>AP9 Brandschott</t>
-  </si>
-  <si>
-    <t>AP10 Dose</t>
-  </si>
-  <si>
-    <t>AP10 Totale</t>
-  </si>
-  <si>
-    <t>AP10 Brandschott</t>
-  </si>
-  <si>
-    <t>AP11 Dose</t>
-  </si>
-  <si>
-    <t>AP11 Totale</t>
-  </si>
-  <si>
-    <t>AP11 Brandschott</t>
-  </si>
-  <si>
-    <t>AP12 Dose</t>
-  </si>
-  <si>
-    <t>AP12 Totale</t>
-  </si>
-  <si>
-    <t>AP12 Brandschott</t>
-  </si>
-  <si>
-    <t>AP13 Dose</t>
-  </si>
-  <si>
-    <t>AP13 Totale</t>
-  </si>
-  <si>
-    <t>AP13 Brandschott</t>
-  </si>
-  <si>
-    <t>AP14 Dose</t>
-  </si>
-  <si>
-    <t>AP14 Totale</t>
-  </si>
-  <si>
-    <t>AP14 Brandschott</t>
-  </si>
-  <si>
-    <t>AP15 Dose</t>
-  </si>
-  <si>
-    <t>AP15 Totale</t>
-  </si>
-  <si>
-    <t>AP15 Brandschott</t>
-  </si>
-  <si>
-    <t>AP16 Dose</t>
-  </si>
-  <si>
-    <t>AP16 Totale</t>
-  </si>
-  <si>
-    <t>AP16 Brandschott</t>
-  </si>
-  <si>
-    <t>07_Accesspoints</t>
-  </si>
-  <si>
-    <t>AP1</t>
-  </si>
-  <si>
-    <t>AP2</t>
-  </si>
-  <si>
-    <t>AP3</t>
-  </si>
-  <si>
-    <t>AP4</t>
-  </si>
-  <si>
-    <t>AP5</t>
-  </si>
-  <si>
-    <t>AP6</t>
-  </si>
-  <si>
-    <t>AP7</t>
-  </si>
-  <si>
-    <t>AP8</t>
-  </si>
-  <si>
-    <t>AP9</t>
-  </si>
-  <si>
-    <t>AP10</t>
-  </si>
-  <si>
-    <t>AP11</t>
-  </si>
-  <si>
-    <t>AP12</t>
-  </si>
-  <si>
-    <t>AP13</t>
-  </si>
-  <si>
-    <t>AP14</t>
-  </si>
-  <si>
-    <t>AP15</t>
-  </si>
-  <si>
-    <t>AP16</t>
-  </si>
-  <si>
-    <t>SN AP1</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP1</t>
-  </si>
-  <si>
-    <t>LIN AP1</t>
-  </si>
-  <si>
-    <t>IoT AP1</t>
-  </si>
-  <si>
-    <t>SN AP2</t>
-  </si>
-  <si>
-    <t>LIN AP2</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP2</t>
-  </si>
-  <si>
-    <t>IoT AP2</t>
-  </si>
-  <si>
-    <t>SN AP3</t>
-  </si>
-  <si>
-    <t>LIN AP3</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP3</t>
-  </si>
-  <si>
-    <t>IoT AP3</t>
-  </si>
-  <si>
-    <t>SN AP4</t>
-  </si>
-  <si>
-    <t>LIN AP4</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP4</t>
-  </si>
-  <si>
-    <t>IoT AP4</t>
-  </si>
-  <si>
-    <t>SN AP5</t>
-  </si>
-  <si>
-    <t>LIN AP5</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP5</t>
-  </si>
-  <si>
-    <t>IoT AP5</t>
-  </si>
-  <si>
-    <t>SN AP6</t>
-  </si>
-  <si>
-    <t>LIN AP6</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP6</t>
-  </si>
-  <si>
-    <t>IoT AP6</t>
-  </si>
-  <si>
-    <t>SN AP7</t>
-  </si>
-  <si>
-    <t>LIN AP7</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP7</t>
-  </si>
-  <si>
-    <t>IoT AP7</t>
-  </si>
-  <si>
-    <t>SN AP8</t>
-  </si>
-  <si>
-    <t>LIN AP8</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP8</t>
-  </si>
-  <si>
-    <t>IoT AP8</t>
-  </si>
-  <si>
-    <t>SN AP9</t>
-  </si>
-  <si>
-    <t>LIN AP9</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP9</t>
-  </si>
-  <si>
-    <t>IoT AP9</t>
-  </si>
-  <si>
-    <t>SN AP10</t>
-  </si>
-  <si>
-    <t>LIN AP10</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP10</t>
-  </si>
-  <si>
-    <t>IoT AP10</t>
-  </si>
-  <si>
-    <t>SN AP11</t>
-  </si>
-  <si>
-    <t>LIN AP11</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP11</t>
-  </si>
-  <si>
-    <t>IoT AP11</t>
-  </si>
-  <si>
-    <t>SN AP12</t>
-  </si>
-  <si>
-    <t>LIN AP12</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP12</t>
-  </si>
-  <si>
-    <t>IoT AP12</t>
-  </si>
-  <si>
-    <t>SN AP13</t>
-  </si>
-  <si>
-    <t>LIN AP13</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP13</t>
-  </si>
-  <si>
-    <t>IoT AP13</t>
-  </si>
-  <si>
-    <t>SN AP14</t>
-  </si>
-  <si>
-    <t>LIN AP14</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP14</t>
-  </si>
-  <si>
-    <t>IoT AP14</t>
-  </si>
-  <si>
-    <t>SN AP15</t>
-  </si>
-  <si>
-    <t>LIN AP15</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP15</t>
-  </si>
-  <si>
-    <t>IoT AP15</t>
-  </si>
-  <si>
-    <t>SN AP16</t>
-  </si>
-  <si>
-    <t>LIN AP16</t>
-  </si>
-  <si>
-    <t>Beschriftung SN + MAC AP16</t>
-  </si>
-  <si>
-    <t>IoT AP16</t>
-  </si>
-  <si>
-    <t>08_Sozialräume</t>
-  </si>
-  <si>
-    <t>Lili Dose</t>
-  </si>
-  <si>
-    <t>Lili Totale</t>
-  </si>
-  <si>
-    <t>PZE Dose</t>
-  </si>
-  <si>
-    <t>PZE Totale</t>
-  </si>
-  <si>
-    <t>PZE gesamt</t>
-  </si>
-  <si>
-    <t>Perso 1 + Perso 2 Dose</t>
-  </si>
-  <si>
-    <t>Perso 1 + Perso 2Totale</t>
-  </si>
-  <si>
-    <t>Headset Strom</t>
-  </si>
-  <si>
-    <t>Headset Totale</t>
-  </si>
-  <si>
-    <t>SN MAT</t>
-  </si>
-  <si>
-    <t>LIN MAT</t>
-  </si>
-  <si>
-    <t>LIN PZE</t>
-  </si>
-  <si>
-    <t>SN Headsets</t>
-  </si>
-  <si>
-    <t>09_Vocovo</t>
-  </si>
-  <si>
-    <t>Vocovo 1</t>
-  </si>
-  <si>
-    <t>Vocovo 1 Dose</t>
-  </si>
-  <si>
-    <t>Vocovo 1 Totale</t>
-  </si>
-  <si>
-    <t>Vocovo 1 Brandschott</t>
-  </si>
-  <si>
-    <t>Vocovo 2 Dose</t>
-  </si>
-  <si>
-    <t>Vocovo 2 Totale</t>
-  </si>
-  <si>
-    <t>Vocovo 2 Brandschott</t>
-  </si>
-  <si>
-    <t>Vocovo 3 Dose</t>
-  </si>
-  <si>
-    <t>Vocovo 3 Totale</t>
-  </si>
-  <si>
-    <t>Vocovo 3 Brandschott</t>
-  </si>
-  <si>
-    <t>Vocovo 4 Dose</t>
-  </si>
-  <si>
-    <t>Vocovo 4 Totale</t>
-  </si>
-  <si>
-    <t>Vocovo 4 Brandschott</t>
-  </si>
-  <si>
-    <t>Vocovo 5 Dose</t>
-  </si>
-  <si>
-    <t>Vocovo 5 Totale</t>
-  </si>
-  <si>
-    <t>Vocovo 5 Brandschott</t>
-  </si>
-  <si>
-    <t>Vocovo 2</t>
-  </si>
-  <si>
-    <t>Vocovo 3</t>
-  </si>
-  <si>
-    <t>Vocovo 4</t>
-  </si>
-  <si>
-    <t>Vocovo 5</t>
-  </si>
-  <si>
-    <t>Vocovo BR Kanal Headsets Modul</t>
-  </si>
-  <si>
-    <t>Vocovo BR Kanal Headsets Totale</t>
-  </si>
-  <si>
-    <t>Vocovo BR Kanal</t>
-  </si>
-  <si>
-    <t>10_Serverraum</t>
-  </si>
-  <si>
-    <t>Netzwerkschränke Vorderseite</t>
-  </si>
-  <si>
-    <t>Netzwerkschränke Rückseite</t>
-  </si>
-  <si>
-    <t>Kabelverlegung Serverraum</t>
-  </si>
-  <si>
-    <t>NWS 1 Detail oben Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 1 Detail mitte Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 1 Detail unten Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 1 Detail oben Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 1 Detail unten Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 1 Kabelweg</t>
-  </si>
-  <si>
-    <t>NWS 1 Abzweigdose Strom</t>
-  </si>
-  <si>
-    <t>NWS 1 Erdung</t>
-  </si>
-  <si>
-    <t>Kabelcodierung NWS 1</t>
-  </si>
-  <si>
-    <t>SN Cisco 01_Router_VPN11_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>LIN Cisco 01_Router_VPN11_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>Beschriftung Cisco 01_Router_VPN11_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>SN Cisco 02_Router_VPN12_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>LIN Cisco 02_Router_VPN12_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>Beschriftung Cisco 02_Router_VPN12_(C1111-8P)</t>
-  </si>
-  <si>
-    <t>SN Huawei S5735-12P WAN-Switche 1</t>
-  </si>
-  <si>
-    <t>LIN + Beschr Huawei S5735-12P WAN-Switche 1</t>
-  </si>
-  <si>
-    <t>SN Huawei S5735-12P WAN-Switche 2</t>
-  </si>
-  <si>
-    <t>LIN + Besch Huawei S5735-12P WAN-Switche 2</t>
-  </si>
-  <si>
-    <t>SN Fortinet Fortigate F60EFirewall 1a</t>
-  </si>
-  <si>
-    <t>LIN Fortinet Fortigate F60EFirewall 1a</t>
-  </si>
-  <si>
-    <t>Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
-  </si>
-  <si>
-    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1a</t>
-  </si>
-  <si>
-    <t>SN Fortinet Fortigate F60EFirewall 1b</t>
-  </si>
-  <si>
-    <t>LIN Fortinet Fortigate F60EFirewall 1b</t>
-  </si>
-  <si>
-    <t>Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
-  </si>
-  <si>
-    <t>Port-Beschriftung Fortinet Fortigate F60EFirewall 1b</t>
-  </si>
-  <si>
-    <t>SN Server</t>
-  </si>
-  <si>
-    <t>LIN Server</t>
-  </si>
-  <si>
-    <t>SN PZE</t>
-  </si>
-  <si>
-    <t>Netzwerkschrank 2</t>
-  </si>
-  <si>
-    <t>NWS 2 Detail oben Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 2 Detail mitte Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 2 Detail unten Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 2 Detail oben Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 2 Detail unten Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 2 Kabelweg</t>
-  </si>
-  <si>
-    <t>NWS 2 Abzweigdose Strom</t>
-  </si>
-  <si>
-    <t>NWS 2 Erdung</t>
-  </si>
-  <si>
-    <t>Switch 1 gepatcht</t>
-  </si>
-  <si>
-    <t>Switch 2 gepatcht</t>
-  </si>
-  <si>
-    <t>Switch 3 gepatcht</t>
-  </si>
-  <si>
-    <t>Kabelcodierung NWS 2</t>
-  </si>
-  <si>
-    <t>SN Frederix</t>
-  </si>
-  <si>
-    <t>LIN Frederix</t>
-  </si>
-  <si>
-    <t>SN Baracuda</t>
-  </si>
-  <si>
-    <t>LIN Baracuda</t>
-  </si>
-  <si>
-    <t>NWS 1 - Beschriftung / SN / LIN</t>
-  </si>
-  <si>
-    <t>NWS 2 - Beschriftung / SN / LIN</t>
-  </si>
-  <si>
-    <t>SN Switch 1</t>
-  </si>
-  <si>
-    <t>LIN Switch 1</t>
-  </si>
-  <si>
-    <t>Beschriftung Switch 1</t>
-  </si>
-  <si>
-    <t>SN Switch 2</t>
-  </si>
-  <si>
-    <t>LIN Switch 2</t>
-  </si>
-  <si>
-    <t>Beschriftung Switch 2</t>
-  </si>
-  <si>
-    <t>SN Switch 3</t>
-  </si>
-  <si>
-    <t>LIN Switch 3</t>
-  </si>
-  <si>
-    <t>Beschriftung Switch 3</t>
-  </si>
-  <si>
-    <t>SN Switch 4</t>
-  </si>
-  <si>
-    <t>LIN Switch 4</t>
-  </si>
-  <si>
-    <t>Beschriftung Switch 4</t>
-  </si>
-  <si>
-    <t>Netzwerkschrank 3</t>
-  </si>
-  <si>
-    <t>NWS 3 Detail oben Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 3 Detail unten Vorderseite</t>
-  </si>
-  <si>
-    <t>NWS 3 Detail oben Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 3 Detail unten Rückseite</t>
-  </si>
-  <si>
-    <t>NWS 3 Kabelweg</t>
-  </si>
-  <si>
-    <t>NWS 3 Abzweigdose Strom</t>
-  </si>
-  <si>
-    <t>NWS 3 Erdung</t>
-  </si>
-  <si>
-    <t>Kabelcodierung NWS 3</t>
-  </si>
-  <si>
-    <t>NWS 3 - Beschriftung / SN / LIN</t>
-  </si>
-  <si>
-    <t>SN AcessA</t>
-  </si>
-  <si>
-    <t>SN AcessB</t>
-  </si>
-  <si>
-    <t>SN LTE-Router Access A</t>
-  </si>
-  <si>
-    <t>SN LTE-Router Access B</t>
-  </si>
-  <si>
-    <t>NWS-UV</t>
-  </si>
-  <si>
-    <t>NWS-UV Front</t>
-  </si>
-  <si>
-    <t>Kabelführung Datenkabel NWS-UV</t>
-  </si>
-  <si>
-    <t>Erdung im NWS-UV</t>
-  </si>
-  <si>
-    <t>Abzweigdose + Potischiene überm NWS-UV</t>
-  </si>
-  <si>
-    <t>NWS-UV geschlossen Totale</t>
-  </si>
-  <si>
-    <t>Kabelcodierung NWS-UV</t>
-  </si>
-  <si>
-    <t>Digitales Backschema</t>
-  </si>
-  <si>
-    <t>SN_KVM Switch</t>
-  </si>
-  <si>
-    <t>LIN_KVM Switch</t>
-  </si>
-  <si>
-    <t>Plantasche NWS</t>
-  </si>
-  <si>
-    <t>Kabelwege Pfand</t>
-  </si>
-  <si>
-    <t>Kabelwege Backnische</t>
-  </si>
-  <si>
-    <t>Kabelwege Kassenzone</t>
-  </si>
-  <si>
-    <t>Kabelwege Aktenraum</t>
-  </si>
-  <si>
-    <t>Kabelwege Filiallager</t>
-  </si>
-  <si>
-    <t>Kabelwege Technikebene</t>
-  </si>
-  <si>
-    <t>Kabelwege Sozialräume</t>
-  </si>
-  <si>
-    <t>Netzwerkschrank 1</t>
-  </si>
-  <si>
-    <t>Allgemein / CCTV / Exit /Blitz</t>
-  </si>
-  <si>
-    <t>Allgemein / KV / Ports</t>
-  </si>
-  <si>
-    <t>Allgemein / Headset / Ports</t>
-  </si>
-  <si>
-    <t>NWS 1 Übersicht / Strom / PE / Codierung</t>
-  </si>
-  <si>
-    <t>NWS 2 Übersicht / Strom / PE / Codierung</t>
-  </si>
-  <si>
-    <t>NWS 3 Übersicht / Strom / PE / Codierung</t>
-  </si>
-  <si>
-    <t>SN_Telefon 1</t>
-  </si>
-  <si>
-    <t>SN_Telefon 2</t>
-  </si>
-  <si>
-    <t>Lautsprecher Monitor</t>
-  </si>
-  <si>
-    <t>SN Main Unit 1</t>
-  </si>
-  <si>
-    <t>SN Main Unit 2</t>
-  </si>
-  <si>
-    <t>SN Bosch Verstärker</t>
-  </si>
-  <si>
-    <t>SN SMC</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 2</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 2</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 5</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 5</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 4</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 4</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 3</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 3</t>
-  </si>
-  <si>
-    <t>LIN Vocovo Controller 1</t>
-  </si>
-  <si>
-    <t>SN Vocovo Controller 1</t>
-  </si>
-  <si>
-    <t>SN Kundenterminal</t>
-  </si>
-  <si>
-    <t>HGA Dose Detail</t>
-  </si>
-  <si>
-    <t>HGA Dose Totale</t>
   </si>
 </sst>
 </file>
@@ -1805,13 +1805,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>4</v>
+        <v>442</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="8">
         <v>1</v>
@@ -1821,7 +1821,7 @@
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -1831,7 +1831,7 @@
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -1841,7 +1841,7 @@
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -1851,7 +1851,7 @@
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -1861,7 +1861,7 @@
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>
@@ -1871,7 +1871,7 @@
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -1881,7 +1881,7 @@
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D9" s="8">
         <v>1</v>
@@ -1891,7 +1891,7 @@
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D10" s="8">
         <v>3</v>
@@ -1900,10 +1900,10 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="5">
         <v>1</v>
@@ -1913,7 +1913,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="5">
         <v>1</v>
@@ -1923,7 +1923,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5">
         <v>1</v>
@@ -1932,10 +1932,10 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="5">
         <v>1</v>
@@ -1945,7 +1945,7 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D15" s="5">
         <v>1</v>
@@ -1955,7 +1955,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="5">
         <v>1</v>
@@ -1964,10 +1964,10 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -1977,7 +1977,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -1987,7 +1987,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -1996,10 +1996,10 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -2009,7 +2009,7 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -2019,7 +2019,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -2028,10 +2028,10 @@
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -2041,7 +2041,7 @@
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -2051,7 +2051,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -2060,10 +2060,10 @@
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" s="5">
         <v>1</v>
@@ -2073,7 +2073,7 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -2083,7 +2083,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -2092,10 +2092,10 @@
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -2105,7 +2105,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" s="5">
         <v>1</v>
@@ -2115,7 +2115,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31" s="5">
         <v>1</v>
@@ -2124,10 +2124,10 @@
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D32" s="5">
         <v>1</v>
@@ -2137,7 +2137,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33" s="5">
         <v>1</v>
@@ -2147,7 +2147,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D34" s="5">
         <v>1</v>
@@ -2156,10 +2156,10 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" s="5">
         <v>1</v>
@@ -2169,7 +2169,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" s="5">
         <v>1</v>
@@ -2179,7 +2179,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="5">
         <v>1</v>
@@ -2188,10 +2188,10 @@
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="D38" s="5">
         <v>1</v>
@@ -2201,7 +2201,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D39" s="5">
         <v>1</v>
@@ -2210,10 +2210,10 @@
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D40" s="5">
         <v>1</v>
@@ -2223,7 +2223,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="5">
         <v>1</v>
@@ -2232,10 +2232,10 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D42" s="5">
         <v>1</v>
@@ -2245,7 +2245,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D43" s="5">
         <v>1</v>
@@ -2254,10 +2254,10 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44" s="5">
         <v>1</v>
@@ -2267,7 +2267,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D45" s="5">
         <v>1</v>
@@ -2276,10 +2276,10 @@
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="5">
         <v>1</v>
@@ -2289,7 +2289,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D47" s="5">
         <v>1</v>
@@ -2298,10 +2298,10 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D48" s="5">
         <v>1</v>
@@ -2311,7 +2311,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="5">
         <v>1</v>
@@ -2320,10 +2320,10 @@
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="5">
         <v>1</v>
@@ -2333,7 +2333,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D51" s="5">
         <v>1</v>
@@ -2342,10 +2342,10 @@
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="5">
         <v>1</v>
@@ -2355,7 +2355,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="5">
         <v>1</v>
@@ -2364,10 +2364,10 @@
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54" s="5">
         <v>1</v>
@@ -2377,7 +2377,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D55" s="5">
         <v>1</v>
@@ -2386,10 +2386,10 @@
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="D56" s="5">
         <v>1</v>
@@ -2399,7 +2399,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D57" s="5">
         <v>1</v>
@@ -2409,7 +2409,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D58" s="5">
         <v>1</v>
@@ -2419,7 +2419,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D59" s="5">
         <v>1</v>
@@ -2428,10 +2428,10 @@
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D60" s="5">
         <v>1</v>
@@ -2441,7 +2441,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D61" s="5">
         <v>1</v>
@@ -2451,7 +2451,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D62" s="5">
         <v>1</v>
@@ -2461,7 +2461,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D63" s="5">
         <v>1</v>
@@ -2471,7 +2471,7 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D64" s="5">
         <v>1</v>
@@ -2481,7 +2481,7 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D65" s="5">
         <v>1</v>
@@ -2491,7 +2491,7 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D66" s="5">
         <v>1</v>
@@ -2501,7 +2501,7 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D67" s="5">
         <v>1</v>
@@ -2511,7 +2511,7 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D68" s="5">
         <v>1</v>
@@ -2521,7 +2521,7 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D69" s="5">
         <v>1</v>
@@ -2529,11 +2529,11 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70" s="5">
         <v>1</v>
@@ -2543,7 +2543,7 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D71" s="5">
         <v>1</v>
@@ -2553,7 +2553,7 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D72" s="5">
         <v>1</v>
@@ -2563,7 +2563,7 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D73" s="5">
         <v>1</v>
@@ -2573,7 +2573,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D74" s="5">
         <v>1</v>
@@ -2583,7 +2583,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D75" s="5">
         <v>1</v>
@@ -2593,7 +2593,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D76" s="5">
         <v>1</v>
@@ -2603,7 +2603,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D77" s="5">
         <v>1</v>
@@ -2613,7 +2613,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D78" s="5">
         <v>1</v>
@@ -2623,7 +2623,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D79" s="5">
         <v>3</v>
@@ -2631,11 +2631,11 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D80" s="5">
         <v>1</v>
@@ -2645,7 +2645,7 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D81" s="5">
         <v>1</v>
@@ -2655,7 +2655,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D82" s="5">
         <v>1</v>
@@ -2665,7 +2665,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D83" s="5">
         <v>1</v>
@@ -2675,7 +2675,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D84" s="5">
         <v>1</v>
@@ -2685,7 +2685,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D85" s="5">
         <v>1</v>
@@ -2695,7 +2695,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D86" s="5">
         <v>1</v>
@@ -2705,7 +2705,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D87" s="5">
         <v>1</v>
@@ -2715,7 +2715,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D88" s="5">
         <v>1</v>
@@ -2725,7 +2725,7 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D89" s="5">
         <v>3</v>
@@ -2735,7 +2735,7 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D90" s="5">
         <v>1</v>
@@ -2745,7 +2745,7 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D91" s="5">
         <v>3</v>
@@ -2753,13 +2753,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>112</v>
       </c>
       <c r="D92" s="5">
         <v>1</v>
@@ -2769,7 +2769,7 @@
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D93" s="5">
         <v>1</v>
@@ -2779,7 +2779,7 @@
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D94" s="5">
         <v>1</v>
@@ -2789,7 +2789,7 @@
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D95" s="5">
         <v>1</v>
@@ -2799,7 +2799,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D96" s="5">
         <v>1</v>
@@ -2809,7 +2809,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D97" s="5">
         <v>1</v>
@@ -2819,7 +2819,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D98" s="5">
         <v>1</v>
@@ -2829,7 +2829,7 @@
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D99" s="5">
         <v>1</v>
@@ -2839,7 +2839,7 @@
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D100" s="5">
         <v>1</v>
@@ -2849,7 +2849,7 @@
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D101" s="5">
         <v>1</v>
@@ -2859,7 +2859,7 @@
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D102" s="5">
         <v>1</v>
@@ -2869,7 +2869,7 @@
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D103" s="5">
         <v>1</v>
@@ -2879,7 +2879,7 @@
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D104" s="5">
         <v>1</v>
@@ -2889,7 +2889,7 @@
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D105" s="5">
         <v>3</v>
@@ -2898,10 +2898,10 @@
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="4"/>
       <c r="B106" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D106" s="5">
         <v>1</v>
@@ -2911,7 +2911,7 @@
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D107" s="5">
         <v>1</v>
@@ -2921,7 +2921,7 @@
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D108" s="5">
         <v>1</v>
@@ -2931,7 +2931,7 @@
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D109" s="5">
         <v>1</v>
@@ -2941,7 +2941,7 @@
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D110" s="5">
         <v>1</v>
@@ -2951,7 +2951,7 @@
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D111" s="5">
         <v>1</v>
@@ -2961,7 +2961,7 @@
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D112" s="5">
         <v>1</v>
@@ -2971,7 +2971,7 @@
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D113" s="5">
         <v>1</v>
@@ -2981,7 +2981,7 @@
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D114" s="5">
         <v>1</v>
@@ -2990,10 +2990,10 @@
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="4"/>
       <c r="B115" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>130</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>131</v>
       </c>
       <c r="D115" s="5">
         <v>1</v>
@@ -3003,7 +3003,7 @@
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D116" s="5">
         <v>1</v>
@@ -3013,7 +3013,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D117" s="5">
         <v>1</v>
@@ -3023,7 +3023,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D118" s="5">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B119" s="4"/>
       <c r="C119" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D119" s="5">
         <v>1</v>
@@ -3045,7 +3045,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D120" s="5">
         <v>1</v>
@@ -3055,7 +3055,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D121" s="5">
         <v>1</v>
@@ -3065,7 +3065,7 @@
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D122" s="5">
         <v>1</v>
@@ -3075,7 +3075,7 @@
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D123" s="5">
         <v>1</v>
@@ -3085,7 +3085,7 @@
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D124" s="5">
         <v>1</v>
@@ -3095,7 +3095,7 @@
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D125" s="5">
         <v>3</v>
@@ -3103,11 +3103,11 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B126" s="4"/>
       <c r="C126" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D126" s="5">
         <v>1</v>
@@ -3117,7 +3117,7 @@
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D127" s="5">
         <v>1</v>
@@ -3127,7 +3127,7 @@
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D128" s="5">
         <v>1</v>
@@ -3137,7 +3137,7 @@
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D129" s="5">
         <v>1</v>
@@ -3147,7 +3147,7 @@
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D130" s="5">
         <v>3</v>
@@ -3155,13 +3155,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B131" s="4" t="s">
-        <v>201</v>
-      </c>
       <c r="C131" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D131" s="5">
         <v>1</v>
@@ -3171,7 +3171,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D132" s="5">
         <v>1</v>
@@ -3181,7 +3181,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D133" s="5">
         <v>1</v>
@@ -3191,7 +3191,7 @@
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D134" s="5">
         <v>1</v>
@@ -3201,7 +3201,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D135" s="5">
         <v>1</v>
@@ -3211,7 +3211,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D136" s="5">
         <v>1</v>
@@ -3221,7 +3221,7 @@
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D137" s="5">
         <v>1</v>
@@ -3230,10 +3230,10 @@
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D138" s="5">
         <v>1</v>
@@ -3243,7 +3243,7 @@
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D139" s="5">
         <v>1</v>
@@ -3253,7 +3253,7 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D140" s="5">
         <v>1</v>
@@ -3263,7 +3263,7 @@
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D141" s="5">
         <v>1</v>
@@ -3273,7 +3273,7 @@
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D142" s="5">
         <v>1</v>
@@ -3283,7 +3283,7 @@
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D143" s="5">
         <v>1</v>
@@ -3293,7 +3293,7 @@
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D144" s="5">
         <v>1</v>
@@ -3302,10 +3302,10 @@
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="4"/>
       <c r="B145" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D145" s="5">
         <v>1</v>
@@ -3315,7 +3315,7 @@
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D146" s="5">
         <v>1</v>
@@ -3325,7 +3325,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D147" s="5">
         <v>1</v>
@@ -3335,7 +3335,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D148" s="5">
         <v>1</v>
@@ -3345,7 +3345,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D149" s="5">
         <v>1</v>
@@ -3355,7 +3355,7 @@
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D150" s="5">
         <v>1</v>
@@ -3365,7 +3365,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D151" s="5">
         <v>1</v>
@@ -3374,10 +3374,10 @@
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D152" s="5">
         <v>1</v>
@@ -3387,7 +3387,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D153" s="5">
         <v>1</v>
@@ -3397,7 +3397,7 @@
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D154" s="5">
         <v>1</v>
@@ -3407,7 +3407,7 @@
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D155" s="5">
         <v>1</v>
@@ -3417,7 +3417,7 @@
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D156" s="5">
         <v>1</v>
@@ -3427,7 +3427,7 @@
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D157" s="5">
         <v>1</v>
@@ -3437,7 +3437,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D158" s="5">
         <v>1</v>
@@ -3446,10 +3446,10 @@
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="4"/>
       <c r="B159" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D159" s="5">
         <v>1</v>
@@ -3459,7 +3459,7 @@
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D160" s="5">
         <v>1</v>
@@ -3469,7 +3469,7 @@
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D161" s="5">
         <v>1</v>
@@ -3479,7 +3479,7 @@
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D162" s="5">
         <v>1</v>
@@ -3489,7 +3489,7 @@
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D163" s="5">
         <v>1</v>
@@ -3499,7 +3499,7 @@
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D164" s="5">
         <v>1</v>
@@ -3509,7 +3509,7 @@
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D165" s="5">
         <v>1</v>
@@ -3518,10 +3518,10 @@
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="4"/>
       <c r="B166" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D166" s="5">
         <v>1</v>
@@ -3531,7 +3531,7 @@
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D167" s="5">
         <v>1</v>
@@ -3541,7 +3541,7 @@
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D168" s="5">
         <v>1</v>
@@ -3551,7 +3551,7 @@
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D169" s="5">
         <v>1</v>
@@ -3561,7 +3561,7 @@
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D170" s="5">
         <v>1</v>
@@ -3571,7 +3571,7 @@
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D171" s="5">
         <v>1</v>
@@ -3581,7 +3581,7 @@
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D172" s="5">
         <v>1</v>
@@ -3590,10 +3590,10 @@
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="4"/>
       <c r="B173" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D173" s="5">
         <v>1</v>
@@ -3603,7 +3603,7 @@
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D174" s="5">
         <v>1</v>
@@ -3613,7 +3613,7 @@
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D175" s="5">
         <v>1</v>
@@ -3623,7 +3623,7 @@
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D176" s="5">
         <v>1</v>
@@ -3633,7 +3633,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D177" s="5">
         <v>1</v>
@@ -3643,7 +3643,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D178" s="5">
         <v>1</v>
@@ -3653,7 +3653,7 @@
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D179" s="5">
         <v>1</v>
@@ -3662,10 +3662,10 @@
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="4"/>
       <c r="B180" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D180" s="5">
         <v>1</v>
@@ -3675,7 +3675,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D181" s="5">
         <v>1</v>
@@ -3685,7 +3685,7 @@
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D182" s="5">
         <v>1</v>
@@ -3695,7 +3695,7 @@
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D183" s="5">
         <v>1</v>
@@ -3705,7 +3705,7 @@
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D184" s="5">
         <v>1</v>
@@ -3715,7 +3715,7 @@
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D185" s="5">
         <v>1</v>
@@ -3725,7 +3725,7 @@
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D186" s="5">
         <v>1</v>
@@ -3734,10 +3734,10 @@
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="4"/>
       <c r="B187" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D187" s="5">
         <v>1</v>
@@ -3747,7 +3747,7 @@
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D188" s="5">
         <v>1</v>
@@ -3757,7 +3757,7 @@
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D189" s="5">
         <v>1</v>
@@ -3767,7 +3767,7 @@
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D190" s="5">
         <v>1</v>
@@ -3777,7 +3777,7 @@
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D191" s="5">
         <v>1</v>
@@ -3787,7 +3787,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D192" s="5">
         <v>1</v>
@@ -3797,7 +3797,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D193" s="5">
         <v>1</v>
@@ -3806,10 +3806,10 @@
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="4"/>
       <c r="B194" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D194" s="5">
         <v>1</v>
@@ -3819,7 +3819,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D195" s="5">
         <v>1</v>
@@ -3829,7 +3829,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D196" s="5">
         <v>1</v>
@@ -3839,7 +3839,7 @@
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D197" s="5">
         <v>1</v>
@@ -3849,7 +3849,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D198" s="5">
         <v>1</v>
@@ -3859,7 +3859,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D199" s="5">
         <v>1</v>
@@ -3869,7 +3869,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D200" s="5">
         <v>1</v>
@@ -3878,10 +3878,10 @@
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="4"/>
       <c r="B201" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D201" s="5">
         <v>1</v>
@@ -3891,7 +3891,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D202" s="5">
         <v>1</v>
@@ -3901,7 +3901,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D203" s="5">
         <v>1</v>
@@ -3911,7 +3911,7 @@
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D204" s="5">
         <v>1</v>
@@ -3921,7 +3921,7 @@
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D205" s="5">
         <v>1</v>
@@ -3931,7 +3931,7 @@
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D206" s="5">
         <v>1</v>
@@ -3941,7 +3941,7 @@
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D207" s="5">
         <v>1</v>
@@ -3950,10 +3950,10 @@
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" s="4"/>
       <c r="B208" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D208" s="5">
         <v>1</v>
@@ -3963,7 +3963,7 @@
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D209" s="5">
         <v>1</v>
@@ -3973,7 +3973,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D210" s="5">
         <v>1</v>
@@ -3983,7 +3983,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D211" s="5">
         <v>1</v>
@@ -3993,7 +3993,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" s="5">
         <v>1</v>
@@ -4003,7 +4003,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D213" s="5">
         <v>1</v>
@@ -4013,7 +4013,7 @@
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D214" s="5">
         <v>1</v>
@@ -4022,10 +4022,10 @@
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" s="4"/>
       <c r="B215" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D215" s="5">
         <v>1</v>
@@ -4035,7 +4035,7 @@
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D216" s="5">
         <v>1</v>
@@ -4045,7 +4045,7 @@
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D217" s="5">
         <v>1</v>
@@ -4055,7 +4055,7 @@
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D218" s="5">
         <v>1</v>
@@ -4065,7 +4065,7 @@
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D219" s="5">
         <v>1</v>
@@ -4075,7 +4075,7 @@
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D220" s="5">
         <v>1</v>
@@ -4085,7 +4085,7 @@
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
       <c r="C221" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D221" s="5">
         <v>1</v>
@@ -4094,10 +4094,10 @@
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" s="4"/>
       <c r="B222" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D222" s="5">
         <v>1</v>
@@ -4107,7 +4107,7 @@
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
       <c r="C223" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D223" s="5">
         <v>1</v>
@@ -4117,7 +4117,7 @@
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
       <c r="C224" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D224" s="5">
         <v>1</v>
@@ -4127,7 +4127,7 @@
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
       <c r="C225" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D225" s="5">
         <v>1</v>
@@ -4137,7 +4137,7 @@
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
       <c r="C226" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D226" s="5">
         <v>1</v>
@@ -4147,7 +4147,7 @@
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
       <c r="C227" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D227" s="5">
         <v>1</v>
@@ -4157,7 +4157,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D228" s="5">
         <v>1</v>
@@ -4166,10 +4166,10 @@
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" s="4"/>
       <c r="B229" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D229" s="5">
         <v>1</v>
@@ -4179,7 +4179,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D230" s="5">
         <v>1</v>
@@ -4189,7 +4189,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D231" s="5">
         <v>1</v>
@@ -4199,7 +4199,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D232" s="5">
         <v>1</v>
@@ -4209,7 +4209,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D233" s="5">
         <v>1</v>
@@ -4219,7 +4219,7 @@
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
       <c r="C234" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D234" s="5">
         <v>1</v>
@@ -4229,7 +4229,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D235" s="5">
         <v>1</v>
@@ -4238,10 +4238,10 @@
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" s="4"/>
       <c r="B236" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D236" s="5">
         <v>1</v>
@@ -4251,7 +4251,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D237" s="5">
         <v>1</v>
@@ -4261,7 +4261,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D238" s="5">
         <v>1</v>
@@ -4271,7 +4271,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D239" s="5">
         <v>1</v>
@@ -4281,7 +4281,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D240" s="5">
         <v>1</v>
@@ -4291,7 +4291,7 @@
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
       <c r="C241" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D241" s="5">
         <v>1</v>
@@ -4301,7 +4301,7 @@
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
       <c r="C242" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D242" s="5">
         <v>1</v>
@@ -4309,13 +4309,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C243" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C243" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="D243" s="5">
         <v>1</v>
@@ -4325,7 +4325,7 @@
       <c r="A244" s="4"/>
       <c r="B244" s="4"/>
       <c r="C244" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D244" s="5">
         <v>1</v>
@@ -4335,7 +4335,7 @@
       <c r="A245" s="4"/>
       <c r="B245" s="4"/>
       <c r="C245" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D245" s="5">
         <v>1</v>
@@ -4345,7 +4345,7 @@
       <c r="A246" s="4"/>
       <c r="B246" s="4"/>
       <c r="C246" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D246" s="5">
         <v>1</v>
@@ -4355,7 +4355,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D247" s="5">
         <v>1</v>
@@ -4365,7 +4365,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D248" s="5">
         <v>1</v>
@@ -4375,7 +4375,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D249" s="5">
         <v>1</v>
@@ -4385,7 +4385,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D250" s="5">
         <v>1</v>
@@ -4395,7 +4395,7 @@
       <c r="A251" s="4"/>
       <c r="B251" s="4"/>
       <c r="C251" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D251" s="5">
         <v>1</v>
@@ -4405,7 +4405,7 @@
       <c r="A252" s="4"/>
       <c r="B252" s="4"/>
       <c r="C252" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D252" s="5">
         <v>3</v>
@@ -4414,10 +4414,10 @@
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" s="4"/>
       <c r="B253" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D253" s="5">
         <v>1</v>
@@ -4427,7 +4427,7 @@
       <c r="A254" s="4"/>
       <c r="B254" s="4"/>
       <c r="C254" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D254" s="5">
         <v>1</v>
@@ -4437,7 +4437,7 @@
       <c r="A255" s="4"/>
       <c r="B255" s="4"/>
       <c r="C255" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D255" s="5">
         <v>1</v>
@@ -4447,7 +4447,7 @@
       <c r="A256" s="4"/>
       <c r="B256" s="4"/>
       <c r="C256" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D256" s="5">
         <v>1</v>
@@ -4457,7 +4457,7 @@
       <c r="A257" s="4"/>
       <c r="B257" s="4"/>
       <c r="C257" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D257" s="5">
         <v>1</v>
@@ -4465,13 +4465,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B258" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="C258" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="C258" s="7" t="s">
-        <v>297</v>
       </c>
       <c r="D258" s="5">
         <v>1</v>
@@ -4481,7 +4481,7 @@
       <c r="A259" s="4"/>
       <c r="B259" s="4"/>
       <c r="C259" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D259" s="5">
         <v>1</v>
@@ -4491,7 +4491,7 @@
       <c r="A260" s="4"/>
       <c r="B260" s="4"/>
       <c r="C260" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D260" s="5">
         <v>1</v>
@@ -4501,7 +4501,7 @@
       <c r="A261" s="4"/>
       <c r="B261" s="4"/>
       <c r="C261" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D261" s="5">
         <v>1</v>
@@ -4511,7 +4511,7 @@
       <c r="A262" s="4"/>
       <c r="B262" s="4"/>
       <c r="C262" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D262" s="5">
         <v>1</v>
@@ -4520,10 +4520,10 @@
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="4"/>
       <c r="B263" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D263" s="5">
         <v>1</v>
@@ -4533,7 +4533,7 @@
       <c r="A264" s="4"/>
       <c r="B264" s="4"/>
       <c r="C264" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D264" s="5">
         <v>1</v>
@@ -4543,7 +4543,7 @@
       <c r="A265" s="4"/>
       <c r="B265" s="4"/>
       <c r="C265" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D265" s="5">
         <v>1</v>
@@ -4553,7 +4553,7 @@
       <c r="A266" s="4"/>
       <c r="B266" s="4"/>
       <c r="C266" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D266" s="5">
         <v>1</v>
@@ -4563,7 +4563,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D267" s="5">
         <v>1</v>
@@ -4572,10 +4572,10 @@
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="4"/>
       <c r="B268" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D268" s="5">
         <v>1</v>
@@ -4585,7 +4585,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D269" s="5">
         <v>1</v>
@@ -4595,7 +4595,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D270" s="5">
         <v>1</v>
@@ -4605,7 +4605,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D271" s="5">
         <v>1</v>
@@ -4615,7 +4615,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D272" s="5">
         <v>1</v>
@@ -4624,10 +4624,10 @@
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="4"/>
       <c r="B273" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C273" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D273" s="5">
         <v>1</v>
@@ -4637,7 +4637,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D274" s="5">
         <v>1</v>
@@ -4647,7 +4647,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D275" s="5">
         <v>1</v>
@@ -4657,7 +4657,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D276" s="5">
         <v>1</v>
@@ -4667,7 +4667,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D277" s="5">
         <v>1</v>
@@ -4676,10 +4676,10 @@
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="4"/>
       <c r="B278" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D278" s="5">
         <v>1</v>
@@ -4689,7 +4689,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D279" s="5">
         <v>1</v>
@@ -4699,7 +4699,7 @@
       <c r="A280" s="4"/>
       <c r="B280" s="4"/>
       <c r="C280" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D280" s="5">
         <v>1</v>
@@ -4709,7 +4709,7 @@
       <c r="A281" s="4"/>
       <c r="B281" s="4"/>
       <c r="C281" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D281" s="5">
         <v>1</v>
@@ -4719,7 +4719,7 @@
       <c r="A282" s="4"/>
       <c r="B282" s="4"/>
       <c r="C282" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D282" s="5">
         <v>1</v>
@@ -4728,10 +4728,10 @@
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="4"/>
       <c r="B283" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D283" s="5">
         <v>1</v>
@@ -4741,7 +4741,7 @@
       <c r="A284" s="4"/>
       <c r="B284" s="4"/>
       <c r="C284" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D284" s="5">
         <v>1</v>
@@ -4749,11 +4749,11 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B285" s="4"/>
       <c r="C285" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D285" s="5">
         <v>1</v>
@@ -4763,7 +4763,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D286" s="5">
         <v>1</v>
@@ -4773,7 +4773,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D287" s="5">
         <v>3</v>
@@ -4783,7 +4783,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D288" s="5">
         <v>1</v>
@@ -4791,13 +4791,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D289" s="5">
         <v>1</v>
@@ -4807,7 +4807,7 @@
       <c r="A290" s="4"/>
       <c r="B290" s="4"/>
       <c r="C290" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D290" s="5">
         <v>1</v>
@@ -4817,7 +4817,7 @@
       <c r="A291" s="4"/>
       <c r="B291" s="4"/>
       <c r="C291" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D291" s="5">
         <v>1</v>
@@ -4827,7 +4827,7 @@
       <c r="A292" s="4"/>
       <c r="B292" s="4"/>
       <c r="C292" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D292" s="5">
         <v>1</v>
@@ -4837,7 +4837,7 @@
       <c r="A293" s="4"/>
       <c r="B293" s="4"/>
       <c r="C293" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D293" s="5">
         <v>1</v>
@@ -4847,7 +4847,7 @@
       <c r="A294" s="4"/>
       <c r="B294" s="4"/>
       <c r="C294" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D294" s="5">
         <v>1</v>
@@ -4857,7 +4857,7 @@
       <c r="A295" s="4"/>
       <c r="B295" s="4"/>
       <c r="C295" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D295" s="5">
         <v>1</v>
@@ -4867,7 +4867,7 @@
       <c r="A296" s="4"/>
       <c r="B296" s="4"/>
       <c r="C296" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D296" s="5">
         <v>1</v>
@@ -4877,7 +4877,7 @@
       <c r="A297" s="4"/>
       <c r="B297" s="4"/>
       <c r="C297" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D297" s="5">
         <v>1</v>
@@ -4886,10 +4886,10 @@
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="4"/>
       <c r="B298" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D298" s="5">
         <v>1</v>
@@ -4899,7 +4899,7 @@
       <c r="A299" s="4"/>
       <c r="B299" s="4"/>
       <c r="C299" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D299" s="5">
         <v>1</v>
@@ -4909,7 +4909,7 @@
       <c r="A300" s="4"/>
       <c r="B300" s="4"/>
       <c r="C300" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D300" s="5">
         <v>1</v>
@@ -4919,7 +4919,7 @@
       <c r="A301" s="4"/>
       <c r="B301" s="4"/>
       <c r="C301" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D301" s="5">
         <v>1</v>
@@ -4929,7 +4929,7 @@
       <c r="A302" s="4"/>
       <c r="B302" s="4"/>
       <c r="C302" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D302" s="5">
         <v>1</v>
@@ -4939,7 +4939,7 @@
       <c r="A303" s="4"/>
       <c r="B303" s="4"/>
       <c r="C303" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D303" s="5">
         <v>1</v>
@@ -4949,7 +4949,7 @@
       <c r="A304" s="4"/>
       <c r="B304" s="4"/>
       <c r="C304" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D304" s="5">
         <v>1</v>
@@ -4959,7 +4959,7 @@
       <c r="A305" s="4"/>
       <c r="B305" s="4"/>
       <c r="C305" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D305" s="5">
         <v>1</v>
@@ -4969,7 +4969,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D306" s="5">
         <v>1</v>
@@ -4979,7 +4979,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D307" s="5">
         <v>1</v>
@@ -4989,7 +4989,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D308" s="5">
         <v>1</v>
@@ -4999,7 +4999,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D309" s="5">
         <v>1</v>
@@ -5009,7 +5009,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D310" s="5">
         <v>1</v>
@@ -5019,7 +5019,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D311" s="5">
         <v>1</v>
@@ -5029,7 +5029,7 @@
       <c r="A312" s="4"/>
       <c r="B312" s="4"/>
       <c r="C312" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D312" s="5">
         <v>1</v>
@@ -5039,7 +5039,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D313" s="5">
         <v>1</v>
@@ -5049,7 +5049,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D314" s="5">
         <v>1</v>
@@ -5059,7 +5059,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D315" s="5">
         <v>1</v>
@@ -5069,7 +5069,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D316" s="5">
         <v>1</v>
@@ -5079,7 +5079,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D317" s="5">
         <v>1</v>
@@ -5089,7 +5089,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D318" s="5">
         <v>1</v>
@@ -5099,7 +5099,7 @@
       <c r="A319" s="4"/>
       <c r="B319" s="4"/>
       <c r="C319" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D319" s="5">
         <v>1</v>
@@ -5109,7 +5109,7 @@
       <c r="A320" s="4"/>
       <c r="B320" s="4"/>
       <c r="C320" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D320" s="5">
         <v>1</v>
@@ -5119,7 +5119,7 @@
       <c r="A321" s="4"/>
       <c r="B321" s="4"/>
       <c r="C321" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D321" s="5">
         <v>1</v>
@@ -5127,13 +5127,13 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C322" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="B322" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="C322" s="7" t="s">
-        <v>354</v>
       </c>
       <c r="D322" s="5">
         <v>1</v>
@@ -5143,7 +5143,7 @@
       <c r="A323" s="4"/>
       <c r="B323" s="4"/>
       <c r="C323" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D323" s="5">
         <v>1</v>
@@ -5153,7 +5153,7 @@
       <c r="A324" s="4"/>
       <c r="B324" s="4"/>
       <c r="C324" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D324" s="5">
         <v>1</v>
@@ -5163,7 +5163,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D325" s="5">
         <v>1</v>
@@ -5173,7 +5173,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D326" s="5">
         <v>1</v>
@@ -5183,7 +5183,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D327" s="5">
         <v>1</v>
@@ -5193,7 +5193,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D328" s="5">
         <v>1</v>
@@ -5203,7 +5203,7 @@
       <c r="A329" s="4"/>
       <c r="B329" s="4"/>
       <c r="C329" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D329" s="5">
         <v>1</v>
@@ -5213,7 +5213,7 @@
       <c r="A330" s="4"/>
       <c r="B330" s="4"/>
       <c r="C330" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D330" s="5">
         <v>1</v>
@@ -5223,7 +5223,7 @@
       <c r="A331" s="4"/>
       <c r="B331" s="4"/>
       <c r="C331" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D331" s="5">
         <v>1</v>
@@ -5233,7 +5233,7 @@
       <c r="A332" s="4"/>
       <c r="B332" s="4"/>
       <c r="C332" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D332" s="5">
         <v>1</v>
@@ -5243,7 +5243,7 @@
       <c r="A333" s="4"/>
       <c r="B333" s="4"/>
       <c r="C333" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D333" s="5">
         <v>1</v>
@@ -5252,10 +5252,10 @@
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C334" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="C334" s="7" t="s">
-        <v>372</v>
       </c>
       <c r="D334" s="5">
         <v>1</v>
@@ -5265,7 +5265,7 @@
       <c r="A335" s="4"/>
       <c r="B335" s="4"/>
       <c r="C335" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D335" s="5">
         <v>1</v>
@@ -5275,7 +5275,7 @@
       <c r="A336" s="4"/>
       <c r="B336" s="4"/>
       <c r="C336" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D336" s="5">
         <v>1</v>
@@ -5285,7 +5285,7 @@
       <c r="A337" s="4"/>
       <c r="B337" s="4"/>
       <c r="C337" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D337" s="5">
         <v>1</v>
@@ -5295,7 +5295,7 @@
       <c r="A338" s="4"/>
       <c r="B338" s="4"/>
       <c r="C338" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D338" s="5">
         <v>1</v>
@@ -5305,7 +5305,7 @@
       <c r="A339" s="4"/>
       <c r="B339" s="4"/>
       <c r="C339" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D339" s="5">
         <v>1</v>
@@ -5315,7 +5315,7 @@
       <c r="A340" s="4"/>
       <c r="B340" s="4"/>
       <c r="C340" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D340" s="5">
         <v>1</v>
@@ -5325,7 +5325,7 @@
       <c r="A341" s="4"/>
       <c r="B341" s="4"/>
       <c r="C341" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D341" s="5">
         <v>1</v>
@@ -5335,7 +5335,7 @@
       <c r="A342" s="4"/>
       <c r="B342" s="4"/>
       <c r="C342" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D342" s="5">
         <v>1</v>
@@ -5345,7 +5345,7 @@
       <c r="A343" s="4"/>
       <c r="B343" s="4"/>
       <c r="C343" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D343" s="5">
         <v>1</v>
@@ -5355,7 +5355,7 @@
       <c r="A344" s="4"/>
       <c r="B344" s="4"/>
       <c r="C344" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D344" s="5">
         <v>1</v>
@@ -5365,7 +5365,7 @@
       <c r="A345" s="4"/>
       <c r="B345" s="4"/>
       <c r="C345" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D345" s="5">
         <v>1</v>
@@ -5373,13 +5373,13 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C346" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="B346" s="4" t="s">
-        <v>422</v>
-      </c>
-      <c r="C346" s="7" t="s">
-        <v>385</v>
       </c>
       <c r="D346" s="5">
         <v>1</v>
@@ -5389,7 +5389,7 @@
       <c r="A347" s="4"/>
       <c r="B347" s="4"/>
       <c r="C347" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D347" s="5">
         <v>1</v>
@@ -5399,7 +5399,7 @@
       <c r="A348" s="4"/>
       <c r="B348" s="4"/>
       <c r="C348" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D348" s="5">
         <v>1</v>
@@ -5409,7 +5409,7 @@
       <c r="A349" s="4"/>
       <c r="B349" s="4"/>
       <c r="C349" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D349" s="5">
         <v>1</v>
@@ -5419,7 +5419,7 @@
       <c r="A350" s="4"/>
       <c r="B350" s="4"/>
       <c r="C350" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D350" s="5">
         <v>1</v>
@@ -5429,7 +5429,7 @@
       <c r="A351" s="4"/>
       <c r="B351" s="4"/>
       <c r="C351" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D351" s="5">
         <v>1</v>
@@ -5439,7 +5439,7 @@
       <c r="A352" s="4"/>
       <c r="B352" s="4"/>
       <c r="C352" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D352" s="5">
         <v>1</v>
@@ -5449,7 +5449,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D353" s="5">
         <v>1</v>
@@ -5458,10 +5458,10 @@
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A354" s="4"/>
       <c r="B354" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C354" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="C354" s="7" t="s">
-        <v>394</v>
       </c>
       <c r="D354" s="5">
         <v>1</v>
@@ -5471,7 +5471,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D355" s="5">
         <v>1</v>
@@ -5481,7 +5481,7 @@
       <c r="A356" s="4"/>
       <c r="B356" s="4"/>
       <c r="C356" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D356" s="5">
         <v>1</v>
@@ -5491,7 +5491,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D357" s="5">
         <v>1</v>
@@ -5501,7 +5501,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D358" s="5">
         <v>1</v>
@@ -5511,7 +5511,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D359" s="5">
         <v>1</v>
@@ -5521,7 +5521,7 @@
       <c r="A360" s="4"/>
       <c r="B360" s="4"/>
       <c r="C360" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D360" s="5">
         <v>1</v>
@@ -5531,7 +5531,7 @@
       <c r="A361" s="4"/>
       <c r="B361" s="4"/>
       <c r="C361" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D361" s="5">
         <v>1</v>
@@ -5539,11 +5539,11 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B362" s="4"/>
       <c r="C362" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D362" s="5">
         <v>1</v>
@@ -5553,7 +5553,7 @@
       <c r="A363" s="4"/>
       <c r="B363" s="4"/>
       <c r="C363" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D363" s="5">
         <v>1</v>
@@ -5563,7 +5563,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D364" s="5">
         <v>1</v>
@@ -5573,7 +5573,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D365" s="5">
         <v>1</v>
@@ -5583,7 +5583,7 @@
       <c r="A366" s="4"/>
       <c r="B366" s="4"/>
       <c r="C366" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D366" s="5">
         <v>1</v>
@@ -5593,7 +5593,7 @@
       <c r="A367" s="4"/>
       <c r="B367" s="4"/>
       <c r="C367" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D367" s="5">
         <v>1</v>
@@ -5601,11 +5601,11 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B368" s="4"/>
       <c r="C368" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D368" s="5">
         <v>1</v>
@@ -5615,7 +5615,7 @@
       <c r="A369" s="4"/>
       <c r="B369" s="4"/>
       <c r="C369" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D369" s="5">
         <v>1</v>
@@ -5625,7 +5625,7 @@
       <c r="A370" s="4"/>
       <c r="B370" s="4"/>
       <c r="C370" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D370" s="5">
         <v>1</v>
@@ -5635,7 +5635,7 @@
       <c r="A371" s="4"/>
       <c r="B371" s="4"/>
       <c r="C371" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D371" s="5">
         <v>1</v>
@@ -5904,11 +5904,11 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -5916,11 +5916,11 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
@@ -5928,11 +5928,11 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
